--- a/Treinamento/Index/Relatório de Recusas 23.02.2026 a 01.03.2026.xlsx
+++ b/Treinamento/Index/Relatório de Recusas 23.02.2026 a 01.03.2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/shirlei_witkowski_allianz_com_br/Documents/Planilha de recusa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{539304B4-426F-4B43-979D-718B765BEB8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A6A7E49-6A09-4E11-9B63-F6455DF9E5CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="23.02" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="168">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -366,6 +366,234 @@
   </si>
   <si>
     <t> O ano modelo informado não corresponde ao chassi do veículo.</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>GABRIEL ALAMINO SABIO FILHO CPF 01532488823</t>
+  </si>
+  <si>
+    <t>sem retorno de pendencia</t>
+  </si>
+  <si>
+    <t>ELISON DE LIMA ANDRADE CPF 05681797490</t>
+  </si>
+  <si>
+    <t>LIENE CRISTINA ATTAB DE ANGELIS CPF 29071511855</t>
+  </si>
+  <si>
+    <t>CAMILA MILANI CPF 02689481006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULO JAIR CAVALINI                          </t>
+  </si>
+  <si>
+    <t>Outros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIANA VERNASCHI SILVA                      </t>
+  </si>
+  <si>
+    <t>Apólice a renovar já utilizada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELISEU SOUSA SILVA                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Falta de vistoria </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANGELICA LUISA GAUSS                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veículo em duplicidade  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANDRA REGINA VALADAO                        </t>
+  </si>
+  <si>
+    <t>Inspeção Veicular obrigatória</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIVANILDO DOS SANTOS                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROGESON SEVERINO DA SILVA ME                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUILHERME ALBERTO DE SOUZA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMILA MILANI                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE RICARDO LEITE MARTINS                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCCA AUGUSTO MOREIRA SANTOS                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCO AURELIO ANTUNES DA SILVA               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELISON DE LIMA ANDRADE                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GILMAR MARTINS DA SILVA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RADAMES ALVES DOS REIS PEREIRA               </t>
+  </si>
+  <si>
+    <t>Chassi da cotação difere do Chassi da emissão</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERICA DANIELA ALMEIDA DE BARROS              </t>
+  </si>
+  <si>
+    <t>Co
+nforme regra, apólice não completou 365 dias vigente , portanto de
+ve-se manter a classe de bônus, assim sendo o bônus correto 0.
+Com a correção ficou 10x R$ 412,64. Podemos emitir desta forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEBORA ASSIS DOS SANTOS                      </t>
+  </si>
+  <si>
+    <t>Correção de bônus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILIPE BAILUNE SAMPAIO                       </t>
+  </si>
+  <si>
+    <t>d
+entificamos que a proposta foi transmitida com bônus 4, conforme C
+BE bonificação está incorreta, apólice anterior consta classe de b
+ônus 4, não havendo sinistro, conforme regra concede 1 classe de b
+ônus, assim sendo o correto bônus 5.
+Com a correção ficou 10x
+R$ 184,17. Podemos emitir desta forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUBENS NETO DUARTE                           </t>
+  </si>
+  <si>
+    <t>Co
+nforme CBE houve quebra de vigência de 104 dias e não houve sinist
+ro , conforme regra reduz 2 classes de bônus, assim sendo o corret
+o bônus 0.
+Com a correção ficou 10x R$ 299,65. Podemos emitir
+desta forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSANGELA ISABEL SANTO URBANO DELLA TORRE    </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, a apólice foi renovada na
+congênere de origem. Portanto, peço a gentileza de encaminhar a d
+ocumentação abaixo para análise:
+ Cópia da apólice congênere c
+om vigência de 2026 a 2027;
+ Endosso de cancelamento emitido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARLENE BEZERRA GUEDES                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCIO DE CASTRO                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GILBERTO LUIZ DA MOTA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JANERLANIA EDNA DOS SANTOS                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA CECILIA DE OLIVEIRA FIGUEIREDO         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA JOSE BATISTA DA SILVA                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOS ALBERTO PRADA MARTINS SIQUEIRA        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">WILLIAN LEANDRO GOMES                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANGELA MARIA MARCELINO                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAIRONE MESSIAS ROSA                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRACE DI NAPOLI PIZZERIA ARTIGIANALE LTDA ME </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIRIAM BENEDETTI NARVAZ                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANA PAULA MARTINES DE AZEVEDO DA SILVA       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">THIAGO REIS RODRIGUES                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIEL SANTOS SANTANA FREIRE                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAGNER GRAZZIOTTI GONCALVES                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IANES LESSA PINHEIRO VARGAS                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIS FERNANDO MARTINEZ                       </t>
+  </si>
+  <si>
+    <t>Favor enviar cópia do endosso de cancelamento da apólice 2025/202
+6 através desse e-mail.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TALITA SCHOLL                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDREIA DO SOCORRO DOS ANJOS BASTOS LTDA ME  </t>
+  </si>
+  <si>
+    <t>BENEDITO PEREIRA DA SILVA CASA DE CARNES LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDHERSON MATEUS CAVALCANTE DA COSTA         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALAN GABRIEL GODENY                          </t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 23.02.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MICHAEL DOUGLAS VIEIRA MACEDO                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCIA APARECIDA GONCALVES                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RODRIGO MARTINEZ PEREIRA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIVIA SILVA DE OLIVEIRA AMORIM               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RONY DE ARAUJO OLIVEIRA                      </t>
+  </si>
+  <si>
+    <t>Veículo informado é diferente do calculado - Vei
+culo Usado
+Identificamos uma divergência entre o modelo do
+veículo informado na transmissão da proposta devido a isso estamo
+s recusando a proposta em questão.</t>
   </si>
 </sst>
 </file>
@@ -430,7 +658,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -671,12 +899,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -826,9 +1065,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -853,8 +1089,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -874,13 +1109,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -896,7 +1127,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -905,22 +1136,23 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Plan2_1" xfId="1" xr:uid="{69F13A52-20D9-46CA-8619-BC7A1BA09FD8}"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1324,19 +1556,19 @@
       <c r="C2" s="25">
         <v>46076</v>
       </c>
-      <c r="D2" s="81">
+      <c r="D2" s="22">
         <v>136644540</v>
       </c>
       <c r="E2" s="17">
         <v>3450244545</v>
       </c>
-      <c r="F2" s="71" t="s">
+      <c r="F2" s="11" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="83" t="s">
+      <c r="H2" s="44" t="s">
         <v>12</v>
       </c>
       <c r="I2" s="43">
@@ -1353,13 +1585,13 @@
       <c r="C3" s="25">
         <v>46076</v>
       </c>
-      <c r="D3" s="81">
+      <c r="D3" s="22">
         <v>136703723</v>
       </c>
       <c r="E3" s="17">
         <v>3450249385</v>
       </c>
-      <c r="F3" s="71" t="s">
+      <c r="F3" s="11" t="s">
         <v>13</v>
       </c>
       <c r="G3" s="42" t="s">
@@ -1382,13 +1614,13 @@
       <c r="C4" s="25">
         <v>46076</v>
       </c>
-      <c r="D4" s="81">
+      <c r="D4" s="22">
         <v>136702771</v>
       </c>
       <c r="E4" s="17">
         <v>3450249319</v>
       </c>
-      <c r="F4" s="71" t="s">
+      <c r="F4" s="11" t="s">
         <v>16</v>
       </c>
       <c r="G4" s="42" t="s">
@@ -1411,19 +1643,19 @@
       <c r="C5" s="25">
         <v>46076</v>
       </c>
-      <c r="D5" s="81">
+      <c r="D5" s="22">
         <v>136709355</v>
       </c>
       <c r="E5" s="17">
         <v>3450249759</v>
       </c>
-      <c r="F5" s="71" t="s">
+      <c r="F5" s="11" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="83" t="s">
+      <c r="H5" s="44" t="s">
         <v>20</v>
       </c>
       <c r="I5" s="43">
@@ -1440,13 +1672,13 @@
       <c r="C6" s="25">
         <v>46076</v>
       </c>
-      <c r="D6" s="81">
+      <c r="D6" s="22">
         <v>136711910</v>
       </c>
       <c r="E6" s="17">
         <v>3450249979</v>
       </c>
-      <c r="F6" s="71" t="s">
+      <c r="F6" s="11" t="s">
         <v>21</v>
       </c>
       <c r="G6" s="42" t="s">
@@ -1469,19 +1701,19 @@
       <c r="C7" s="25">
         <v>46076</v>
       </c>
-      <c r="D7" s="81">
+      <c r="D7" s="22">
         <v>136650596</v>
       </c>
       <c r="E7" s="17">
         <v>3450246096</v>
       </c>
-      <c r="F7" s="71" t="s">
+      <c r="F7" s="11" t="s">
         <v>24</v>
       </c>
       <c r="G7" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="83" t="s">
+      <c r="H7" s="44" t="s">
         <v>25</v>
       </c>
       <c r="I7" s="43">
@@ -1498,19 +1730,19 @@
       <c r="C8" s="25">
         <v>46076</v>
       </c>
-      <c r="D8" s="81">
+      <c r="D8" s="22">
         <v>136653043</v>
       </c>
       <c r="E8" s="17">
         <v>3450246305</v>
       </c>
-      <c r="F8" s="71" t="s">
+      <c r="F8" s="11" t="s">
         <v>26</v>
       </c>
       <c r="G8" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="83" t="s">
+      <c r="H8" s="44" t="s">
         <v>27</v>
       </c>
       <c r="I8" s="43">
@@ -1527,13 +1759,13 @@
       <c r="C9" s="25">
         <v>46076</v>
       </c>
-      <c r="D9" s="81">
+      <c r="D9" s="22">
         <v>136695554</v>
       </c>
       <c r="E9" s="17">
         <v>3450248615</v>
       </c>
-      <c r="F9" s="71" t="s">
+      <c r="F9" s="11" t="s">
         <v>28</v>
       </c>
       <c r="G9" s="42" t="s">
@@ -1556,13 +1788,13 @@
       <c r="C10" s="25">
         <v>46076</v>
       </c>
-      <c r="D10" s="81">
+      <c r="D10" s="22">
         <v>136696152</v>
       </c>
       <c r="E10" s="17">
         <v>3450248659</v>
       </c>
-      <c r="F10" s="71" t="s">
+      <c r="F10" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G10" s="42" t="s">
@@ -1585,13 +1817,13 @@
       <c r="C11" s="25">
         <v>46076</v>
       </c>
-      <c r="D11" s="81">
+      <c r="D11" s="22">
         <v>136698227</v>
       </c>
       <c r="E11" s="17">
         <v>3450248835</v>
       </c>
-      <c r="F11" s="71" t="s">
+      <c r="F11" s="11" t="s">
         <v>31</v>
       </c>
       <c r="G11" s="42" t="s">
@@ -1614,13 +1846,13 @@
       <c r="C12" s="25">
         <v>46076</v>
       </c>
-      <c r="D12" s="81">
+      <c r="D12" s="22">
         <v>136699763</v>
       </c>
       <c r="E12" s="17">
         <v>3450248956</v>
       </c>
-      <c r="F12" s="71" t="s">
+      <c r="F12" s="11" t="s">
         <v>32</v>
       </c>
       <c r="G12" s="42" t="s">
@@ -1643,13 +1875,13 @@
       <c r="C13" s="25">
         <v>46076</v>
       </c>
-      <c r="D13" s="81">
+      <c r="D13" s="22">
         <v>136701112</v>
       </c>
       <c r="E13" s="17">
         <v>3450249110</v>
       </c>
-      <c r="F13" s="71" t="s">
+      <c r="F13" s="11" t="s">
         <v>33</v>
       </c>
       <c r="G13" s="42" t="s">
@@ -1672,13 +1904,13 @@
       <c r="C14" s="25">
         <v>46076</v>
       </c>
-      <c r="D14" s="81">
+      <c r="D14" s="22">
         <v>136701862</v>
       </c>
       <c r="E14" s="17">
         <v>3450242576</v>
       </c>
-      <c r="F14" s="71" t="s">
+      <c r="F14" s="11" t="s">
         <v>34</v>
       </c>
       <c r="G14" s="42" t="s">
@@ -1701,13 +1933,13 @@
       <c r="C15" s="25">
         <v>46076</v>
       </c>
-      <c r="D15" s="81">
+      <c r="D15" s="22">
         <v>136702698</v>
       </c>
       <c r="E15" s="17">
         <v>3450249286</v>
       </c>
-      <c r="F15" s="71" t="s">
+      <c r="F15" s="11" t="s">
         <v>35</v>
       </c>
       <c r="G15" s="42" t="s">
@@ -1730,13 +1962,13 @@
       <c r="C16" s="25">
         <v>46076</v>
       </c>
-      <c r="D16" s="81">
+      <c r="D16" s="22">
         <v>136703294</v>
       </c>
       <c r="E16" s="17">
         <v>3450249330</v>
       </c>
-      <c r="F16" s="71" t="s">
+      <c r="F16" s="11" t="s">
         <v>36</v>
       </c>
       <c r="G16" s="42" t="s">
@@ -1759,13 +1991,13 @@
       <c r="C17" s="25">
         <v>46076</v>
       </c>
-      <c r="D17" s="81">
+      <c r="D17" s="22">
         <v>136703949</v>
       </c>
       <c r="E17" s="17">
         <v>3450249429</v>
       </c>
-      <c r="F17" s="71" t="s">
+      <c r="F17" s="11" t="s">
         <v>39</v>
       </c>
       <c r="G17" s="42" t="s">
@@ -1788,13 +2020,13 @@
       <c r="C18" s="25">
         <v>46076</v>
       </c>
-      <c r="D18" s="81">
+      <c r="D18" s="22">
         <v>136705066</v>
       </c>
       <c r="E18" s="17">
         <v>3450249495</v>
       </c>
-      <c r="F18" s="71" t="s">
+      <c r="F18" s="11" t="s">
         <v>40</v>
       </c>
       <c r="G18" s="42" t="s">
@@ -1817,13 +2049,13 @@
       <c r="C19" s="25">
         <v>46076</v>
       </c>
-      <c r="D19" s="81">
+      <c r="D19" s="22">
         <v>136706584</v>
       </c>
       <c r="E19" s="17">
         <v>3450249583</v>
       </c>
-      <c r="F19" s="71" t="s">
+      <c r="F19" s="11" t="s">
         <v>41</v>
       </c>
       <c r="G19" s="42" t="s">
@@ -1846,13 +2078,13 @@
       <c r="C20" s="25">
         <v>46076</v>
       </c>
-      <c r="D20" s="81">
+      <c r="D20" s="22">
         <v>136709051</v>
       </c>
       <c r="E20" s="17">
         <v>3450249726</v>
       </c>
-      <c r="F20" s="71" t="s">
+      <c r="F20" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G20" s="42" t="s">
@@ -1875,19 +2107,19 @@
       <c r="C21" s="25">
         <v>46076</v>
       </c>
-      <c r="D21" s="81">
+      <c r="D21" s="22">
         <v>136709458</v>
       </c>
       <c r="E21" s="17">
         <v>3450249760</v>
       </c>
-      <c r="F21" s="71" t="s">
+      <c r="F21" s="11" t="s">
         <v>43</v>
       </c>
       <c r="G21" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="H21" s="83" t="s">
+      <c r="H21" s="44" t="s">
         <v>44</v>
       </c>
       <c r="I21" s="43">
@@ -1904,13 +2136,13 @@
       <c r="C22" s="25">
         <v>46076</v>
       </c>
-      <c r="D22" s="81">
+      <c r="D22" s="22">
         <v>136710590</v>
       </c>
       <c r="E22" s="17">
         <v>3450249870</v>
       </c>
-      <c r="F22" s="71" t="s">
+      <c r="F22" s="11" t="s">
         <v>45</v>
       </c>
       <c r="G22" s="42" t="s">
@@ -1933,13 +2165,13 @@
       <c r="C23" s="25">
         <v>46076</v>
       </c>
-      <c r="D23" s="81">
+      <c r="D23" s="22">
         <v>136712058</v>
       </c>
       <c r="E23" s="17">
         <v>3450250012</v>
       </c>
-      <c r="F23" s="71" t="s">
+      <c r="F23" s="11" t="s">
         <v>46</v>
       </c>
       <c r="G23" s="42" t="s">
@@ -1962,13 +2194,13 @@
       <c r="C24" s="25">
         <v>46076</v>
       </c>
-      <c r="D24" s="81">
+      <c r="D24" s="22">
         <v>136712893</v>
       </c>
       <c r="E24" s="17">
         <v>3450250067</v>
       </c>
-      <c r="F24" s="71" t="s">
+      <c r="F24" s="11" t="s">
         <v>47</v>
       </c>
       <c r="G24" s="42" t="s">
@@ -1991,13 +2223,13 @@
       <c r="C25" s="25">
         <v>46076</v>
       </c>
-      <c r="D25" s="81">
+      <c r="D25" s="22">
         <v>136713212</v>
       </c>
       <c r="E25" s="17">
         <v>3450250078</v>
       </c>
-      <c r="F25" s="71" t="s">
+      <c r="F25" s="11" t="s">
         <v>48</v>
       </c>
       <c r="G25" s="42" t="s">
@@ -2020,13 +2252,13 @@
       <c r="C26" s="25">
         <v>46076</v>
       </c>
-      <c r="D26" s="81">
+      <c r="D26" s="22">
         <v>136713293</v>
       </c>
       <c r="E26" s="17">
         <v>3450250090</v>
       </c>
-      <c r="F26" s="71" t="s">
+      <c r="F26" s="11" t="s">
         <v>49</v>
       </c>
       <c r="G26" s="42" t="s">
@@ -2049,13 +2281,13 @@
       <c r="C27" s="25">
         <v>46076</v>
       </c>
-      <c r="D27" s="81">
+      <c r="D27" s="22">
         <v>136780424</v>
       </c>
       <c r="E27" s="17">
         <v>3450253972</v>
       </c>
-      <c r="F27" s="71" t="s">
+      <c r="F27" s="11" t="s">
         <v>51</v>
       </c>
       <c r="G27" s="42" t="s">
@@ -2078,13 +2310,13 @@
       <c r="C28" s="25">
         <v>46076</v>
       </c>
-      <c r="D28" s="81">
+      <c r="D28" s="22">
         <v>136757725</v>
       </c>
       <c r="E28" s="17">
         <v>3450253026</v>
       </c>
-      <c r="F28" s="71" t="s">
+      <c r="F28" s="11" t="s">
         <v>54</v>
       </c>
       <c r="G28" s="42" t="s">
@@ -2107,13 +2339,13 @@
       <c r="C29" s="25">
         <v>46076</v>
       </c>
-      <c r="D29" s="81">
+      <c r="D29" s="22">
         <v>136793836</v>
       </c>
       <c r="E29" s="17">
         <v>3450254819</v>
       </c>
-      <c r="F29" s="71" t="s">
+      <c r="F29" s="11" t="s">
         <v>56</v>
       </c>
       <c r="G29" s="42" t="s">
@@ -2136,13 +2368,13 @@
       <c r="C30" s="25">
         <v>46076</v>
       </c>
-      <c r="D30" s="81">
+      <c r="D30" s="22">
         <v>136726098</v>
       </c>
       <c r="E30" s="17">
         <v>3450250606</v>
       </c>
-      <c r="F30" s="71" t="s">
+      <c r="F30" s="11" t="s">
         <v>57</v>
       </c>
       <c r="G30" s="42" t="s">
@@ -2155,32 +2387,32 @@
         <v>46073</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="93" customFormat="1">
-      <c r="A31" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" s="85">
+    <row r="31" spans="1:9" s="89" customFormat="1">
+      <c r="A31" s="80" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="81">
         <v>46066</v>
       </c>
-      <c r="C31" s="86">
+      <c r="C31" s="82">
         <v>46076</v>
       </c>
-      <c r="D31" s="87">
+      <c r="D31" s="83">
         <v>136751753</v>
       </c>
-      <c r="E31" s="88">
+      <c r="E31" s="84">
         <v>3450252531</v>
       </c>
-      <c r="F31" s="89" t="s">
+      <c r="F31" s="85" t="s">
         <v>58</v>
       </c>
-      <c r="G31" s="90" t="s">
+      <c r="G31" s="86" t="s">
         <v>37</v>
       </c>
-      <c r="H31" s="91" t="s">
+      <c r="H31" s="87" t="s">
         <v>55</v>
       </c>
-      <c r="I31" s="92">
+      <c r="I31" s="88">
         <v>46073</v>
       </c>
     </row>
@@ -2194,13 +2426,13 @@
       <c r="C32" s="25">
         <v>46076</v>
       </c>
-      <c r="D32" s="81">
+      <c r="D32" s="22">
         <v>136741623</v>
       </c>
       <c r="E32" s="17">
         <v>3450251662</v>
       </c>
-      <c r="F32" s="71" t="s">
+      <c r="F32" s="11" t="s">
         <v>59</v>
       </c>
       <c r="G32" s="42" t="s">
@@ -2223,13 +2455,13 @@
       <c r="C33" s="25">
         <v>46076</v>
       </c>
-      <c r="D33" s="81">
+      <c r="D33" s="22">
         <v>136741773</v>
       </c>
       <c r="E33" s="17">
         <v>3450251695</v>
       </c>
-      <c r="F33" s="71" t="s">
+      <c r="F33" s="11" t="s">
         <v>60</v>
       </c>
       <c r="G33" s="42" t="s">
@@ -2252,13 +2484,13 @@
       <c r="C34" s="25">
         <v>46076</v>
       </c>
-      <c r="D34" s="81">
+      <c r="D34" s="22">
         <v>136743307</v>
       </c>
       <c r="E34" s="17">
         <v>3450247130</v>
       </c>
-      <c r="F34" s="71" t="s">
+      <c r="F34" s="11" t="s">
         <v>61</v>
       </c>
       <c r="G34" s="42" t="s">
@@ -2281,13 +2513,13 @@
       <c r="C35" s="25">
         <v>46076</v>
       </c>
-      <c r="D35" s="81">
+      <c r="D35" s="22">
         <v>136745446</v>
       </c>
       <c r="E35" s="17">
         <v>3450251960</v>
       </c>
-      <c r="F35" s="71" t="s">
+      <c r="F35" s="11" t="s">
         <v>62</v>
       </c>
       <c r="G35" s="42" t="s">
@@ -2310,13 +2542,13 @@
       <c r="C36" s="25">
         <v>46076</v>
       </c>
-      <c r="D36" s="81">
+      <c r="D36" s="22">
         <v>136745892</v>
       </c>
       <c r="E36" s="17">
         <v>3450252036</v>
       </c>
-      <c r="F36" s="71" t="s">
+      <c r="F36" s="11" t="s">
         <v>63</v>
       </c>
       <c r="G36" s="42" t="s">
@@ -2339,13 +2571,13 @@
       <c r="C37" s="25">
         <v>46076</v>
       </c>
-      <c r="D37" s="81">
+      <c r="D37" s="22">
         <v>136746253</v>
       </c>
       <c r="E37" s="17">
         <v>3450252069</v>
       </c>
-      <c r="F37" s="71" t="s">
+      <c r="F37" s="11" t="s">
         <v>64</v>
       </c>
       <c r="G37" s="42" t="s">
@@ -2368,13 +2600,13 @@
       <c r="C38" s="25">
         <v>46076</v>
       </c>
-      <c r="D38" s="81">
+      <c r="D38" s="22">
         <v>136747220</v>
       </c>
       <c r="E38" s="17">
         <v>3450252102</v>
       </c>
-      <c r="F38" s="71" t="s">
+      <c r="F38" s="11" t="s">
         <v>65</v>
       </c>
       <c r="G38" s="42" t="s">
@@ -2397,13 +2629,13 @@
       <c r="C39" s="25">
         <v>46076</v>
       </c>
-      <c r="D39" s="81">
+      <c r="D39" s="22">
         <v>136747223</v>
       </c>
       <c r="E39" s="17">
         <v>3450250001</v>
       </c>
-      <c r="F39" s="71" t="s">
+      <c r="F39" s="11" t="s">
         <v>66</v>
       </c>
       <c r="G39" s="42" t="s">
@@ -2426,13 +2658,13 @@
       <c r="C40" s="25">
         <v>46076</v>
       </c>
-      <c r="D40" s="81">
+      <c r="D40" s="22">
         <v>136747238</v>
       </c>
       <c r="E40" s="17">
         <v>3450252113</v>
       </c>
-      <c r="F40" s="71" t="s">
+      <c r="F40" s="11" t="s">
         <v>67</v>
       </c>
       <c r="G40" s="42" t="s">
@@ -2455,13 +2687,13 @@
       <c r="C41" s="25">
         <v>46076</v>
       </c>
-      <c r="D41" s="81">
+      <c r="D41" s="22">
         <v>136748548</v>
       </c>
       <c r="E41" s="17">
         <v>3450252223</v>
       </c>
-      <c r="F41" s="71" t="s">
+      <c r="F41" s="11" t="s">
         <v>68</v>
       </c>
       <c r="G41" s="42" t="s">
@@ -2484,13 +2716,13 @@
       <c r="C42" s="25">
         <v>46076</v>
       </c>
-      <c r="D42" s="81">
+      <c r="D42" s="22">
         <v>136748679</v>
       </c>
       <c r="E42" s="17">
         <v>3450252234</v>
       </c>
-      <c r="F42" s="71" t="s">
+      <c r="F42" s="11" t="s">
         <v>69</v>
       </c>
       <c r="G42" s="42" t="s">
@@ -2513,13 +2745,13 @@
       <c r="C43" s="25">
         <v>46076</v>
       </c>
-      <c r="D43" s="81">
+      <c r="D43" s="22">
         <v>136749016</v>
       </c>
       <c r="E43" s="17">
         <v>3450249352</v>
       </c>
-      <c r="F43" s="71" t="s">
+      <c r="F43" s="11" t="s">
         <v>70</v>
       </c>
       <c r="G43" s="42" t="s">
@@ -2542,13 +2774,13 @@
       <c r="C44" s="25">
         <v>46076</v>
       </c>
-      <c r="D44" s="81">
+      <c r="D44" s="22">
         <v>136749185</v>
       </c>
       <c r="E44" s="17">
         <v>3450252289</v>
       </c>
-      <c r="F44" s="71" t="s">
+      <c r="F44" s="11" t="s">
         <v>71</v>
       </c>
       <c r="G44" s="42" t="s">
@@ -2571,13 +2803,13 @@
       <c r="C45" s="25">
         <v>46076</v>
       </c>
-      <c r="D45" s="81">
+      <c r="D45" s="22">
         <v>136749240</v>
       </c>
       <c r="E45" s="17">
         <v>3450252300</v>
       </c>
-      <c r="F45" s="71" t="s">
+      <c r="F45" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G45" s="42" t="s">
@@ -2600,13 +2832,13 @@
       <c r="C46" s="25">
         <v>46076</v>
       </c>
-      <c r="D46" s="81">
+      <c r="D46" s="22">
         <v>136749297</v>
       </c>
       <c r="E46" s="17">
         <v>3450252311</v>
       </c>
-      <c r="F46" s="71" t="s">
+      <c r="F46" s="11" t="s">
         <v>73</v>
       </c>
       <c r="G46" s="42" t="s">
@@ -2629,13 +2861,13 @@
       <c r="C47" s="25">
         <v>46076</v>
       </c>
-      <c r="D47" s="81">
+      <c r="D47" s="22">
         <v>136749595</v>
       </c>
       <c r="E47" s="17">
         <v>3450249077</v>
       </c>
-      <c r="F47" s="71" t="s">
+      <c r="F47" s="11" t="s">
         <v>76</v>
       </c>
       <c r="G47" s="42" t="s">
@@ -2658,13 +2890,13 @@
       <c r="C48" s="25">
         <v>46076</v>
       </c>
-      <c r="D48" s="81">
+      <c r="D48" s="22">
         <v>136749625</v>
       </c>
       <c r="E48" s="17">
         <v>3450252322</v>
       </c>
-      <c r="F48" s="71" t="s">
+      <c r="F48" s="11" t="s">
         <v>77</v>
       </c>
       <c r="G48" s="42" t="s">
@@ -2687,13 +2919,13 @@
       <c r="C49" s="25">
         <v>46076</v>
       </c>
-      <c r="D49" s="81">
+      <c r="D49" s="22">
         <v>136750369</v>
       </c>
       <c r="E49" s="17">
         <v>3450252421</v>
       </c>
-      <c r="F49" s="71" t="s">
+      <c r="F49" s="11" t="s">
         <v>78</v>
       </c>
       <c r="G49" s="42" t="s">
@@ -2716,13 +2948,13 @@
       <c r="C50" s="25">
         <v>46076</v>
       </c>
-      <c r="D50" s="81">
+      <c r="D50" s="22">
         <v>136751442</v>
       </c>
       <c r="E50" s="17">
         <v>3450252509</v>
       </c>
-      <c r="F50" s="71" t="s">
+      <c r="F50" s="11" t="s">
         <v>79</v>
       </c>
       <c r="G50" s="42" t="s">
@@ -2745,13 +2977,13 @@
       <c r="C51" s="25">
         <v>46076</v>
       </c>
-      <c r="D51" s="81">
+      <c r="D51" s="22">
         <v>136752831</v>
       </c>
       <c r="E51" s="17">
         <v>3450252586</v>
       </c>
-      <c r="F51" s="71" t="s">
+      <c r="F51" s="11" t="s">
         <v>80</v>
       </c>
       <c r="G51" s="42" t="s">
@@ -2774,13 +3006,13 @@
       <c r="C52" s="25">
         <v>46076</v>
       </c>
-      <c r="D52" s="81">
+      <c r="D52" s="22">
         <v>136754474</v>
       </c>
       <c r="E52" s="17">
         <v>3450252751</v>
       </c>
-      <c r="F52" s="71" t="s">
+      <c r="F52" s="11" t="s">
         <v>81</v>
       </c>
       <c r="G52" s="42" t="s">
@@ -2803,13 +3035,13 @@
       <c r="C53" s="25">
         <v>46076</v>
       </c>
-      <c r="D53" s="81">
+      <c r="D53" s="22">
         <v>136754971</v>
       </c>
       <c r="E53" s="17">
         <v>3450252817</v>
       </c>
-      <c r="F53" s="71" t="s">
+      <c r="F53" s="11" t="s">
         <v>82</v>
       </c>
       <c r="G53" s="42" t="s">
@@ -2832,13 +3064,13 @@
       <c r="C54" s="25">
         <v>46076</v>
       </c>
-      <c r="D54" s="81">
+      <c r="D54" s="22">
         <v>136755061</v>
       </c>
       <c r="E54" s="17">
         <v>3450251299</v>
       </c>
-      <c r="F54" s="71" t="s">
+      <c r="F54" s="11" t="s">
         <v>83</v>
       </c>
       <c r="G54" s="42" t="s">
@@ -2861,13 +3093,13 @@
       <c r="C55" s="25">
         <v>46076</v>
       </c>
-      <c r="D55" s="81">
+      <c r="D55" s="22">
         <v>136756419</v>
       </c>
       <c r="E55" s="17">
         <v>3450252950</v>
       </c>
-      <c r="F55" s="71" t="s">
+      <c r="F55" s="11" t="s">
         <v>84</v>
       </c>
       <c r="G55" s="42" t="s">
@@ -2890,13 +3122,13 @@
       <c r="C56" s="25">
         <v>46076</v>
       </c>
-      <c r="D56" s="81">
+      <c r="D56" s="22">
         <v>136756531</v>
       </c>
       <c r="E56" s="17">
         <v>3450250617</v>
       </c>
-      <c r="F56" s="71" t="s">
+      <c r="F56" s="11" t="s">
         <v>85</v>
       </c>
       <c r="G56" s="42" t="s">
@@ -2919,13 +3151,13 @@
       <c r="C57" s="25">
         <v>46076</v>
       </c>
-      <c r="D57" s="81">
+      <c r="D57" s="22">
         <v>136759573</v>
       </c>
       <c r="E57" s="17">
         <v>3450253158</v>
       </c>
-      <c r="F57" s="71" t="s">
+      <c r="F57" s="11" t="s">
         <v>86</v>
       </c>
       <c r="G57" s="42" t="s">
@@ -2948,13 +3180,13 @@
       <c r="C58" s="25">
         <v>46076</v>
       </c>
-      <c r="D58" s="81">
+      <c r="D58" s="22">
         <v>136759623</v>
       </c>
       <c r="E58" s="17">
         <v>3450253169</v>
       </c>
-      <c r="F58" s="71" t="s">
+      <c r="F58" s="11" t="s">
         <v>87</v>
       </c>
       <c r="G58" s="42" t="s">
@@ -2977,13 +3209,13 @@
       <c r="C59" s="25">
         <v>46076</v>
       </c>
-      <c r="D59" s="81">
+      <c r="D59" s="22">
         <v>136760271</v>
       </c>
       <c r="E59" s="17">
         <v>3450253235</v>
       </c>
-      <c r="F59" s="71" t="s">
+      <c r="F59" s="11" t="s">
         <v>88</v>
       </c>
       <c r="G59" s="42" t="s">
@@ -3006,13 +3238,13 @@
       <c r="C60" s="25">
         <v>46076</v>
       </c>
-      <c r="D60" s="81">
+      <c r="D60" s="22">
         <v>136760300</v>
       </c>
       <c r="E60" s="17">
         <v>3450253246</v>
       </c>
-      <c r="F60" s="71" t="s">
+      <c r="F60" s="11" t="s">
         <v>89</v>
       </c>
       <c r="G60" s="42" t="s">
@@ -3035,13 +3267,13 @@
       <c r="C61" s="25">
         <v>46076</v>
       </c>
-      <c r="D61" s="81">
+      <c r="D61" s="22">
         <v>136761612</v>
       </c>
       <c r="E61" s="17">
         <v>3450253378</v>
       </c>
-      <c r="F61" s="71" t="s">
+      <c r="F61" s="11" t="s">
         <v>90</v>
       </c>
       <c r="G61" s="42" t="s">
@@ -3064,13 +3296,13 @@
       <c r="C62" s="25">
         <v>46076</v>
       </c>
-      <c r="D62" s="81">
+      <c r="D62" s="22">
         <v>136761764</v>
       </c>
       <c r="E62" s="17">
         <v>3450253390</v>
       </c>
-      <c r="F62" s="71" t="s">
+      <c r="F62" s="11" t="s">
         <v>91</v>
       </c>
       <c r="G62" s="42" t="s">
@@ -3093,13 +3325,13 @@
       <c r="C63" s="25">
         <v>46076</v>
       </c>
-      <c r="D63" s="81">
+      <c r="D63" s="22">
         <v>136761926</v>
       </c>
       <c r="E63" s="17">
         <v>3450253400</v>
       </c>
-      <c r="F63" s="71" t="s">
+      <c r="F63" s="11" t="s">
         <v>92</v>
       </c>
       <c r="G63" s="42" t="s">
@@ -3122,13 +3354,13 @@
       <c r="C64" s="25">
         <v>46076</v>
       </c>
-      <c r="D64" s="81">
+      <c r="D64" s="22">
         <v>136761966</v>
       </c>
       <c r="E64" s="17">
         <v>3450253411</v>
       </c>
-      <c r="F64" s="71" t="s">
+      <c r="F64" s="11" t="s">
         <v>93</v>
       </c>
       <c r="G64" s="42" t="s">
@@ -3151,13 +3383,13 @@
       <c r="C65" s="25">
         <v>46076</v>
       </c>
-      <c r="D65" s="81">
+      <c r="D65" s="22">
         <v>136762270</v>
       </c>
       <c r="E65" s="17">
         <v>3450253433</v>
       </c>
-      <c r="F65" s="71" t="s">
+      <c r="F65" s="11" t="s">
         <v>94</v>
       </c>
       <c r="G65" s="42" t="s">
@@ -3180,13 +3412,13 @@
       <c r="C66" s="25">
         <v>46076</v>
       </c>
-      <c r="D66" s="81">
+      <c r="D66" s="22">
         <v>136762890</v>
       </c>
       <c r="E66" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="F66" s="71" t="s">
+      <c r="F66" s="11" t="s">
         <v>96</v>
       </c>
       <c r="G66" s="6" t="s">
@@ -3206,7 +3438,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D55:F66">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A66" xr:uid="{9AD193C7-0C28-47DE-BB22-7B92526E3023}">
@@ -3222,18 +3454,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFA17127-7620-4DD9-9061-6C654E2EC5C2}">
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" customWidth="1"/>
-    <col min="3" max="3" width="21.5703125" customWidth="1"/>
-    <col min="4" max="4" width="27.7109375" style="16" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" customWidth="1"/>
-    <col min="6" max="6" width="31.5703125" customWidth="1"/>
-    <col min="7" max="7" width="19.7109375" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" style="15" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34.42578125" customWidth="1"/>
+    <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="31.85546875" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" style="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -3275,7 +3507,7 @@
       <c r="C2" s="55">
         <v>46077</v>
       </c>
-      <c r="D2" s="59" t="s">
+      <c r="D2" s="22" t="s">
         <v>97</v>
       </c>
       <c r="E2" s="56">
@@ -3290,423 +3522,1606 @@
       <c r="H2" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="I2" s="58"/>
+      <c r="I2" s="58" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="12"/>
+      <c r="B3" s="7">
+        <v>46058</v>
+      </c>
+      <c r="C3" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="E3" s="56">
+        <v>3450242609</v>
+      </c>
+      <c r="F3" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="G3" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>102</v>
+      </c>
       <c r="I3" s="43"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="12"/>
+      <c r="B4" s="7">
+        <v>46062</v>
+      </c>
+      <c r="C4" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="E4" s="56">
+        <v>3450246261</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="G4" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>102</v>
+      </c>
       <c r="I4" s="43"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="12"/>
+      <c r="B5" s="7">
+        <v>46064</v>
+      </c>
+      <c r="C5" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" s="56">
+        <v>3450249374</v>
+      </c>
+      <c r="F5" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="G5" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>102</v>
+      </c>
       <c r="I5" s="43"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="12"/>
+      <c r="B6" s="7">
+        <v>46071</v>
+      </c>
+      <c r="C6" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" s="56">
+        <v>3450254654</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="G6" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>102</v>
+      </c>
       <c r="I6" s="43"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="11"/>
+      <c r="B7" s="7">
+        <v>46068</v>
+      </c>
+      <c r="C7" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D7" s="90" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" s="63">
+        <v>3450253543</v>
+      </c>
+      <c r="F7" s="91" t="s">
+        <v>105</v>
+      </c>
+      <c r="G7" s="92" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>102</v>
+      </c>
       <c r="I7" s="43"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="55"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="43"/>
+      <c r="B8" s="7">
+        <v>46088</v>
+      </c>
+      <c r="C8" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D8" s="22">
+        <v>136838916</v>
+      </c>
+      <c r="E8" s="17">
+        <v>3450258735</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="G8" s="93" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="78" t="s">
+        <v>107</v>
+      </c>
+      <c r="I8" s="43">
+        <v>46077</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="55"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="43"/>
+      <c r="B9" s="7">
+        <v>46077</v>
+      </c>
+      <c r="C9" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D9" s="22">
+        <v>136728307</v>
+      </c>
+      <c r="E9" s="17">
+        <v>3450250782</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="G9" s="93" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="78" t="s">
+        <v>109</v>
+      </c>
+      <c r="I9" s="43">
+        <v>46077</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="43"/>
+      <c r="B10" s="7">
+        <v>46065</v>
+      </c>
+      <c r="C10" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D10" s="22">
+        <v>136734997</v>
+      </c>
+      <c r="E10" s="17">
+        <v>3450251409</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="G10" s="93" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="78" t="s">
+        <v>111</v>
+      </c>
+      <c r="I10" s="43">
+        <v>46065</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="55"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="43"/>
+      <c r="B11" s="7">
+        <v>46064</v>
+      </c>
+      <c r="C11" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D11" s="22">
+        <v>136722223</v>
+      </c>
+      <c r="E11" s="17">
+        <v>3450250166</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="G11" s="93" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="78" t="s">
+        <v>113</v>
+      </c>
+      <c r="I11" s="43">
+        <v>46077</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="43"/>
+      <c r="B12" s="7">
+        <v>46063</v>
+      </c>
+      <c r="C12" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D12" s="22">
+        <v>136724519</v>
+      </c>
+      <c r="E12" s="17">
+        <v>3450244061</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="G12" s="93" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="78" t="s">
+        <v>115</v>
+      </c>
+      <c r="I12" s="43">
+        <v>46077</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="43"/>
+      <c r="B13" s="7">
+        <v>46065</v>
+      </c>
+      <c r="C13" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D13" s="22">
+        <v>136735180</v>
+      </c>
+      <c r="E13" s="17">
+        <v>3450251420</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="G13" s="93" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="78" t="s">
+        <v>111</v>
+      </c>
+      <c r="I13" s="43">
+        <v>46065</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="43"/>
+      <c r="B14" s="7">
+        <v>46065</v>
+      </c>
+      <c r="C14" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D14" s="22">
+        <v>136723934</v>
+      </c>
+      <c r="E14" s="17">
+        <v>3450250375</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="G14" s="93" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="78" t="s">
+        <v>111</v>
+      </c>
+      <c r="I14" s="43">
+        <v>46065</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="43"/>
+      <c r="B15" s="7">
+        <v>46080</v>
+      </c>
+      <c r="C15" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D15" s="22">
+        <v>136729172</v>
+      </c>
+      <c r="E15" s="17">
+        <v>3450250892</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="G15" s="93" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="78" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="43">
+        <v>46077</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="55"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="43"/>
+      <c r="B16" s="7">
+        <v>46059</v>
+      </c>
+      <c r="C16" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D16" s="22">
+        <v>136725270</v>
+      </c>
+      <c r="E16" s="17">
+        <v>3450243445</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="G16" s="93" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="78" t="s">
+        <v>111</v>
+      </c>
+      <c r="I16" s="43">
+        <v>46059</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="43"/>
+      <c r="B17" s="7">
+        <v>46077</v>
+      </c>
+      <c r="C17" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D17" s="22">
+        <v>136723951</v>
+      </c>
+      <c r="E17" s="17">
+        <v>3450250386</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="G17" s="93" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="78" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" s="43">
+        <v>46077</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="43"/>
+      <c r="B18" s="7">
+        <v>46065</v>
+      </c>
+      <c r="C18" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D18" s="22">
+        <v>136726576</v>
+      </c>
+      <c r="E18" s="17">
+        <v>3450250661</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="G18" s="93" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="78" t="s">
+        <v>111</v>
+      </c>
+      <c r="I18" s="43">
+        <v>46065</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="43"/>
+      <c r="B19" s="7">
+        <v>46059</v>
+      </c>
+      <c r="C19" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D19" s="22">
+        <v>136724366</v>
+      </c>
+      <c r="E19" s="17">
+        <v>3450244248</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="G19" s="93" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="78" t="s">
+        <v>111</v>
+      </c>
+      <c r="I19" s="43">
+        <v>46059</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="43"/>
+      <c r="B20" s="7">
+        <v>46062</v>
+      </c>
+      <c r="C20" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D20" s="22">
+        <v>136730089</v>
+      </c>
+      <c r="E20" s="17">
+        <v>3450246657</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="G20" s="93" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="78" t="s">
+        <v>111</v>
+      </c>
+      <c r="I20" s="43">
+        <v>46062</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="55"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="43"/>
+      <c r="B21" s="7">
+        <v>46079</v>
+      </c>
+      <c r="C21" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D21" s="22">
+        <v>136724217</v>
+      </c>
+      <c r="E21" s="17">
+        <v>3450250430</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="G21" s="93" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" s="78" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" s="43">
+        <v>46077</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="55"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="43"/>
+      <c r="B22" s="7">
+        <v>46065</v>
+      </c>
+      <c r="C22" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D22" s="22">
+        <v>136724245</v>
+      </c>
+      <c r="E22" s="17">
+        <v>3450250441</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="G22" s="93" t="s">
+        <v>22</v>
+      </c>
+      <c r="H22" s="78" t="s">
+        <v>126</v>
+      </c>
+      <c r="I22" s="43">
+        <v>46077</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="43"/>
+      <c r="B23" s="7">
+        <v>46064</v>
+      </c>
+      <c r="C23" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D23" s="22">
+        <v>136673325</v>
+      </c>
+      <c r="E23" s="17">
+        <v>3450247163</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G23" s="93" t="s">
+        <v>11</v>
+      </c>
+      <c r="H23" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="I23" s="43">
+        <v>46076</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="55"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="42"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="43"/>
+      <c r="B24" s="7">
+        <v>46072</v>
+      </c>
+      <c r="C24" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D24" s="22">
+        <v>136724805</v>
+      </c>
+      <c r="E24" s="17">
+        <v>3450250518</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="G24" s="93" t="s">
+        <v>11</v>
+      </c>
+      <c r="H24" s="78" t="s">
+        <v>130</v>
+      </c>
+      <c r="I24" s="43">
+        <v>46077</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="55"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="43"/>
+      <c r="B25" s="7">
+        <v>46087</v>
+      </c>
+      <c r="C25" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D25" s="22">
+        <v>136679933</v>
+      </c>
+      <c r="E25" s="17">
+        <v>3450247560</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="G25" s="93" t="s">
+        <v>11</v>
+      </c>
+      <c r="H25" s="94" t="s">
+        <v>132</v>
+      </c>
+      <c r="I25" s="43">
+        <v>46076</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="55"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="43"/>
+      <c r="B26" s="7">
+        <v>46063</v>
+      </c>
+      <c r="C26" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D26" s="22">
+        <v>136679581</v>
+      </c>
+      <c r="E26" s="17">
+        <v>3450247537</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G26" s="93" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" s="94" t="s">
+        <v>134</v>
+      </c>
+      <c r="I26" s="43">
+        <v>46076</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="55"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="43"/>
+      <c r="B27" s="7">
+        <v>46068</v>
+      </c>
+      <c r="C27" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D27" s="22">
+        <v>136681490</v>
+      </c>
+      <c r="E27" s="17">
+        <v>3450247636</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="G27" s="93" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27" s="94" t="s">
+        <v>136</v>
+      </c>
+      <c r="I27" s="43">
+        <v>46076</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="42"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="43"/>
+      <c r="B28" s="7">
+        <v>46066</v>
+      </c>
+      <c r="C28" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D28" s="22">
+        <v>136722921</v>
+      </c>
+      <c r="E28" s="17">
+        <v>3450250221</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="G28" s="93" t="s">
+        <v>11</v>
+      </c>
+      <c r="H28" s="78" t="s">
+        <v>130</v>
+      </c>
+      <c r="I28" s="43">
+        <v>46077</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="55"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="43"/>
+      <c r="B29" s="7">
+        <v>46065</v>
+      </c>
+      <c r="C29" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D29" s="22">
+        <v>136733403</v>
+      </c>
+      <c r="E29" s="17">
+        <v>3450251211</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="G29" s="93" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29" s="78" t="s">
+        <v>111</v>
+      </c>
+      <c r="I29" s="43">
+        <v>46065</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="55"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="42"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="43"/>
+      <c r="B30" s="7">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D30" s="22">
+        <v>136733601</v>
+      </c>
+      <c r="E30" s="17">
+        <v>3450251255</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="G30" s="93" t="s">
+        <v>17</v>
+      </c>
+      <c r="H30" s="78" t="s">
+        <v>18</v>
+      </c>
+      <c r="I30" s="43">
+        <v>46077</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="55"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="42"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="43"/>
+      <c r="B31" s="7">
+        <v>46065</v>
+      </c>
+      <c r="C31" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D31" s="22">
+        <v>136733681</v>
+      </c>
+      <c r="E31" s="17">
+        <v>3450251266</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="G31" s="93" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" s="78" t="s">
+        <v>111</v>
+      </c>
+      <c r="I31" s="43">
+        <v>46065</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="55"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="43"/>
+      <c r="B32" s="7">
+        <v>46065</v>
+      </c>
+      <c r="C32" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D32" s="22">
+        <v>136733785</v>
+      </c>
+      <c r="E32" s="17">
+        <v>3450251277</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="G32" s="93" t="s">
+        <v>14</v>
+      </c>
+      <c r="H32" s="78" t="s">
+        <v>111</v>
+      </c>
+      <c r="I32" s="43">
+        <v>46065</v>
+      </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="6"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="49"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="24"/>
+      <c r="A33" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="7">
+        <v>46065</v>
+      </c>
+      <c r="C33" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D33" s="22">
+        <v>136727335</v>
+      </c>
+      <c r="E33" s="17">
+        <v>3450250716</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="G33" s="93" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" s="78" t="s">
+        <v>111</v>
+      </c>
+      <c r="I33" s="43">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="7">
+        <v>46065</v>
+      </c>
+      <c r="C34" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D34" s="22">
+        <v>136734786</v>
+      </c>
+      <c r="E34" s="17">
+        <v>3450251376</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="G34" s="93" t="s">
+        <v>14</v>
+      </c>
+      <c r="H34" s="78" t="s">
+        <v>111</v>
+      </c>
+      <c r="I34" s="43">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="7">
+        <v>46066</v>
+      </c>
+      <c r="C35" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D35" s="22">
+        <v>136736493</v>
+      </c>
+      <c r="E35" s="17">
+        <v>3450251519</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="G35" s="93" t="s">
+        <v>17</v>
+      </c>
+      <c r="H35" s="78" t="s">
+        <v>18</v>
+      </c>
+      <c r="I35" s="43">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="7">
+        <v>46065</v>
+      </c>
+      <c r="C36" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D36" s="22">
+        <v>136735931</v>
+      </c>
+      <c r="E36" s="17">
+        <v>3450251442</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="G36" s="93" t="s">
+        <v>14</v>
+      </c>
+      <c r="H36" s="78" t="s">
+        <v>111</v>
+      </c>
+      <c r="I36" s="43">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="7">
+        <v>46065</v>
+      </c>
+      <c r="C37" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D37" s="22">
+        <v>136727233</v>
+      </c>
+      <c r="E37" s="17">
+        <v>3450250705</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="G37" s="93" t="s">
+        <v>14</v>
+      </c>
+      <c r="H37" s="78" t="s">
+        <v>111</v>
+      </c>
+      <c r="I37" s="43">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" s="7">
+        <v>46065</v>
+      </c>
+      <c r="C38" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D38" s="22">
+        <v>136730654</v>
+      </c>
+      <c r="E38" s="17">
+        <v>3450251013</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G38" s="93" t="s">
+        <v>17</v>
+      </c>
+      <c r="H38" s="78" t="s">
+        <v>18</v>
+      </c>
+      <c r="I38" s="43">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" s="7">
+        <v>46067</v>
+      </c>
+      <c r="C39" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D39" s="22">
+        <v>136730967</v>
+      </c>
+      <c r="E39" s="17">
+        <v>3450251024</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="G39" s="93" t="s">
+        <v>17</v>
+      </c>
+      <c r="H39" s="78" t="s">
+        <v>18</v>
+      </c>
+      <c r="I39" s="43">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" s="7">
+        <v>46065</v>
+      </c>
+      <c r="C40" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D40" s="22">
+        <v>136731705</v>
+      </c>
+      <c r="E40" s="17">
+        <v>3450251090</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="G40" s="93" t="s">
+        <v>14</v>
+      </c>
+      <c r="H40" s="78" t="s">
+        <v>111</v>
+      </c>
+      <c r="I40" s="43">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" s="7">
+        <v>46065</v>
+      </c>
+      <c r="C41" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D41" s="22">
+        <v>136733115</v>
+      </c>
+      <c r="E41" s="17">
+        <v>3450251156</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="G41" s="93" t="s">
+        <v>22</v>
+      </c>
+      <c r="H41" s="78" t="s">
+        <v>126</v>
+      </c>
+      <c r="I41" s="43">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" s="7">
+        <v>46065</v>
+      </c>
+      <c r="C42" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D42" s="22">
+        <v>136733202</v>
+      </c>
+      <c r="E42" s="17">
+        <v>3450251178</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G42" s="93" t="s">
+        <v>22</v>
+      </c>
+      <c r="H42" s="78" t="s">
+        <v>126</v>
+      </c>
+      <c r="I42" s="43">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" s="7">
+        <v>46062</v>
+      </c>
+      <c r="C43" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D43" s="22">
+        <v>136734975</v>
+      </c>
+      <c r="E43" s="17">
+        <v>3450246195</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="G43" s="93" t="s">
+        <v>14</v>
+      </c>
+      <c r="H43" s="78" t="s">
+        <v>111</v>
+      </c>
+      <c r="I43" s="43">
+        <v>46062</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" s="7">
+        <v>46062</v>
+      </c>
+      <c r="C44" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D44" s="22">
+        <v>136735098</v>
+      </c>
+      <c r="E44" s="17">
+        <v>3450246173</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="G44" s="93" t="s">
+        <v>14</v>
+      </c>
+      <c r="H44" s="78" t="s">
+        <v>111</v>
+      </c>
+      <c r="I44" s="43">
+        <v>46062</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" s="7">
+        <v>46090</v>
+      </c>
+      <c r="C45" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D45" s="22">
+        <v>136667128</v>
+      </c>
+      <c r="E45" s="17">
+        <v>3450246712</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="G45" s="93" t="s">
+        <v>11</v>
+      </c>
+      <c r="H45" s="94" t="s">
+        <v>27</v>
+      </c>
+      <c r="I45" s="43">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" s="7">
+        <v>46079</v>
+      </c>
+      <c r="C46" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D46" s="22">
+        <v>136669978</v>
+      </c>
+      <c r="E46" s="17">
+        <v>3450246877</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="G46" s="93" t="s">
+        <v>11</v>
+      </c>
+      <c r="H46" s="94" t="s">
+        <v>136</v>
+      </c>
+      <c r="I46" s="43">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47" s="7">
+        <v>46063</v>
+      </c>
+      <c r="C47" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D47" s="22">
+        <v>136689136</v>
+      </c>
+      <c r="E47" s="17">
+        <v>3450248330</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="G47" s="93" t="s">
+        <v>11</v>
+      </c>
+      <c r="H47" s="94" t="s">
+        <v>155</v>
+      </c>
+      <c r="I47" s="43">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48" s="7">
+        <v>46065</v>
+      </c>
+      <c r="C48" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D48" s="22">
+        <v>136723546</v>
+      </c>
+      <c r="E48" s="17">
+        <v>3450250287</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="G48" s="93" t="s">
+        <v>17</v>
+      </c>
+      <c r="H48" s="78" t="s">
+        <v>18</v>
+      </c>
+      <c r="I48" s="43">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" s="7">
+        <v>46065</v>
+      </c>
+      <c r="C49" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D49" s="22">
+        <v>136723669</v>
+      </c>
+      <c r="E49" s="17">
+        <v>3450250320</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="G49" s="93" t="s">
+        <v>14</v>
+      </c>
+      <c r="H49" s="78" t="s">
+        <v>111</v>
+      </c>
+      <c r="I49" s="43">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="7">
+        <v>46065</v>
+      </c>
+      <c r="C50" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D50" s="22">
+        <v>136725436</v>
+      </c>
+      <c r="E50" s="17">
+        <v>3450250562</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="G50" s="93" t="s">
+        <v>17</v>
+      </c>
+      <c r="H50" s="78" t="s">
+        <v>18</v>
+      </c>
+      <c r="I50" s="43">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B51" s="7">
+        <v>46065</v>
+      </c>
+      <c r="C51" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D51" s="22">
+        <v>136725702</v>
+      </c>
+      <c r="E51" s="17">
+        <v>3450250573</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="G51" s="93" t="s">
+        <v>14</v>
+      </c>
+      <c r="H51" s="78" t="s">
+        <v>111</v>
+      </c>
+      <c r="I51" s="43">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" s="7">
+        <v>46069</v>
+      </c>
+      <c r="C52" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D52" s="22">
+        <v>136740470</v>
+      </c>
+      <c r="E52" s="17">
+        <v>3450251607</v>
+      </c>
+      <c r="F52" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="G52" s="93" t="s">
+        <v>37</v>
+      </c>
+      <c r="H52" s="78" t="s">
+        <v>161</v>
+      </c>
+      <c r="I52" s="43">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B53" s="7">
+        <v>46073</v>
+      </c>
+      <c r="C53" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D53" s="22">
+        <v>136823048</v>
+      </c>
+      <c r="E53" s="17">
+        <v>3450257481</v>
+      </c>
+      <c r="F53" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="G53" s="93" t="s">
+        <v>37</v>
+      </c>
+      <c r="H53" s="78" t="s">
+        <v>161</v>
+      </c>
+      <c r="I53" s="43">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B54" s="7">
+        <v>46073</v>
+      </c>
+      <c r="C54" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D54" s="22">
+        <v>136816299</v>
+      </c>
+      <c r="E54" s="17">
+        <v>3450256777</v>
+      </c>
+      <c r="F54" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="G54" s="93" t="s">
+        <v>37</v>
+      </c>
+      <c r="H54" s="78" t="s">
+        <v>161</v>
+      </c>
+      <c r="I54" s="43">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B55" s="7">
+        <v>46078</v>
+      </c>
+      <c r="C55" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D55" s="22">
+        <v>136825656</v>
+      </c>
+      <c r="E55" s="17">
+        <v>3450257756</v>
+      </c>
+      <c r="F55" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="G55" s="93" t="s">
+        <v>37</v>
+      </c>
+      <c r="H55" s="78" t="s">
+        <v>161</v>
+      </c>
+      <c r="I55" s="43">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B56" s="7">
+        <v>46073</v>
+      </c>
+      <c r="C56" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D56" s="22">
+        <v>136757414</v>
+      </c>
+      <c r="E56" s="17">
+        <v>3450252993</v>
+      </c>
+      <c r="F56" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="G56" s="93" t="s">
+        <v>37</v>
+      </c>
+      <c r="H56" s="78" t="s">
+        <v>38</v>
+      </c>
+      <c r="I56" s="43">
+        <v>46073</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B57" s="7">
+        <v>46072</v>
+      </c>
+      <c r="C57" s="55">
+        <v>46077</v>
+      </c>
+      <c r="D57" s="22">
+        <v>136804031</v>
+      </c>
+      <c r="E57" s="17">
+        <v>3450255820</v>
+      </c>
+      <c r="F57" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="G57" s="93" t="s">
+        <v>22</v>
+      </c>
+      <c r="H57" s="94" t="s">
+        <v>167</v>
+      </c>
+      <c r="I57" s="43">
+        <v>46077</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="3">
+    <cfRule type="notContainsBlanks" priority="6">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:F32">
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
-  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A32" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A57" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G33" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G57" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3762,20 +5177,20 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="60"/>
+      <c r="B2" s="59"/>
       <c r="C2" s="25"/>
       <c r="D2" s="26"/>
       <c r="E2" s="17"/>
       <c r="F2" s="11"/>
       <c r="G2" s="19"/>
-      <c r="H2" s="61"/>
+      <c r="H2" s="60"/>
       <c r="I2" s="43"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="60"/>
+      <c r="B3" s="59"/>
       <c r="C3" s="25"/>
       <c r="D3" s="26"/>
       <c r="E3" s="17"/>
@@ -3803,18 +5218,18 @@
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="25"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="67"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="66"/>
       <c r="I5" s="48"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="60"/>
+      <c r="B6" s="59"/>
       <c r="C6" s="25"/>
       <c r="D6" s="22"/>
       <c r="E6" s="17"/>
@@ -3827,7 +5242,7 @@
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="60"/>
+      <c r="B7" s="59"/>
       <c r="C7" s="25"/>
       <c r="D7" s="22"/>
       <c r="E7" s="17"/>
@@ -3840,7 +5255,7 @@
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="60"/>
+      <c r="B8" s="59"/>
       <c r="C8" s="25"/>
       <c r="D8" s="22"/>
       <c r="E8" s="17"/>
@@ -3853,7 +5268,7 @@
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="60"/>
+      <c r="B9" s="59"/>
       <c r="C9" s="25"/>
       <c r="D9" s="22"/>
       <c r="E9" s="17"/>
@@ -3866,12 +5281,12 @@
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="60"/>
+      <c r="B10" s="59"/>
       <c r="C10" s="25"/>
       <c r="D10" s="22"/>
       <c r="E10" s="17"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="62"/>
+      <c r="G10" s="61"/>
       <c r="H10" s="12"/>
       <c r="I10" s="43"/>
     </row>
@@ -3879,7 +5294,7 @@
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="60"/>
+      <c r="B11" s="59"/>
       <c r="C11" s="25"/>
       <c r="D11" s="22"/>
       <c r="E11" s="17"/>
@@ -3892,12 +5307,12 @@
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="60"/>
+      <c r="B12" s="59"/>
       <c r="C12" s="25"/>
       <c r="D12" s="22"/>
       <c r="E12" s="17"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="62"/>
+      <c r="G12" s="61"/>
       <c r="H12" s="12"/>
       <c r="I12" s="43"/>
     </row>
@@ -3905,7 +5320,7 @@
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="60"/>
+      <c r="B13" s="59"/>
       <c r="C13" s="25"/>
       <c r="D13" s="22"/>
       <c r="E13" s="17"/>
@@ -3918,7 +5333,7 @@
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="60"/>
+      <c r="B14" s="59"/>
       <c r="C14" s="25"/>
       <c r="D14" s="22"/>
       <c r="E14" s="17"/>
@@ -3931,12 +5346,12 @@
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="60"/>
+      <c r="B15" s="59"/>
       <c r="C15" s="25"/>
       <c r="D15" s="22"/>
       <c r="E15" s="17"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="62"/>
+      <c r="G15" s="61"/>
       <c r="H15" s="12"/>
       <c r="I15" s="43"/>
     </row>
@@ -3944,7 +5359,7 @@
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="60"/>
+      <c r="B16" s="59"/>
       <c r="C16" s="25"/>
       <c r="D16" s="22"/>
       <c r="E16" s="17"/>
@@ -3957,7 +5372,7 @@
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="60"/>
+      <c r="B17" s="59"/>
       <c r="C17" s="25"/>
       <c r="D17" s="22"/>
       <c r="E17" s="17"/>
@@ -4014,7 +5429,7 @@
       <c r="D21" s="22"/>
       <c r="E21" s="17"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="62"/>
+      <c r="G21" s="61"/>
       <c r="H21" s="12"/>
       <c r="I21" s="43"/>
     </row>
@@ -4035,10 +5450,10 @@
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
       <c r="C23" s="25"/>
-      <c r="D23" s="68"/>
+      <c r="D23" s="67"/>
       <c r="E23" s="56"/>
       <c r="F23" s="31"/>
-      <c r="G23" s="69"/>
+      <c r="G23" s="68"/>
       <c r="H23" s="14"/>
     </row>
     <row r="24" spans="1:9">
@@ -6185,7 +7600,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="51" t="s">
@@ -6206,7 +7621,7 @@
       <c r="G1" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="76" t="s">
+      <c r="H1" s="74" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="50" t="s">
@@ -6214,894 +7629,894 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="71" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="43"/>
       <c r="C2" s="43"/>
-      <c r="D2" s="81"/>
+      <c r="D2" s="22"/>
       <c r="E2" s="17"/>
-      <c r="F2" s="71"/>
+      <c r="F2" s="11"/>
       <c r="G2" s="42"/>
-      <c r="H2" s="77"/>
+      <c r="H2" s="75"/>
       <c r="I2" s="58"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="73"/>
+      <c r="A3" s="71"/>
       <c r="B3" s="43"/>
       <c r="C3" s="43"/>
-      <c r="D3" s="81"/>
+      <c r="D3" s="22"/>
       <c r="E3" s="17"/>
-      <c r="F3" s="71"/>
+      <c r="F3" s="11"/>
       <c r="G3" s="42"/>
-      <c r="H3" s="77"/>
+      <c r="H3" s="75"/>
       <c r="I3" s="58"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="73"/>
+      <c r="A4" s="71"/>
       <c r="B4" s="43"/>
       <c r="C4" s="43"/>
-      <c r="D4" s="81"/>
+      <c r="D4" s="22"/>
       <c r="E4" s="17"/>
-      <c r="F4" s="71"/>
+      <c r="F4" s="11"/>
       <c r="G4" s="42"/>
-      <c r="H4" s="77"/>
+      <c r="H4" s="75"/>
       <c r="I4" s="58"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="73"/>
+      <c r="A5" s="71"/>
       <c r="B5" s="43"/>
       <c r="C5" s="43"/>
-      <c r="D5" s="81"/>
+      <c r="D5" s="22"/>
       <c r="E5" s="17"/>
-      <c r="F5" s="71"/>
+      <c r="F5" s="11"/>
       <c r="G5" s="42"/>
-      <c r="H5" s="77"/>
+      <c r="H5" s="75"/>
       <c r="I5" s="58"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="73"/>
+      <c r="A6" s="71"/>
       <c r="B6" s="43"/>
       <c r="C6" s="43"/>
-      <c r="D6" s="81"/>
+      <c r="D6" s="22"/>
       <c r="E6" s="17"/>
-      <c r="F6" s="71"/>
+      <c r="F6" s="11"/>
       <c r="G6" s="42"/>
-      <c r="H6" s="77"/>
+      <c r="H6" s="75"/>
       <c r="I6" s="58"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="73"/>
+      <c r="A7" s="71"/>
       <c r="B7" s="43"/>
       <c r="C7" s="43"/>
-      <c r="D7" s="81"/>
+      <c r="D7" s="22"/>
       <c r="E7" s="17"/>
-      <c r="F7" s="71"/>
+      <c r="F7" s="11"/>
       <c r="G7" s="42"/>
-      <c r="H7" s="77"/>
+      <c r="H7" s="75"/>
       <c r="I7" s="58"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="73"/>
+      <c r="A8" s="71"/>
       <c r="B8" s="43"/>
       <c r="C8" s="43"/>
-      <c r="D8" s="81"/>
+      <c r="D8" s="22"/>
       <c r="E8" s="17"/>
-      <c r="F8" s="71"/>
+      <c r="F8" s="11"/>
       <c r="G8" s="42"/>
-      <c r="H8" s="77"/>
+      <c r="H8" s="75"/>
       <c r="I8" s="58"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="73"/>
+      <c r="A9" s="71"/>
       <c r="B9" s="43"/>
       <c r="C9" s="43"/>
-      <c r="D9" s="81"/>
+      <c r="D9" s="22"/>
       <c r="E9" s="17"/>
-      <c r="F9" s="71"/>
+      <c r="F9" s="11"/>
       <c r="G9" s="42"/>
-      <c r="H9" s="77"/>
+      <c r="H9" s="75"/>
       <c r="I9" s="58"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="73"/>
+      <c r="A10" s="71"/>
       <c r="B10" s="43"/>
       <c r="C10" s="43"/>
-      <c r="D10" s="81"/>
+      <c r="D10" s="22"/>
       <c r="E10" s="17"/>
-      <c r="F10" s="71"/>
+      <c r="F10" s="11"/>
       <c r="G10" s="42"/>
-      <c r="H10" s="77"/>
+      <c r="H10" s="75"/>
       <c r="I10" s="58"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="73"/>
+      <c r="A11" s="71"/>
       <c r="B11" s="43"/>
       <c r="C11" s="43"/>
-      <c r="D11" s="81"/>
+      <c r="D11" s="22"/>
       <c r="E11" s="17"/>
-      <c r="F11" s="71"/>
+      <c r="F11" s="11"/>
       <c r="G11" s="42"/>
-      <c r="H11" s="77"/>
+      <c r="H11" s="75"/>
       <c r="I11" s="58"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="73"/>
+      <c r="A12" s="71"/>
       <c r="B12" s="43"/>
       <c r="C12" s="43"/>
-      <c r="D12" s="81"/>
+      <c r="D12" s="22"/>
       <c r="E12" s="17"/>
-      <c r="F12" s="71"/>
+      <c r="F12" s="11"/>
       <c r="G12" s="42"/>
-      <c r="H12" s="77"/>
+      <c r="H12" s="75"/>
       <c r="I12" s="58"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="73"/>
+      <c r="A13" s="71"/>
       <c r="B13" s="43"/>
       <c r="C13" s="43"/>
-      <c r="D13" s="81"/>
+      <c r="D13" s="22"/>
       <c r="E13" s="17"/>
-      <c r="F13" s="71"/>
+      <c r="F13" s="11"/>
       <c r="G13" s="42"/>
-      <c r="H13" s="77"/>
+      <c r="H13" s="75"/>
       <c r="I13" s="58"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="73"/>
+      <c r="A14" s="71"/>
       <c r="B14" s="43"/>
       <c r="C14" s="43"/>
-      <c r="D14" s="81"/>
+      <c r="D14" s="22"/>
       <c r="E14" s="17"/>
-      <c r="F14" s="71"/>
+      <c r="F14" s="11"/>
       <c r="G14" s="42"/>
-      <c r="H14" s="77"/>
+      <c r="H14" s="75"/>
       <c r="I14" s="58"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="73"/>
+      <c r="A15" s="71"/>
       <c r="B15" s="43"/>
       <c r="C15" s="43"/>
-      <c r="D15" s="81"/>
+      <c r="D15" s="22"/>
       <c r="E15" s="17"/>
-      <c r="F15" s="71"/>
+      <c r="F15" s="11"/>
       <c r="G15" s="42"/>
-      <c r="H15" s="77"/>
+      <c r="H15" s="75"/>
       <c r="I15" s="58"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="73"/>
+      <c r="A16" s="71"/>
       <c r="B16" s="43"/>
       <c r="C16" s="43"/>
-      <c r="D16" s="81"/>
+      <c r="D16" s="22"/>
       <c r="E16" s="17"/>
-      <c r="F16" s="71"/>
+      <c r="F16" s="11"/>
       <c r="G16" s="42"/>
-      <c r="H16" s="77"/>
+      <c r="H16" s="75"/>
       <c r="I16" s="58"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="73"/>
+      <c r="A17" s="71"/>
       <c r="B17" s="43"/>
       <c r="C17" s="43"/>
-      <c r="D17" s="81"/>
+      <c r="D17" s="22"/>
       <c r="E17" s="17"/>
-      <c r="F17" s="71"/>
+      <c r="F17" s="11"/>
       <c r="G17" s="42"/>
-      <c r="H17" s="77"/>
+      <c r="H17" s="75"/>
       <c r="I17" s="58"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="73"/>
+      <c r="A18" s="71"/>
       <c r="B18" s="43"/>
       <c r="C18" s="43"/>
-      <c r="D18" s="81"/>
+      <c r="D18" s="22"/>
       <c r="E18" s="17"/>
-      <c r="F18" s="71"/>
+      <c r="F18" s="11"/>
       <c r="G18" s="42"/>
-      <c r="H18" s="77"/>
+      <c r="H18" s="75"/>
       <c r="I18" s="58"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="73"/>
+      <c r="A19" s="71"/>
       <c r="B19" s="43"/>
       <c r="C19" s="43"/>
-      <c r="D19" s="81"/>
+      <c r="D19" s="22"/>
       <c r="E19" s="17"/>
-      <c r="F19" s="71"/>
+      <c r="F19" s="11"/>
       <c r="G19" s="42"/>
-      <c r="H19" s="77"/>
+      <c r="H19" s="75"/>
       <c r="I19" s="58"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="73"/>
+      <c r="A20" s="71"/>
       <c r="B20" s="43"/>
       <c r="C20" s="43"/>
-      <c r="D20" s="81"/>
+      <c r="D20" s="22"/>
       <c r="E20" s="17"/>
-      <c r="F20" s="71"/>
+      <c r="F20" s="11"/>
       <c r="G20" s="42"/>
-      <c r="H20" s="77"/>
+      <c r="H20" s="75"/>
       <c r="I20" s="58"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="73"/>
+      <c r="A21" s="71"/>
       <c r="B21" s="43"/>
       <c r="C21" s="43"/>
-      <c r="D21" s="81"/>
+      <c r="D21" s="22"/>
       <c r="E21" s="17"/>
-      <c r="F21" s="71"/>
+      <c r="F21" s="11"/>
       <c r="G21" s="42"/>
-      <c r="H21" s="77"/>
+      <c r="H21" s="75"/>
       <c r="I21" s="58"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="73"/>
+      <c r="A22" s="71"/>
       <c r="B22" s="43"/>
       <c r="C22" s="43"/>
-      <c r="D22" s="81"/>
+      <c r="D22" s="22"/>
       <c r="E22" s="17"/>
-      <c r="F22" s="71"/>
+      <c r="F22" s="11"/>
       <c r="G22" s="42"/>
-      <c r="H22" s="77"/>
+      <c r="H22" s="75"/>
       <c r="I22" s="58"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="73"/>
+      <c r="A23" s="71"/>
       <c r="B23" s="43"/>
       <c r="C23" s="43"/>
-      <c r="D23" s="81"/>
+      <c r="D23" s="22"/>
       <c r="E23" s="17"/>
-      <c r="F23" s="71"/>
+      <c r="F23" s="11"/>
       <c r="G23" s="42"/>
-      <c r="H23" s="77"/>
+      <c r="H23" s="75"/>
       <c r="I23" s="58"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="73"/>
+      <c r="A24" s="71"/>
       <c r="B24" s="43"/>
       <c r="C24" s="43"/>
-      <c r="D24" s="81"/>
+      <c r="D24" s="22"/>
       <c r="E24" s="17"/>
-      <c r="F24" s="71"/>
+      <c r="F24" s="11"/>
       <c r="G24" s="42"/>
-      <c r="H24" s="77"/>
+      <c r="H24" s="75"/>
       <c r="I24" s="58"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="73"/>
+      <c r="A25" s="71"/>
       <c r="B25" s="43"/>
       <c r="C25" s="43"/>
-      <c r="D25" s="81"/>
+      <c r="D25" s="22"/>
       <c r="E25" s="17"/>
-      <c r="F25" s="71"/>
+      <c r="F25" s="11"/>
       <c r="G25" s="42"/>
-      <c r="H25" s="77"/>
+      <c r="H25" s="75"/>
       <c r="I25" s="58"/>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="73"/>
+      <c r="A26" s="71"/>
       <c r="B26" s="43"/>
       <c r="C26" s="43"/>
-      <c r="D26" s="81"/>
+      <c r="D26" s="22"/>
       <c r="E26" s="17"/>
-      <c r="F26" s="71"/>
+      <c r="F26" s="11"/>
       <c r="G26" s="42"/>
-      <c r="H26" s="77"/>
+      <c r="H26" s="75"/>
       <c r="I26" s="58"/>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="73"/>
+      <c r="A27" s="71"/>
       <c r="B27" s="43"/>
       <c r="C27" s="43"/>
-      <c r="D27" s="81"/>
+      <c r="D27" s="22"/>
       <c r="E27" s="17"/>
-      <c r="F27" s="71"/>
+      <c r="F27" s="11"/>
       <c r="G27" s="42"/>
-      <c r="H27" s="77"/>
+      <c r="H27" s="75"/>
       <c r="I27" s="58"/>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="73"/>
+      <c r="A28" s="71"/>
       <c r="B28" s="43"/>
       <c r="C28" s="43"/>
-      <c r="D28" s="81"/>
+      <c r="D28" s="22"/>
       <c r="E28" s="17"/>
-      <c r="F28" s="71"/>
+      <c r="F28" s="11"/>
       <c r="G28" s="42"/>
-      <c r="H28" s="77"/>
+      <c r="H28" s="75"/>
       <c r="I28" s="58"/>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="73"/>
+      <c r="A29" s="71"/>
       <c r="B29" s="43"/>
       <c r="C29" s="43"/>
-      <c r="D29" s="81"/>
+      <c r="D29" s="22"/>
       <c r="E29" s="17"/>
-      <c r="F29" s="71"/>
+      <c r="F29" s="11"/>
       <c r="G29" s="42"/>
-      <c r="H29" s="77"/>
+      <c r="H29" s="75"/>
       <c r="I29" s="58"/>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="73"/>
+      <c r="A30" s="71"/>
       <c r="B30" s="43"/>
       <c r="C30" s="43"/>
-      <c r="D30" s="81"/>
+      <c r="D30" s="22"/>
       <c r="E30" s="17"/>
-      <c r="F30" s="71"/>
+      <c r="F30" s="11"/>
       <c r="G30" s="42"/>
-      <c r="H30" s="77"/>
+      <c r="H30" s="75"/>
       <c r="I30" s="58"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="73"/>
+      <c r="A31" s="71"/>
       <c r="B31" s="43"/>
       <c r="C31" s="43"/>
-      <c r="D31" s="81"/>
+      <c r="D31" s="22"/>
       <c r="E31" s="17"/>
-      <c r="F31" s="71"/>
+      <c r="F31" s="11"/>
       <c r="G31" s="42"/>
-      <c r="H31" s="77"/>
+      <c r="H31" s="75"/>
       <c r="I31" s="58"/>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="73"/>
+      <c r="A32" s="71"/>
       <c r="B32" s="43"/>
       <c r="C32" s="43"/>
-      <c r="D32" s="81"/>
+      <c r="D32" s="22"/>
       <c r="E32" s="17"/>
-      <c r="F32" s="71"/>
+      <c r="F32" s="11"/>
       <c r="G32" s="42"/>
-      <c r="H32" s="77"/>
+      <c r="H32" s="75"/>
       <c r="I32" s="58"/>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="73"/>
+      <c r="A33" s="71"/>
       <c r="B33" s="43"/>
       <c r="C33" s="43"/>
-      <c r="D33" s="81"/>
+      <c r="D33" s="22"/>
       <c r="E33" s="17"/>
-      <c r="F33" s="71"/>
+      <c r="F33" s="11"/>
       <c r="G33" s="42"/>
-      <c r="H33" s="77"/>
+      <c r="H33" s="75"/>
       <c r="I33" s="58"/>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="73"/>
+      <c r="A34" s="71"/>
       <c r="B34" s="43"/>
       <c r="C34" s="43"/>
-      <c r="D34" s="81"/>
+      <c r="D34" s="22"/>
       <c r="E34" s="17"/>
-      <c r="F34" s="71"/>
+      <c r="F34" s="11"/>
       <c r="G34" s="42"/>
-      <c r="H34" s="77"/>
+      <c r="H34" s="75"/>
       <c r="I34" s="58"/>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="73"/>
+      <c r="A35" s="71"/>
       <c r="B35" s="43"/>
       <c r="C35" s="43"/>
-      <c r="D35" s="81"/>
+      <c r="D35" s="22"/>
       <c r="E35" s="17"/>
-      <c r="F35" s="71"/>
+      <c r="F35" s="11"/>
       <c r="G35" s="42"/>
-      <c r="H35" s="77"/>
+      <c r="H35" s="75"/>
       <c r="I35" s="58"/>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="73"/>
+      <c r="A36" s="71"/>
       <c r="B36" s="43"/>
       <c r="C36" s="43"/>
-      <c r="D36" s="81"/>
+      <c r="D36" s="22"/>
       <c r="E36" s="17"/>
-      <c r="F36" s="71"/>
+      <c r="F36" s="11"/>
       <c r="G36" s="42"/>
-      <c r="H36" s="77"/>
+      <c r="H36" s="75"/>
       <c r="I36" s="58"/>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" s="73"/>
+      <c r="A37" s="71"/>
       <c r="B37" s="43"/>
       <c r="C37" s="43"/>
-      <c r="D37" s="81"/>
+      <c r="D37" s="22"/>
       <c r="E37" s="17"/>
-      <c r="F37" s="71"/>
+      <c r="F37" s="11"/>
       <c r="G37" s="42"/>
-      <c r="H37" s="77"/>
+      <c r="H37" s="75"/>
       <c r="I37" s="58"/>
     </row>
     <row r="38" spans="1:9">
-      <c r="A38" s="73"/>
+      <c r="A38" s="71"/>
       <c r="B38" s="43"/>
       <c r="C38" s="43"/>
-      <c r="D38" s="81"/>
+      <c r="D38" s="22"/>
       <c r="E38" s="17"/>
-      <c r="F38" s="71"/>
+      <c r="F38" s="11"/>
       <c r="G38" s="42"/>
-      <c r="H38" s="77"/>
+      <c r="H38" s="75"/>
       <c r="I38" s="58"/>
     </row>
     <row r="39" spans="1:9">
-      <c r="A39" s="73"/>
+      <c r="A39" s="71"/>
       <c r="B39" s="43"/>
       <c r="C39" s="43"/>
-      <c r="D39" s="81"/>
+      <c r="D39" s="22"/>
       <c r="E39" s="17"/>
-      <c r="F39" s="71"/>
+      <c r="F39" s="11"/>
       <c r="G39" s="42"/>
-      <c r="H39" s="77"/>
+      <c r="H39" s="75"/>
       <c r="I39" s="58"/>
     </row>
     <row r="40" spans="1:9">
-      <c r="A40" s="73"/>
+      <c r="A40" s="71"/>
       <c r="B40" s="43"/>
       <c r="C40" s="43"/>
-      <c r="D40" s="81"/>
+      <c r="D40" s="22"/>
       <c r="E40" s="17"/>
-      <c r="F40" s="71"/>
+      <c r="F40" s="11"/>
       <c r="G40" s="42"/>
-      <c r="H40" s="77"/>
+      <c r="H40" s="75"/>
       <c r="I40" s="58"/>
     </row>
     <row r="41" spans="1:9">
-      <c r="A41" s="73"/>
+      <c r="A41" s="71"/>
       <c r="B41" s="43"/>
       <c r="C41" s="43"/>
-      <c r="D41" s="81"/>
+      <c r="D41" s="22"/>
       <c r="E41" s="17"/>
-      <c r="F41" s="71"/>
+      <c r="F41" s="11"/>
       <c r="G41" s="42"/>
-      <c r="H41" s="77"/>
+      <c r="H41" s="75"/>
       <c r="I41" s="58"/>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="73"/>
+      <c r="A42" s="71"/>
       <c r="B42" s="43"/>
       <c r="C42" s="43"/>
-      <c r="D42" s="81"/>
+      <c r="D42" s="22"/>
       <c r="E42" s="17"/>
-      <c r="F42" s="71"/>
+      <c r="F42" s="11"/>
       <c r="G42" s="42"/>
-      <c r="H42" s="77"/>
+      <c r="H42" s="75"/>
       <c r="I42" s="58"/>
     </row>
     <row r="43" spans="1:9">
-      <c r="A43" s="73"/>
+      <c r="A43" s="71"/>
       <c r="B43" s="43"/>
       <c r="C43" s="43"/>
-      <c r="D43" s="81"/>
+      <c r="D43" s="22"/>
       <c r="E43" s="17"/>
-      <c r="F43" s="71"/>
+      <c r="F43" s="11"/>
       <c r="G43" s="42"/>
-      <c r="H43" s="77"/>
+      <c r="H43" s="75"/>
       <c r="I43" s="58"/>
     </row>
     <row r="44" spans="1:9">
-      <c r="A44" s="73"/>
+      <c r="A44" s="71"/>
       <c r="B44" s="43"/>
       <c r="C44" s="43"/>
-      <c r="D44" s="81"/>
+      <c r="D44" s="22"/>
       <c r="E44" s="17"/>
-      <c r="F44" s="71"/>
+      <c r="F44" s="11"/>
       <c r="G44" s="42"/>
-      <c r="H44" s="77"/>
+      <c r="H44" s="75"/>
       <c r="I44" s="58"/>
     </row>
     <row r="45" spans="1:9">
-      <c r="A45" s="73"/>
+      <c r="A45" s="71"/>
       <c r="B45" s="43"/>
       <c r="C45" s="43"/>
-      <c r="D45" s="81"/>
+      <c r="D45" s="22"/>
       <c r="E45" s="17"/>
-      <c r="F45" s="71"/>
+      <c r="F45" s="11"/>
       <c r="G45" s="42"/>
-      <c r="H45" s="77"/>
+      <c r="H45" s="75"/>
       <c r="I45" s="58"/>
     </row>
     <row r="46" spans="1:9">
-      <c r="A46" s="73"/>
+      <c r="A46" s="71"/>
       <c r="B46" s="43"/>
       <c r="C46" s="43"/>
-      <c r="D46" s="81"/>
+      <c r="D46" s="22"/>
       <c r="E46" s="17"/>
-      <c r="F46" s="71"/>
+      <c r="F46" s="11"/>
       <c r="G46" s="42"/>
-      <c r="H46" s="77"/>
+      <c r="H46" s="75"/>
       <c r="I46" s="58"/>
     </row>
     <row r="47" spans="1:9">
-      <c r="A47" s="73"/>
+      <c r="A47" s="71"/>
       <c r="B47" s="43"/>
       <c r="C47" s="43"/>
-      <c r="D47" s="81"/>
+      <c r="D47" s="22"/>
       <c r="E47" s="17"/>
-      <c r="F47" s="71"/>
+      <c r="F47" s="11"/>
       <c r="G47" s="42"/>
-      <c r="H47" s="77"/>
+      <c r="H47" s="75"/>
       <c r="I47" s="58"/>
     </row>
     <row r="48" spans="1:9">
-      <c r="A48" s="73"/>
+      <c r="A48" s="71"/>
       <c r="B48" s="43"/>
       <c r="C48" s="43"/>
-      <c r="D48" s="81"/>
+      <c r="D48" s="22"/>
       <c r="E48" s="17"/>
-      <c r="F48" s="71"/>
+      <c r="F48" s="11"/>
       <c r="G48" s="42"/>
-      <c r="H48" s="77"/>
+      <c r="H48" s="75"/>
       <c r="I48" s="58"/>
     </row>
     <row r="49" spans="1:9">
-      <c r="A49" s="73"/>
+      <c r="A49" s="71"/>
       <c r="B49" s="43"/>
       <c r="C49" s="43"/>
-      <c r="D49" s="81"/>
+      <c r="D49" s="22"/>
       <c r="E49" s="17"/>
-      <c r="F49" s="71"/>
+      <c r="F49" s="11"/>
       <c r="G49" s="42"/>
-      <c r="H49" s="77"/>
+      <c r="H49" s="75"/>
       <c r="I49" s="58"/>
     </row>
     <row r="50" spans="1:9">
-      <c r="A50" s="74" t="s">
+      <c r="A50" s="72" t="s">
         <v>9</v>
       </c>
       <c r="B50" s="43"/>
       <c r="C50" s="43"/>
-      <c r="D50" s="81"/>
+      <c r="D50" s="22"/>
       <c r="E50" s="17"/>
-      <c r="F50" s="71"/>
+      <c r="F50" s="11"/>
       <c r="G50" s="42"/>
-      <c r="H50" s="78"/>
+      <c r="H50" s="76"/>
       <c r="I50" s="43"/>
     </row>
     <row r="51" spans="1:9">
-      <c r="A51" s="74" t="s">
+      <c r="A51" s="72" t="s">
         <v>9</v>
       </c>
       <c r="B51" s="43"/>
       <c r="C51" s="43"/>
-      <c r="D51" s="81"/>
+      <c r="D51" s="22"/>
       <c r="E51" s="17"/>
-      <c r="F51" s="71"/>
+      <c r="F51" s="11"/>
       <c r="G51" s="42"/>
-      <c r="H51" s="78"/>
+      <c r="H51" s="76"/>
       <c r="I51" s="43"/>
     </row>
     <row r="52" spans="1:9">
-      <c r="A52" s="74" t="s">
+      <c r="A52" s="72" t="s">
         <v>9</v>
       </c>
       <c r="B52" s="43"/>
       <c r="C52" s="43"/>
-      <c r="D52" s="81"/>
+      <c r="D52" s="22"/>
       <c r="E52" s="17"/>
-      <c r="F52" s="71"/>
+      <c r="F52" s="11"/>
       <c r="G52" s="42"/>
-      <c r="H52" s="78"/>
+      <c r="H52" s="76"/>
       <c r="I52" s="43"/>
     </row>
     <row r="53" spans="1:9">
-      <c r="A53" s="74" t="s">
+      <c r="A53" s="72" t="s">
         <v>9</v>
       </c>
       <c r="B53" s="43"/>
       <c r="C53" s="43"/>
-      <c r="D53" s="81"/>
+      <c r="D53" s="22"/>
       <c r="E53" s="17"/>
-      <c r="F53" s="71"/>
+      <c r="F53" s="11"/>
       <c r="G53" s="42"/>
-      <c r="H53" s="79"/>
+      <c r="H53" s="77"/>
       <c r="I53" s="43"/>
     </row>
     <row r="54" spans="1:9">
-      <c r="A54" s="74" t="s">
+      <c r="A54" s="72" t="s">
         <v>9</v>
       </c>
       <c r="B54" s="43"/>
       <c r="C54" s="43"/>
-      <c r="D54" s="81"/>
+      <c r="D54" s="22"/>
       <c r="E54" s="17"/>
-      <c r="F54" s="71"/>
+      <c r="F54" s="11"/>
       <c r="G54" s="42"/>
-      <c r="H54" s="78"/>
+      <c r="H54" s="76"/>
       <c r="I54" s="43"/>
     </row>
     <row r="55" spans="1:9">
-      <c r="A55" s="74" t="s">
+      <c r="A55" s="72" t="s">
         <v>9</v>
       </c>
       <c r="B55" s="43"/>
       <c r="C55" s="43"/>
-      <c r="D55" s="81"/>
+      <c r="D55" s="22"/>
       <c r="E55" s="17"/>
-      <c r="F55" s="71"/>
+      <c r="F55" s="11"/>
       <c r="G55" s="42"/>
-      <c r="H55" s="78"/>
+      <c r="H55" s="76"/>
       <c r="I55" s="43"/>
     </row>
     <row r="56" spans="1:9">
-      <c r="A56" s="74" t="s">
+      <c r="A56" s="72" t="s">
         <v>9</v>
       </c>
       <c r="B56" s="43"/>
       <c r="C56" s="43"/>
-      <c r="D56" s="81"/>
+      <c r="D56" s="22"/>
       <c r="E56" s="17"/>
-      <c r="F56" s="71"/>
+      <c r="F56" s="11"/>
       <c r="G56" s="42"/>
-      <c r="H56" s="78"/>
+      <c r="H56" s="76"/>
       <c r="I56" s="43"/>
     </row>
     <row r="57" spans="1:9">
-      <c r="A57" s="74" t="s">
+      <c r="A57" s="72" t="s">
         <v>9</v>
       </c>
       <c r="B57" s="43"/>
       <c r="C57" s="43"/>
-      <c r="D57" s="81"/>
+      <c r="D57" s="22"/>
       <c r="E57" s="17"/>
-      <c r="F57" s="71"/>
+      <c r="F57" s="11"/>
       <c r="G57" s="42"/>
-      <c r="H57" s="78"/>
+      <c r="H57" s="76"/>
       <c r="I57" s="43"/>
     </row>
     <row r="58" spans="1:9">
-      <c r="A58" s="74" t="s">
+      <c r="A58" s="72" t="s">
         <v>9</v>
       </c>
       <c r="B58" s="43"/>
       <c r="C58" s="43"/>
-      <c r="D58" s="81"/>
+      <c r="D58" s="22"/>
       <c r="E58" s="17"/>
-      <c r="F58" s="71"/>
+      <c r="F58" s="11"/>
       <c r="G58" s="42"/>
-      <c r="H58" s="78"/>
+      <c r="H58" s="76"/>
       <c r="I58" s="43"/>
     </row>
     <row r="59" spans="1:9">
-      <c r="A59" s="74" t="s">
+      <c r="A59" s="72" t="s">
         <v>9</v>
       </c>
       <c r="B59" s="43"/>
       <c r="C59" s="43"/>
-      <c r="D59" s="81"/>
+      <c r="D59" s="22"/>
       <c r="E59" s="17"/>
-      <c r="F59" s="71"/>
+      <c r="F59" s="11"/>
       <c r="G59" s="42"/>
-      <c r="H59" s="78"/>
+      <c r="H59" s="76"/>
       <c r="I59" s="43"/>
     </row>
     <row r="60" spans="1:9">
-      <c r="A60" s="74" t="s">
+      <c r="A60" s="72" t="s">
         <v>9</v>
       </c>
       <c r="B60" s="43"/>
       <c r="C60" s="43"/>
-      <c r="D60" s="81"/>
+      <c r="D60" s="22"/>
       <c r="E60" s="17"/>
-      <c r="F60" s="71"/>
+      <c r="F60" s="11"/>
       <c r="G60" s="42"/>
-      <c r="H60" s="78"/>
+      <c r="H60" s="76"/>
       <c r="I60" s="43"/>
     </row>
     <row r="61" spans="1:9">
-      <c r="A61" s="75" t="s">
+      <c r="A61" s="73" t="s">
         <v>9</v>
       </c>
       <c r="B61" s="43"/>
       <c r="C61" s="43"/>
-      <c r="D61" s="81"/>
+      <c r="D61" s="22"/>
       <c r="E61" s="17"/>
-      <c r="F61" s="71"/>
+      <c r="F61" s="11"/>
       <c r="G61" s="42"/>
-      <c r="H61" s="78"/>
+      <c r="H61" s="76"/>
       <c r="I61" s="43"/>
     </row>
     <row r="62" spans="1:9">
-      <c r="A62" s="74" t="s">
+      <c r="A62" s="72" t="s">
         <v>9</v>
       </c>
       <c r="B62" s="43"/>
       <c r="C62" s="43"/>
-      <c r="D62" s="81"/>
+      <c r="D62" s="22"/>
       <c r="E62" s="17"/>
-      <c r="F62" s="71"/>
+      <c r="F62" s="11"/>
       <c r="G62" s="42"/>
-      <c r="H62" s="78"/>
+      <c r="H62" s="76"/>
       <c r="I62" s="43"/>
     </row>
     <row r="63" spans="1:9">
-      <c r="A63" s="74"/>
+      <c r="A63" s="72"/>
       <c r="B63" s="43"/>
       <c r="C63" s="43"/>
-      <c r="D63" s="81"/>
+      <c r="D63" s="22"/>
       <c r="E63" s="12"/>
-      <c r="F63" s="71"/>
+      <c r="F63" s="11"/>
       <c r="G63" s="42"/>
-      <c r="H63" s="80"/>
+      <c r="H63" s="78"/>
       <c r="I63" s="43"/>
     </row>
     <row r="64" spans="1:9">
-      <c r="A64" s="74"/>
+      <c r="A64" s="72"/>
       <c r="B64" s="43"/>
       <c r="C64" s="43"/>
-      <c r="D64" s="81"/>
+      <c r="D64" s="22"/>
       <c r="E64" s="12"/>
-      <c r="F64" s="71"/>
+      <c r="F64" s="11"/>
       <c r="G64" s="42"/>
-      <c r="H64" s="80"/>
+      <c r="H64" s="78"/>
       <c r="I64" s="43"/>
     </row>
     <row r="65" spans="1:9">
-      <c r="A65" s="74"/>
+      <c r="A65" s="72"/>
       <c r="B65" s="43"/>
       <c r="C65" s="43"/>
-      <c r="D65" s="81"/>
+      <c r="D65" s="22"/>
       <c r="E65" s="12"/>
-      <c r="F65" s="71"/>
+      <c r="F65" s="11"/>
       <c r="G65" s="42"/>
-      <c r="H65" s="80"/>
+      <c r="H65" s="78"/>
       <c r="I65" s="43"/>
     </row>
     <row r="66" spans="1:9">
-      <c r="A66" s="74"/>
+      <c r="A66" s="72"/>
       <c r="B66" s="43"/>
       <c r="C66" s="43"/>
-      <c r="D66" s="81"/>
+      <c r="D66" s="22"/>
       <c r="E66" s="12"/>
-      <c r="F66" s="71"/>
+      <c r="F66" s="11"/>
       <c r="G66" s="42"/>
-      <c r="H66" s="80"/>
+      <c r="H66" s="78"/>
       <c r="I66" s="43"/>
     </row>
     <row r="67" spans="1:9">
-      <c r="A67" s="74"/>
+      <c r="A67" s="72"/>
       <c r="B67" s="43"/>
       <c r="C67" s="43"/>
-      <c r="D67" s="81"/>
+      <c r="D67" s="22"/>
       <c r="E67" s="12"/>
-      <c r="F67" s="71"/>
+      <c r="F67" s="11"/>
       <c r="G67" s="42"/>
-      <c r="H67" s="80"/>
+      <c r="H67" s="78"/>
       <c r="I67" s="43"/>
     </row>
     <row r="68" spans="1:9">
-      <c r="A68" s="74"/>
+      <c r="A68" s="72"/>
       <c r="B68" s="43"/>
       <c r="C68" s="43"/>
-      <c r="D68" s="81"/>
+      <c r="D68" s="22"/>
       <c r="E68" s="12"/>
-      <c r="F68" s="71"/>
+      <c r="F68" s="11"/>
       <c r="G68" s="42"/>
-      <c r="H68" s="80"/>
+      <c r="H68" s="78"/>
       <c r="I68" s="43"/>
     </row>
     <row r="69" spans="1:9">
-      <c r="A69" s="74"/>
+      <c r="A69" s="72"/>
       <c r="B69" s="43"/>
       <c r="C69" s="43"/>
-      <c r="D69" s="81"/>
+      <c r="D69" s="22"/>
       <c r="E69" s="12"/>
-      <c r="F69" s="71"/>
+      <c r="F69" s="11"/>
       <c r="G69" s="42"/>
-      <c r="H69" s="80"/>
+      <c r="H69" s="78"/>
       <c r="I69" s="43"/>
     </row>
     <row r="70" spans="1:9">
-      <c r="A70" s="74"/>
+      <c r="A70" s="72"/>
       <c r="B70" s="43"/>
       <c r="C70" s="43"/>
-      <c r="D70" s="81"/>
+      <c r="D70" s="22"/>
       <c r="E70" s="12"/>
-      <c r="F70" s="71"/>
+      <c r="F70" s="11"/>
       <c r="G70" s="42"/>
-      <c r="H70" s="80"/>
+      <c r="H70" s="78"/>
       <c r="I70" s="43"/>
     </row>
     <row r="71" spans="1:9">
-      <c r="A71" s="74"/>
+      <c r="A71" s="72"/>
       <c r="B71" s="43"/>
       <c r="C71" s="43"/>
-      <c r="D71" s="81"/>
+      <c r="D71" s="22"/>
       <c r="E71" s="12"/>
-      <c r="F71" s="71"/>
+      <c r="F71" s="11"/>
       <c r="G71" s="42"/>
-      <c r="H71" s="80"/>
+      <c r="H71" s="78"/>
       <c r="I71" s="43"/>
     </row>
     <row r="72" spans="1:9">
-      <c r="A72" s="74"/>
+      <c r="A72" s="72"/>
       <c r="B72" s="43"/>
       <c r="C72" s="43"/>
-      <c r="D72" s="81"/>
+      <c r="D72" s="22"/>
       <c r="E72" s="12"/>
-      <c r="F72" s="71"/>
+      <c r="F72" s="11"/>
       <c r="G72" s="42"/>
-      <c r="H72" s="80"/>
+      <c r="H72" s="78"/>
       <c r="I72" s="43"/>
     </row>
     <row r="73" spans="1:9">
-      <c r="A73" s="74"/>
+      <c r="A73" s="72"/>
       <c r="B73" s="43"/>
       <c r="C73" s="43"/>
-      <c r="D73" s="81"/>
+      <c r="D73" s="22"/>
       <c r="E73" s="12"/>
-      <c r="F73" s="71"/>
+      <c r="F73" s="11"/>
       <c r="G73" s="42"/>
-      <c r="H73" s="80"/>
+      <c r="H73" s="78"/>
       <c r="I73" s="43"/>
     </row>
     <row r="74" spans="1:9">
-      <c r="A74" s="74"/>
+      <c r="A74" s="72"/>
       <c r="B74" s="43"/>
       <c r="C74" s="43"/>
-      <c r="D74" s="81"/>
+      <c r="D74" s="22"/>
       <c r="E74" s="12"/>
-      <c r="F74" s="71"/>
+      <c r="F74" s="11"/>
       <c r="G74" s="42"/>
-      <c r="H74" s="80"/>
+      <c r="H74" s="78"/>
       <c r="I74" s="43"/>
     </row>
     <row r="75" spans="1:9">
-      <c r="A75" s="74"/>
+      <c r="A75" s="72"/>
       <c r="B75" s="17"/>
       <c r="C75" s="43"/>
-      <c r="D75" s="81"/>
+      <c r="D75" s="22"/>
       <c r="E75" s="17"/>
-      <c r="F75" s="71"/>
+      <c r="F75" s="11"/>
       <c r="G75" s="42"/>
-      <c r="H75" s="80"/>
+      <c r="H75" s="78"/>
       <c r="I75" s="12"/>
     </row>
     <row r="76" spans="1:9">
-      <c r="D76" s="82"/>
-      <c r="F76" s="70"/>
+      <c r="D76" s="79"/>
+      <c r="F76" s="69"/>
     </row>
     <row r="77" spans="1:9">
-      <c r="D77" s="82"/>
-      <c r="F77" s="70"/>
+      <c r="D77" s="79"/>
+      <c r="F77" s="69"/>
     </row>
     <row r="78" spans="1:9">
-      <c r="D78" s="82"/>
-      <c r="F78" s="70"/>
+      <c r="D78" s="79"/>
+      <c r="F78" s="69"/>
     </row>
     <row r="79" spans="1:9">
-      <c r="D79" s="82"/>
-      <c r="F79" s="70"/>
+      <c r="D79" s="79"/>
+      <c r="F79" s="69"/>
     </row>
     <row r="80" spans="1:9">
-      <c r="D80" s="82"/>
-      <c r="F80" s="70"/>
+      <c r="D80" s="79"/>
+      <c r="F80" s="69"/>
     </row>
     <row r="81" spans="4:6">
-      <c r="D81" s="82"/>
-      <c r="F81" s="70"/>
+      <c r="D81" s="79"/>
+      <c r="F81" s="69"/>
     </row>
     <row r="82" spans="4:6">
-      <c r="D82" s="82"/>
-      <c r="F82" s="70"/>
+      <c r="D82" s="79"/>
+      <c r="F82" s="69"/>
     </row>
     <row r="83" spans="4:6">
-      <c r="D83" s="82"/>
-      <c r="F83" s="70"/>
+      <c r="D83" s="79"/>
+      <c r="F83" s="69"/>
     </row>
     <row r="84" spans="4:6">
-      <c r="D84" s="82"/>
-      <c r="F84" s="70"/>
+      <c r="D84" s="79"/>
+      <c r="F84" s="69"/>
     </row>
     <row r="85" spans="4:6">
-      <c r="D85" s="82"/>
-      <c r="F85" s="70"/>
+      <c r="D85" s="79"/>
+      <c r="F85" s="69"/>
     </row>
     <row r="86" spans="4:6">
-      <c r="D86" s="82"/>
-      <c r="F86" s="70"/>
+      <c r="D86" s="79"/>
+      <c r="F86" s="69"/>
     </row>
     <row r="87" spans="4:6">
-      <c r="D87" s="82"/>
-      <c r="F87" s="70"/>
+      <c r="D87" s="79"/>
+      <c r="F87" s="69"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
@@ -7180,6 +8595,65 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="45" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="489f8e21b9a70c9d7a16fa4497d5b683">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2f3b4a981d4ba54fcf1b71789fe9b31f" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -7563,71 +9037,12 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268BCB75-17D2-45F5-B1E9-C5CD2BE347D5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7635,5 +9050,5 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{085BABE9-4E2E-49DF-BDAB-445AA4DA56A3}"/>
 </file>
--- a/Treinamento/Index/Relatório de Recusas 23.02.2026 a 01.03.2026.xlsx
+++ b/Treinamento/Index/Relatório de Recusas 23.02.2026 a 01.03.2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/shirlei_witkowski_allianz_com_br/Documents/Planilha de recusa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A6A7E49-6A09-4E11-9B63-F6455DF9E5CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BE62940-F149-4817-A5E8-0CDE7F85C401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="23.02" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="213">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -594,6 +594,185 @@
 Identificamos uma divergência entre o modelo do
 veículo informado na transmissão da proposta devido a isso estamo
 s recusando a proposta em questão.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUELI PATRICIA DA ROCHA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCO AURELIO BRUNO CRESTO                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANA CAROLINA LOBO GLUCK PAUL                 </t>
+  </si>
+  <si>
+    <t>Favor enviar cópia completa da apólice referente 2025/2026 (Não
+será aceito a CI, uma vez em que a CBE não retorna os dados).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIZ ANTONIO MACHADO MELLO                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOAO PAULO TREVISAN                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FELIPE GENOVES EIGENHEER                     </t>
+  </si>
+  <si>
+    <t>Proposta em duplicidade
+Informamos que a pr
+oposta em questão se encontra em duplicidade com a proposta 136723
+533 , para prosseguirmos com a emissão se faz necessário realizar
+o cancelamento da mesma.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MILTON APARECIDO DO NASCIMENTO               </t>
+  </si>
+  <si>
+    <t>Proposta em duplicidade
+Informamos que a pr
+oposta em questão se encontra em duplicidade com a apólice 5177202
+651310177770, para prosseguirmos com a emissão se faz necessário r
+ealizar o cancelamento da mesma.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIZ CARLOS SANTOS RAMOS                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATRICIA DE ALMEIDA PASSOS                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRANSPORTES GRS LTDA ME                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FABIO FERNANDES DE FREITAS                   </t>
+  </si>
+  <si>
+    <t>Conforme CBE pela regra de mudança de cobertura
+, ocorre a redução de 1 classe de bônus, assim sendo o correto bôn
+us 0.Com a correção ficou 10x R$ 517,14. Podemos emitir desta for
+ma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCIO MEDRANO                               </t>
+  </si>
+  <si>
+    <t>Apólice que está sendo renovada já foi utilizada na renovação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCAS VASCONCELOS PINHEIRO                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DONIZETE DO NASCIMENTO                       </t>
+  </si>
+  <si>
+    <t>C
+onforme CBE houve sinistro na apólice anterior, portanto a renovaç
+ão correta é externa COM sinistro, conforme regra diminui uma clas
+se debônus, assim sendo o correto bônus  0 .
+Com a correção
+ficou 10x R$ 1.402,95. Podemos emitir desta forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAIR RODRIGUES AVELAR                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOAO PEDRO FLORES OLIVEIRA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIEGO FERNANDO CHACON                        </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não
+há possibilidade efetuar a transferência de bônus para o(a) senhor
+(a) DIEGO FERNANDO CHACON, pois este não consta no quadro de sócio
+s administradores da empresa.
+Neste caso estamos nesta data e
+fetuando a recusa desta proposta. Orientamos transmitir um novo pr
+ocesso como Seguro Novo."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIEL FERREIRA DE BARROS JUNIOR             </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não
+há possibilidade efetuar a transferência de bônus para o(a) senhor
+(a) DANIEL FERREIRA DE BARROS JUNIOR, pois este consta como condu
+tor a menos de 60 dias na apólice.
+Para que possamos seguir com
+a emissão do documento, a forma de contratação deverá ocorrer com
+o Seguro Novo.
+Neste caso estamos nesta data efetuando a recusa
+desta proposta. Orientamos transmitir um novo processo como Segur
+o Novo."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRACEMA VENTURINI                            </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que
+a apólice consta ativa na congênere, para que possamos prossegui
+r coma liberação do bloqueio será necessário a apresentação do e
+ndosso de cancelamento emitido, a atualização junto a Central de B
+ônus.
+Observação: A Liberação só poderá ser realiza
+da mediante documento solicitado, não serão aceitos protocolos
+ou qualquer outro documento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCISCO LUCAS MARIANO DA ROCHA             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALEXANDRE LUIZ PINTO DO AMARAL               </t>
+  </si>
+  <si>
+    <t>Confirmação de bônus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GREICE LUZIA POZZA                           </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, a apólice foi renovada na
+congênere de origem. Portanto, peço a gentileza de encaminhar a d
+ocumentação abaixo para análise:
+ Cópia da apólice congênere c
+om vigência de 2026 a 2027.
+ Endosso de cancelamento emitido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUCELIO ALEIXO DE BARROS                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAMES ERNESTO SANCHEZ FUENTES                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">59 247 683 LOURENCO MENDES MALAFAIA FILHO ME </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VISTORIA A FRUSTRAR COM FOTOS INCORRETAS. FOTO: CHASSI.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUGEMIRO TEIXEIRA VASCONCELLOS               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCINEIDE FLAUZINO DIAS                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMANDA VALEJO FERRAZ                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDRO PAULO DE CARVALHO ALMEIDA              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HELEN SILVA CERQUEIRA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GABRIELLA JORGE DE MORAES                    </t>
+  </si>
+  <si>
+    <t>E H CONSTRUTORA E EMPREENDIMENTOS IMOBILIARIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RENATA GOMES COSTANTINI                      </t>
   </si>
 </sst>
 </file>
@@ -658,7 +837,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -836,39 +1015,6 @@
     <border>
       <left/>
       <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
@@ -915,7 +1061,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -967,14 +1113,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1068,26 +1208,11 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1102,13 +1227,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1139,14 +1264,32 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1553,10 +1696,10 @@
       <c r="B2" s="7">
         <v>46059</v>
       </c>
-      <c r="C2" s="25">
+      <c r="C2" s="23">
         <v>46076</v>
       </c>
-      <c r="D2" s="22">
+      <c r="D2" s="21">
         <v>136644540</v>
       </c>
       <c r="E2" s="17">
@@ -1565,13 +1708,13 @@
       <c r="F2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="42" t="s">
+      <c r="G2" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="44" t="s">
+      <c r="H2" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="43">
+      <c r="I2" s="41">
         <v>46066</v>
       </c>
     </row>
@@ -1582,10 +1725,10 @@
       <c r="B3" s="7">
         <v>46064</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C3" s="23">
         <v>46076</v>
       </c>
-      <c r="D3" s="22">
+      <c r="D3" s="21">
         <v>136703723</v>
       </c>
       <c r="E3" s="17">
@@ -1594,13 +1737,13 @@
       <c r="F3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="42" t="s">
+      <c r="G3" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="44" t="s">
+      <c r="H3" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="43">
+      <c r="I3" s="41">
         <v>46064</v>
       </c>
     </row>
@@ -1611,10 +1754,10 @@
       <c r="B4" s="7">
         <v>46064</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="23">
         <v>46076</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="21">
         <v>136702771</v>
       </c>
       <c r="E4" s="17">
@@ -1623,13 +1766,13 @@
       <c r="F4" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="42" t="s">
+      <c r="G4" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="44" t="s">
+      <c r="H4" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="43">
+      <c r="I4" s="41">
         <v>46076</v>
       </c>
     </row>
@@ -1640,10 +1783,10 @@
       <c r="B5" s="7">
         <v>46064</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="23">
         <v>46076</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="21">
         <v>136709355</v>
       </c>
       <c r="E5" s="17">
@@ -1652,13 +1795,13 @@
       <c r="F5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="42" t="s">
+      <c r="G5" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="44" t="s">
+      <c r="H5" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="41">
         <v>46076</v>
       </c>
     </row>
@@ -1669,10 +1812,10 @@
       <c r="B6" s="7">
         <v>46064</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="23">
         <v>46076</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="21">
         <v>136711910</v>
       </c>
       <c r="E6" s="17">
@@ -1681,13 +1824,13 @@
       <c r="F6" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="42" t="s">
+      <c r="G6" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="44" t="s">
+      <c r="H6" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="I6" s="43">
+      <c r="I6" s="41">
         <v>46064</v>
       </c>
     </row>
@@ -1698,10 +1841,10 @@
       <c r="B7" s="7">
         <v>46065</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="23">
         <v>46076</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="21">
         <v>136650596</v>
       </c>
       <c r="E7" s="17">
@@ -1710,13 +1853,13 @@
       <c r="F7" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="42" t="s">
+      <c r="G7" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="44" t="s">
+      <c r="H7" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="43">
+      <c r="I7" s="41">
         <v>46072</v>
       </c>
     </row>
@@ -1727,10 +1870,10 @@
       <c r="B8" s="7">
         <v>46066</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="23">
         <v>46076</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="21">
         <v>136653043</v>
       </c>
       <c r="E8" s="17">
@@ -1739,13 +1882,13 @@
       <c r="F8" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="42" t="s">
+      <c r="G8" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="44" t="s">
+      <c r="H8" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="I8" s="43">
+      <c r="I8" s="41">
         <v>46073</v>
       </c>
     </row>
@@ -1756,10 +1899,10 @@
       <c r="B9" s="7">
         <v>46076</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="23">
         <v>46076</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="21">
         <v>136695554</v>
       </c>
       <c r="E9" s="17">
@@ -1768,13 +1911,13 @@
       <c r="F9" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="42" t="s">
+      <c r="G9" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="44" t="s">
+      <c r="H9" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="43">
+      <c r="I9" s="41">
         <v>46076</v>
       </c>
     </row>
@@ -1785,10 +1928,10 @@
       <c r="B10" s="7">
         <v>46064</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="23">
         <v>46076</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="21">
         <v>136696152</v>
       </c>
       <c r="E10" s="17">
@@ -1797,13 +1940,13 @@
       <c r="F10" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="G10" s="42" t="s">
+      <c r="G10" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="44" t="s">
+      <c r="H10" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I10" s="43">
+      <c r="I10" s="41">
         <v>46064</v>
       </c>
     </row>
@@ -1814,10 +1957,10 @@
       <c r="B11" s="7">
         <v>46061</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="23">
         <v>46076</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="21">
         <v>136698227</v>
       </c>
       <c r="E11" s="17">
@@ -1826,13 +1969,13 @@
       <c r="F11" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G11" s="42" t="s">
+      <c r="G11" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="44" t="s">
+      <c r="H11" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="I11" s="43">
+      <c r="I11" s="41">
         <v>46076</v>
       </c>
     </row>
@@ -1843,10 +1986,10 @@
       <c r="B12" s="7">
         <v>46064</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="23">
         <v>46076</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="21">
         <v>136699763</v>
       </c>
       <c r="E12" s="17">
@@ -1855,13 +1998,13 @@
       <c r="F12" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="42" t="s">
+      <c r="G12" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H12" s="44" t="s">
+      <c r="H12" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I12" s="43">
+      <c r="I12" s="41">
         <v>46064</v>
       </c>
     </row>
@@ -1872,10 +2015,10 @@
       <c r="B13" s="7">
         <v>46064</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="23">
         <v>46076</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="21">
         <v>136701112</v>
       </c>
       <c r="E13" s="17">
@@ -1884,13 +2027,13 @@
       <c r="F13" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="G13" s="42" t="s">
+      <c r="G13" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="44" t="s">
+      <c r="H13" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="43">
+      <c r="I13" s="41">
         <v>46064</v>
       </c>
     </row>
@@ -1901,10 +2044,10 @@
       <c r="B14" s="7">
         <v>46058</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="23">
         <v>46076</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="21">
         <v>136701862</v>
       </c>
       <c r="E14" s="17">
@@ -1913,13 +2056,13 @@
       <c r="F14" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="42" t="s">
+      <c r="G14" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="44" t="s">
+      <c r="H14" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="43">
+      <c r="I14" s="41">
         <v>46058</v>
       </c>
     </row>
@@ -1930,10 +2073,10 @@
       <c r="B15" s="7">
         <v>46064</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="23">
         <v>46076</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="21">
         <v>136702698</v>
       </c>
       <c r="E15" s="17">
@@ -1942,13 +2085,13 @@
       <c r="F15" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="G15" s="42" t="s">
+      <c r="G15" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H15" s="44" t="s">
+      <c r="H15" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I15" s="43">
+      <c r="I15" s="41">
         <v>46064</v>
       </c>
     </row>
@@ -1959,10 +2102,10 @@
       <c r="B16" s="7">
         <v>46077</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="23">
         <v>46076</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="21">
         <v>136703294</v>
       </c>
       <c r="E16" s="17">
@@ -1971,13 +2114,13 @@
       <c r="F16" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="G16" s="42" t="s">
+      <c r="G16" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="H16" s="44" t="s">
+      <c r="H16" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="I16" s="43">
+      <c r="I16" s="41">
         <v>46072</v>
       </c>
     </row>
@@ -1988,10 +2131,10 @@
       <c r="B17" s="7">
         <v>46064</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="23">
         <v>46076</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="21">
         <v>136703949</v>
       </c>
       <c r="E17" s="17">
@@ -2000,13 +2143,13 @@
       <c r="F17" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G17" s="42" t="s">
+      <c r="G17" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="H17" s="44" t="s">
+      <c r="H17" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="I17" s="43">
+      <c r="I17" s="41">
         <v>46076</v>
       </c>
     </row>
@@ -2017,10 +2160,10 @@
       <c r="B18" s="7">
         <v>46064</v>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="23">
         <v>46076</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="21">
         <v>136705066</v>
       </c>
       <c r="E18" s="17">
@@ -2029,13 +2172,13 @@
       <c r="F18" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G18" s="42" t="s">
+      <c r="G18" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H18" s="44" t="s">
+      <c r="H18" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I18" s="43">
+      <c r="I18" s="41">
         <v>46064</v>
       </c>
     </row>
@@ -2046,10 +2189,10 @@
       <c r="B19" s="7">
         <v>46064</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="23">
         <v>46076</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="21">
         <v>136706584</v>
       </c>
       <c r="E19" s="17">
@@ -2058,13 +2201,13 @@
       <c r="F19" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="G19" s="42" t="s">
+      <c r="G19" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H19" s="44" t="s">
+      <c r="H19" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="43">
+      <c r="I19" s="41">
         <v>46064</v>
       </c>
     </row>
@@ -2075,10 +2218,10 @@
       <c r="B20" s="7">
         <v>46064</v>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="23">
         <v>46076</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="21">
         <v>136709051</v>
       </c>
       <c r="E20" s="17">
@@ -2087,13 +2230,13 @@
       <c r="F20" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="G20" s="42" t="s">
+      <c r="G20" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H20" s="44" t="s">
+      <c r="H20" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="43">
+      <c r="I20" s="41">
         <v>46064</v>
       </c>
     </row>
@@ -2104,10 +2247,10 @@
       <c r="B21" s="7">
         <v>46074</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="23">
         <v>46076</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="21">
         <v>136709458</v>
       </c>
       <c r="E21" s="17">
@@ -2116,13 +2259,13 @@
       <c r="F21" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="G21" s="42" t="s">
+      <c r="G21" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="H21" s="44" t="s">
+      <c r="H21" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="I21" s="43">
+      <c r="I21" s="41">
         <v>46073</v>
       </c>
     </row>
@@ -2133,10 +2276,10 @@
       <c r="B22" s="7">
         <v>46064</v>
       </c>
-      <c r="C22" s="25">
+      <c r="C22" s="23">
         <v>46076</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="21">
         <v>136710590</v>
       </c>
       <c r="E22" s="17">
@@ -2145,13 +2288,13 @@
       <c r="F22" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G22" s="42" t="s">
+      <c r="G22" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H22" s="44" t="s">
+      <c r="H22" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="43">
+      <c r="I22" s="41">
         <v>11</v>
       </c>
     </row>
@@ -2162,10 +2305,10 @@
       <c r="B23" s="7">
         <v>46064</v>
       </c>
-      <c r="C23" s="25">
+      <c r="C23" s="23">
         <v>46076</v>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="21">
         <v>136712058</v>
       </c>
       <c r="E23" s="17">
@@ -2174,13 +2317,13 @@
       <c r="F23" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="G23" s="42" t="s">
+      <c r="G23" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H23" s="44" t="s">
+      <c r="H23" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I23" s="43">
+      <c r="I23" s="41">
         <v>46064</v>
       </c>
     </row>
@@ -2191,10 +2334,10 @@
       <c r="B24" s="7">
         <v>46064</v>
       </c>
-      <c r="C24" s="25">
+      <c r="C24" s="23">
         <v>46076</v>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="21">
         <v>136712893</v>
       </c>
       <c r="E24" s="17">
@@ -2203,13 +2346,13 @@
       <c r="F24" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="G24" s="42" t="s">
+      <c r="G24" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H24" s="44" t="s">
+      <c r="H24" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I24" s="43">
+      <c r="I24" s="41">
         <v>46064</v>
       </c>
     </row>
@@ -2220,10 +2363,10 @@
       <c r="B25" s="7">
         <v>46064</v>
       </c>
-      <c r="C25" s="25">
+      <c r="C25" s="23">
         <v>46076</v>
       </c>
-      <c r="D25" s="22">
+      <c r="D25" s="21">
         <v>136713212</v>
       </c>
       <c r="E25" s="17">
@@ -2232,13 +2375,13 @@
       <c r="F25" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G25" s="42" t="s">
+      <c r="G25" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="H25" s="44" t="s">
+      <c r="H25" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="I25" s="43">
+      <c r="I25" s="41">
         <v>46076</v>
       </c>
     </row>
@@ -2249,10 +2392,10 @@
       <c r="B26" s="7">
         <v>46064</v>
       </c>
-      <c r="C26" s="25">
+      <c r="C26" s="23">
         <v>46076</v>
       </c>
-      <c r="D26" s="22">
+      <c r="D26" s="21">
         <v>136713293</v>
       </c>
       <c r="E26" s="17">
@@ -2261,13 +2404,13 @@
       <c r="F26" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G26" s="42" t="s">
+      <c r="G26" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="H26" s="44" t="s">
+      <c r="H26" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="I26" s="43">
+      <c r="I26" s="41">
         <v>46076</v>
       </c>
     </row>
@@ -2278,10 +2421,10 @@
       <c r="B27" s="7">
         <v>46071</v>
       </c>
-      <c r="C27" s="25">
+      <c r="C27" s="23">
         <v>46076</v>
       </c>
-      <c r="D27" s="22">
+      <c r="D27" s="21">
         <v>136780424</v>
       </c>
       <c r="E27" s="17">
@@ -2290,13 +2433,13 @@
       <c r="F27" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="G27" s="42" t="s">
+      <c r="G27" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="H27" s="44" t="s">
+      <c r="H27" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="I27" s="43">
+      <c r="I27" s="41">
         <v>46071</v>
       </c>
     </row>
@@ -2307,10 +2450,10 @@
       <c r="B28" s="7">
         <v>46066</v>
       </c>
-      <c r="C28" s="25">
+      <c r="C28" s="23">
         <v>46076</v>
       </c>
-      <c r="D28" s="22">
+      <c r="D28" s="21">
         <v>136757725</v>
       </c>
       <c r="E28" s="17">
@@ -2319,13 +2462,13 @@
       <c r="F28" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="G28" s="42" t="s">
+      <c r="G28" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="H28" s="44" t="s">
+      <c r="H28" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="I28" s="43">
+      <c r="I28" s="41">
         <v>46073</v>
       </c>
     </row>
@@ -2336,10 +2479,10 @@
       <c r="B29" s="7">
         <v>46073</v>
       </c>
-      <c r="C29" s="25">
+      <c r="C29" s="23">
         <v>46076</v>
       </c>
-      <c r="D29" s="22">
+      <c r="D29" s="21">
         <v>136793836</v>
       </c>
       <c r="E29" s="17">
@@ -2348,13 +2491,13 @@
       <c r="F29" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="G29" s="42" t="s">
+      <c r="G29" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="H29" s="44" t="s">
+      <c r="H29" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="I29" s="43">
+      <c r="I29" s="41">
         <v>46073</v>
       </c>
     </row>
@@ -2365,10 +2508,10 @@
       <c r="B30" s="7">
         <v>46066</v>
       </c>
-      <c r="C30" s="25">
+      <c r="C30" s="23">
         <v>46076</v>
       </c>
-      <c r="D30" s="22">
+      <c r="D30" s="21">
         <v>136726098</v>
       </c>
       <c r="E30" s="17">
@@ -2377,42 +2520,42 @@
       <c r="F30" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G30" s="42" t="s">
+      <c r="G30" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="H30" s="45" t="s">
+      <c r="H30" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="I30" s="43">
+      <c r="I30" s="41">
         <v>46073</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="89" customFormat="1">
-      <c r="A31" s="80" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" s="81">
+    <row r="31" spans="1:9" s="80" customFormat="1">
+      <c r="A31" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="72">
         <v>46066</v>
       </c>
-      <c r="C31" s="82">
+      <c r="C31" s="73">
         <v>46076</v>
       </c>
-      <c r="D31" s="83">
+      <c r="D31" s="74">
         <v>136751753</v>
       </c>
-      <c r="E31" s="84">
+      <c r="E31" s="75">
         <v>3450252531</v>
       </c>
-      <c r="F31" s="85" t="s">
+      <c r="F31" s="76" t="s">
         <v>58</v>
       </c>
-      <c r="G31" s="86" t="s">
+      <c r="G31" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="H31" s="87" t="s">
+      <c r="H31" s="78" t="s">
         <v>55</v>
       </c>
-      <c r="I31" s="88">
+      <c r="I31" s="79">
         <v>46073</v>
       </c>
     </row>
@@ -2423,10 +2566,10 @@
       <c r="B32" s="7">
         <v>46066</v>
       </c>
-      <c r="C32" s="25">
+      <c r="C32" s="23">
         <v>46076</v>
       </c>
-      <c r="D32" s="22">
+      <c r="D32" s="21">
         <v>136741623</v>
       </c>
       <c r="E32" s="17">
@@ -2435,13 +2578,13 @@
       <c r="F32" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G32" s="42" t="s">
+      <c r="G32" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H32" s="44" t="s">
+      <c r="H32" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I32" s="43">
+      <c r="I32" s="41">
         <v>46066</v>
       </c>
     </row>
@@ -2452,10 +2595,10 @@
       <c r="B33" s="7">
         <v>46066</v>
       </c>
-      <c r="C33" s="25">
+      <c r="C33" s="23">
         <v>46076</v>
       </c>
-      <c r="D33" s="22">
+      <c r="D33" s="21">
         <v>136741773</v>
       </c>
       <c r="E33" s="17">
@@ -2464,13 +2607,13 @@
       <c r="F33" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="G33" s="42" t="s">
+      <c r="G33" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H33" s="44" t="s">
+      <c r="H33" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I33" s="43">
+      <c r="I33" s="41">
         <v>46066</v>
       </c>
     </row>
@@ -2481,10 +2624,10 @@
       <c r="B34" s="7">
         <v>46063</v>
       </c>
-      <c r="C34" s="25">
+      <c r="C34" s="23">
         <v>46076</v>
       </c>
-      <c r="D34" s="22">
+      <c r="D34" s="21">
         <v>136743307</v>
       </c>
       <c r="E34" s="17">
@@ -2493,13 +2636,13 @@
       <c r="F34" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="G34" s="42" t="s">
+      <c r="G34" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H34" s="44" t="s">
+      <c r="H34" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I34" s="43">
+      <c r="I34" s="41">
         <v>46063</v>
       </c>
     </row>
@@ -2510,10 +2653,10 @@
       <c r="B35" s="7">
         <v>46066</v>
       </c>
-      <c r="C35" s="25">
+      <c r="C35" s="23">
         <v>46076</v>
       </c>
-      <c r="D35" s="22">
+      <c r="D35" s="21">
         <v>136745446</v>
       </c>
       <c r="E35" s="17">
@@ -2522,13 +2665,13 @@
       <c r="F35" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="G35" s="42" t="s">
+      <c r="G35" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H35" s="44" t="s">
+      <c r="H35" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I35" s="43">
+      <c r="I35" s="41">
         <v>46066</v>
       </c>
     </row>
@@ -2539,10 +2682,10 @@
       <c r="B36" s="7">
         <v>46066</v>
       </c>
-      <c r="C36" s="25">
+      <c r="C36" s="23">
         <v>46076</v>
       </c>
-      <c r="D36" s="22">
+      <c r="D36" s="21">
         <v>136745892</v>
       </c>
       <c r="E36" s="17">
@@ -2551,13 +2694,13 @@
       <c r="F36" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G36" s="42" t="s">
+      <c r="G36" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H36" s="44" t="s">
+      <c r="H36" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I36" s="43">
+      <c r="I36" s="41">
         <v>46066</v>
       </c>
     </row>
@@ -2568,10 +2711,10 @@
       <c r="B37" s="7">
         <v>46066</v>
       </c>
-      <c r="C37" s="25">
+      <c r="C37" s="23">
         <v>46076</v>
       </c>
-      <c r="D37" s="22">
+      <c r="D37" s="21">
         <v>136746253</v>
       </c>
       <c r="E37" s="17">
@@ -2580,13 +2723,13 @@
       <c r="F37" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="G37" s="42" t="s">
+      <c r="G37" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H37" s="44" t="s">
+      <c r="H37" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I37" s="43">
+      <c r="I37" s="41">
         <v>46066</v>
       </c>
     </row>
@@ -2597,10 +2740,10 @@
       <c r="B38" s="7">
         <v>46066</v>
       </c>
-      <c r="C38" s="25">
+      <c r="C38" s="23">
         <v>46076</v>
       </c>
-      <c r="D38" s="22">
+      <c r="D38" s="21">
         <v>136747220</v>
       </c>
       <c r="E38" s="17">
@@ -2609,13 +2752,13 @@
       <c r="F38" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="G38" s="42" t="s">
+      <c r="G38" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H38" s="44" t="s">
+      <c r="H38" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I38" s="43">
+      <c r="I38" s="41">
         <v>46066</v>
       </c>
     </row>
@@ -2626,10 +2769,10 @@
       <c r="B39" s="7">
         <v>46064</v>
       </c>
-      <c r="C39" s="25">
+      <c r="C39" s="23">
         <v>46076</v>
       </c>
-      <c r="D39" s="22">
+      <c r="D39" s="21">
         <v>136747223</v>
       </c>
       <c r="E39" s="17">
@@ -2638,13 +2781,13 @@
       <c r="F39" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="G39" s="42" t="s">
+      <c r="G39" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H39" s="44" t="s">
+      <c r="H39" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I39" s="43">
+      <c r="I39" s="41">
         <v>46064</v>
       </c>
     </row>
@@ -2655,10 +2798,10 @@
       <c r="B40" s="7">
         <v>46066</v>
       </c>
-      <c r="C40" s="25">
+      <c r="C40" s="23">
         <v>46076</v>
       </c>
-      <c r="D40" s="22">
+      <c r="D40" s="21">
         <v>136747238</v>
       </c>
       <c r="E40" s="17">
@@ -2667,13 +2810,13 @@
       <c r="F40" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="G40" s="42" t="s">
+      <c r="G40" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H40" s="44" t="s">
+      <c r="H40" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I40" s="43">
+      <c r="I40" s="41">
         <v>46066</v>
       </c>
     </row>
@@ -2684,10 +2827,10 @@
       <c r="B41" s="7">
         <v>46066</v>
       </c>
-      <c r="C41" s="25">
+      <c r="C41" s="23">
         <v>46076</v>
       </c>
-      <c r="D41" s="22">
+      <c r="D41" s="21">
         <v>136748548</v>
       </c>
       <c r="E41" s="17">
@@ -2696,13 +2839,13 @@
       <c r="F41" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="G41" s="42" t="s">
+      <c r="G41" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H41" s="44" t="s">
+      <c r="H41" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I41" s="43">
+      <c r="I41" s="41">
         <v>46066</v>
       </c>
     </row>
@@ -2713,10 +2856,10 @@
       <c r="B42" s="7">
         <v>46066</v>
       </c>
-      <c r="C42" s="25">
+      <c r="C42" s="23">
         <v>46076</v>
       </c>
-      <c r="D42" s="22">
+      <c r="D42" s="21">
         <v>136748679</v>
       </c>
       <c r="E42" s="17">
@@ -2725,13 +2868,13 @@
       <c r="F42" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="G42" s="42" t="s">
+      <c r="G42" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H42" s="44" t="s">
+      <c r="H42" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I42" s="43">
+      <c r="I42" s="41">
         <v>46066</v>
       </c>
     </row>
@@ -2742,10 +2885,10 @@
       <c r="B43" s="7">
         <v>46064</v>
       </c>
-      <c r="C43" s="25">
+      <c r="C43" s="23">
         <v>46076</v>
       </c>
-      <c r="D43" s="22">
+      <c r="D43" s="21">
         <v>136749016</v>
       </c>
       <c r="E43" s="17">
@@ -2754,13 +2897,13 @@
       <c r="F43" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="G43" s="42" t="s">
+      <c r="G43" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H43" s="44" t="s">
+      <c r="H43" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I43" s="43">
+      <c r="I43" s="41">
         <v>46064</v>
       </c>
     </row>
@@ -2771,10 +2914,10 @@
       <c r="B44" s="7">
         <v>46066</v>
       </c>
-      <c r="C44" s="25">
+      <c r="C44" s="23">
         <v>46076</v>
       </c>
-      <c r="D44" s="22">
+      <c r="D44" s="21">
         <v>136749185</v>
       </c>
       <c r="E44" s="17">
@@ -2783,13 +2926,13 @@
       <c r="F44" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="G44" s="42" t="s">
+      <c r="G44" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H44" s="44" t="s">
+      <c r="H44" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I44" s="43">
+      <c r="I44" s="41">
         <v>46066</v>
       </c>
     </row>
@@ -2800,10 +2943,10 @@
       <c r="B45" s="7">
         <v>46066</v>
       </c>
-      <c r="C45" s="25">
+      <c r="C45" s="23">
         <v>46076</v>
       </c>
-      <c r="D45" s="22">
+      <c r="D45" s="21">
         <v>136749240</v>
       </c>
       <c r="E45" s="17">
@@ -2812,13 +2955,13 @@
       <c r="F45" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="G45" s="42" t="s">
+      <c r="G45" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H45" s="44" t="s">
+      <c r="H45" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I45" s="43">
+      <c r="I45" s="41">
         <v>46066</v>
       </c>
     </row>
@@ -2829,10 +2972,10 @@
       <c r="B46" s="7">
         <v>46066</v>
       </c>
-      <c r="C46" s="25">
+      <c r="C46" s="23">
         <v>46076</v>
       </c>
-      <c r="D46" s="22">
+      <c r="D46" s="21">
         <v>136749297</v>
       </c>
       <c r="E46" s="17">
@@ -2841,13 +2984,13 @@
       <c r="F46" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="G46" s="42" t="s">
+      <c r="G46" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="H46" s="44" t="s">
+      <c r="H46" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="I46" s="43">
+      <c r="I46" s="41">
         <v>46066</v>
       </c>
     </row>
@@ -2858,10 +3001,10 @@
       <c r="B47" s="7">
         <v>46064</v>
       </c>
-      <c r="C47" s="25">
+      <c r="C47" s="23">
         <v>46076</v>
       </c>
-      <c r="D47" s="22">
+      <c r="D47" s="21">
         <v>136749595</v>
       </c>
       <c r="E47" s="17">
@@ -2870,13 +3013,13 @@
       <c r="F47" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="G47" s="42" t="s">
+      <c r="G47" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H47" s="44" t="s">
+      <c r="H47" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I47" s="43">
+      <c r="I47" s="41">
         <v>46064</v>
       </c>
     </row>
@@ -2887,10 +3030,10 @@
       <c r="B48" s="7">
         <v>46066</v>
       </c>
-      <c r="C48" s="25">
+      <c r="C48" s="23">
         <v>46076</v>
       </c>
-      <c r="D48" s="22">
+      <c r="D48" s="21">
         <v>136749625</v>
       </c>
       <c r="E48" s="17">
@@ -2899,13 +3042,13 @@
       <c r="F48" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="G48" s="42" t="s">
+      <c r="G48" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H48" s="44" t="s">
+      <c r="H48" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I48" s="43">
+      <c r="I48" s="41">
         <v>46066</v>
       </c>
     </row>
@@ -2916,10 +3059,10 @@
       <c r="B49" s="7">
         <v>46066</v>
       </c>
-      <c r="C49" s="25">
+      <c r="C49" s="23">
         <v>46076</v>
       </c>
-      <c r="D49" s="22">
+      <c r="D49" s="21">
         <v>136750369</v>
       </c>
       <c r="E49" s="17">
@@ -2928,13 +3071,13 @@
       <c r="F49" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="G49" s="42" t="s">
+      <c r="G49" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H49" s="44" t="s">
+      <c r="H49" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I49" s="43">
+      <c r="I49" s="41">
         <v>46066</v>
       </c>
     </row>
@@ -2945,10 +3088,10 @@
       <c r="B50" s="7">
         <v>46066</v>
       </c>
-      <c r="C50" s="25">
+      <c r="C50" s="23">
         <v>46076</v>
       </c>
-      <c r="D50" s="22">
+      <c r="D50" s="21">
         <v>136751442</v>
       </c>
       <c r="E50" s="17">
@@ -2957,13 +3100,13 @@
       <c r="F50" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="G50" s="42" t="s">
+      <c r="G50" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H50" s="44" t="s">
+      <c r="H50" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I50" s="43">
+      <c r="I50" s="41">
         <v>46066</v>
       </c>
     </row>
@@ -2974,10 +3117,10 @@
       <c r="B51" s="7">
         <v>46066</v>
       </c>
-      <c r="C51" s="25">
+      <c r="C51" s="23">
         <v>46076</v>
       </c>
-      <c r="D51" s="22">
+      <c r="D51" s="21">
         <v>136752831</v>
       </c>
       <c r="E51" s="17">
@@ -2986,13 +3129,13 @@
       <c r="F51" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="G51" s="42" t="s">
+      <c r="G51" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H51" s="44" t="s">
+      <c r="H51" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I51" s="43">
+      <c r="I51" s="41">
         <v>46066</v>
       </c>
     </row>
@@ -3000,13 +3143,13 @@
       <c r="A52" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B52" s="46">
+      <c r="B52" s="44">
         <v>46066</v>
       </c>
-      <c r="C52" s="25">
+      <c r="C52" s="23">
         <v>46076</v>
       </c>
-      <c r="D52" s="22">
+      <c r="D52" s="21">
         <v>136754474</v>
       </c>
       <c r="E52" s="17">
@@ -3015,13 +3158,13 @@
       <c r="F52" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="G52" s="42" t="s">
+      <c r="G52" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H52" s="44" t="s">
+      <c r="H52" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I52" s="43">
+      <c r="I52" s="41">
         <v>46066</v>
       </c>
     </row>
@@ -3032,10 +3175,10 @@
       <c r="B53" s="7">
         <v>46066</v>
       </c>
-      <c r="C53" s="25">
+      <c r="C53" s="23">
         <v>46076</v>
       </c>
-      <c r="D53" s="22">
+      <c r="D53" s="21">
         <v>136754971</v>
       </c>
       <c r="E53" s="17">
@@ -3044,13 +3187,13 @@
       <c r="F53" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="G53" s="42" t="s">
+      <c r="G53" s="40" t="s">
         <v>14</v>
       </c>
       <c r="H53" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I53" s="43">
+      <c r="I53" s="41">
         <v>46066</v>
       </c>
     </row>
@@ -3061,10 +3204,10 @@
       <c r="B54" s="7">
         <v>46065</v>
       </c>
-      <c r="C54" s="25">
+      <c r="C54" s="23">
         <v>46076</v>
       </c>
-      <c r="D54" s="22">
+      <c r="D54" s="21">
         <v>136755061</v>
       </c>
       <c r="E54" s="17">
@@ -3073,13 +3216,13 @@
       <c r="F54" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="G54" s="42" t="s">
+      <c r="G54" s="40" t="s">
         <v>14</v>
       </c>
       <c r="H54" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I54" s="43">
+      <c r="I54" s="41">
         <v>46065</v>
       </c>
     </row>
@@ -3090,10 +3233,10 @@
       <c r="B55" s="7">
         <v>46066</v>
       </c>
-      <c r="C55" s="25">
+      <c r="C55" s="23">
         <v>46076</v>
       </c>
-      <c r="D55" s="22">
+      <c r="D55" s="21">
         <v>136756419</v>
       </c>
       <c r="E55" s="17">
@@ -3102,13 +3245,13 @@
       <c r="F55" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="G55" s="42" t="s">
+      <c r="G55" s="40" t="s">
         <v>14</v>
       </c>
       <c r="H55" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I55" s="43">
+      <c r="I55" s="41">
         <v>46066</v>
       </c>
     </row>
@@ -3119,10 +3262,10 @@
       <c r="B56" s="7">
         <v>46065</v>
       </c>
-      <c r="C56" s="25">
+      <c r="C56" s="23">
         <v>46076</v>
       </c>
-      <c r="D56" s="22">
+      <c r="D56" s="21">
         <v>136756531</v>
       </c>
       <c r="E56" s="17">
@@ -3131,13 +3274,13 @@
       <c r="F56" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="G56" s="42" t="s">
+      <c r="G56" s="40" t="s">
         <v>14</v>
       </c>
       <c r="H56" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I56" s="43">
+      <c r="I56" s="41">
         <v>46065</v>
       </c>
     </row>
@@ -3148,10 +3291,10 @@
       <c r="B57" s="7">
         <v>46066</v>
       </c>
-      <c r="C57" s="25">
+      <c r="C57" s="23">
         <v>46076</v>
       </c>
-      <c r="D57" s="22">
+      <c r="D57" s="21">
         <v>136759573</v>
       </c>
       <c r="E57" s="17">
@@ -3160,13 +3303,13 @@
       <c r="F57" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="G57" s="42" t="s">
+      <c r="G57" s="40" t="s">
         <v>14</v>
       </c>
       <c r="H57" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I57" s="43">
+      <c r="I57" s="41">
         <v>46066</v>
       </c>
     </row>
@@ -3177,10 +3320,10 @@
       <c r="B58" s="7">
         <v>46066</v>
       </c>
-      <c r="C58" s="25">
+      <c r="C58" s="23">
         <v>46076</v>
       </c>
-      <c r="D58" s="22">
+      <c r="D58" s="21">
         <v>136759623</v>
       </c>
       <c r="E58" s="17">
@@ -3189,13 +3332,13 @@
       <c r="F58" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="G58" s="42" t="s">
+      <c r="G58" s="40" t="s">
         <v>14</v>
       </c>
       <c r="H58" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I58" s="43">
+      <c r="I58" s="41">
         <v>46066</v>
       </c>
     </row>
@@ -3206,10 +3349,10 @@
       <c r="B59" s="7">
         <v>46066</v>
       </c>
-      <c r="C59" s="25">
+      <c r="C59" s="23">
         <v>46076</v>
       </c>
-      <c r="D59" s="22">
+      <c r="D59" s="21">
         <v>136760271</v>
       </c>
       <c r="E59" s="17">
@@ -3218,13 +3361,13 @@
       <c r="F59" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="G59" s="42" t="s">
+      <c r="G59" s="40" t="s">
         <v>14</v>
       </c>
       <c r="H59" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I59" s="43">
+      <c r="I59" s="41">
         <v>46066</v>
       </c>
     </row>
@@ -3235,10 +3378,10 @@
       <c r="B60" s="7">
         <v>46066</v>
       </c>
-      <c r="C60" s="25">
+      <c r="C60" s="23">
         <v>46076</v>
       </c>
-      <c r="D60" s="22">
+      <c r="D60" s="21">
         <v>136760300</v>
       </c>
       <c r="E60" s="17">
@@ -3247,13 +3390,13 @@
       <c r="F60" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="G60" s="42" t="s">
+      <c r="G60" s="40" t="s">
         <v>14</v>
       </c>
       <c r="H60" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I60" s="43">
+      <c r="I60" s="41">
         <v>46066</v>
       </c>
     </row>
@@ -3264,10 +3407,10 @@
       <c r="B61" s="7">
         <v>46066</v>
       </c>
-      <c r="C61" s="25">
+      <c r="C61" s="23">
         <v>46076</v>
       </c>
-      <c r="D61" s="22">
+      <c r="D61" s="21">
         <v>136761612</v>
       </c>
       <c r="E61" s="17">
@@ -3276,13 +3419,13 @@
       <c r="F61" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="G61" s="42" t="s">
+      <c r="G61" s="40" t="s">
         <v>14</v>
       </c>
       <c r="H61" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I61" s="43">
+      <c r="I61" s="41">
         <v>46066</v>
       </c>
     </row>
@@ -3293,10 +3436,10 @@
       <c r="B62" s="7">
         <v>46066</v>
       </c>
-      <c r="C62" s="25">
+      <c r="C62" s="23">
         <v>46076</v>
       </c>
-      <c r="D62" s="22">
+      <c r="D62" s="21">
         <v>136761764</v>
       </c>
       <c r="E62" s="17">
@@ -3305,13 +3448,13 @@
       <c r="F62" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="G62" s="42" t="s">
+      <c r="G62" s="40" t="s">
         <v>14</v>
       </c>
       <c r="H62" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I62" s="43">
+      <c r="I62" s="41">
         <v>46066</v>
       </c>
     </row>
@@ -3322,10 +3465,10 @@
       <c r="B63" s="7">
         <v>46066</v>
       </c>
-      <c r="C63" s="25">
+      <c r="C63" s="23">
         <v>46076</v>
       </c>
-      <c r="D63" s="22">
+      <c r="D63" s="21">
         <v>136761926</v>
       </c>
       <c r="E63" s="17">
@@ -3334,13 +3477,13 @@
       <c r="F63" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="G63" s="42" t="s">
+      <c r="G63" s="40" t="s">
         <v>14</v>
       </c>
       <c r="H63" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I63" s="43">
+      <c r="I63" s="41">
         <v>46066</v>
       </c>
     </row>
@@ -3351,10 +3494,10 @@
       <c r="B64" s="7">
         <v>46066</v>
       </c>
-      <c r="C64" s="25">
+      <c r="C64" s="23">
         <v>46076</v>
       </c>
-      <c r="D64" s="22">
+      <c r="D64" s="21">
         <v>136761966</v>
       </c>
       <c r="E64" s="17">
@@ -3363,13 +3506,13 @@
       <c r="F64" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="G64" s="42" t="s">
+      <c r="G64" s="40" t="s">
         <v>14</v>
       </c>
       <c r="H64" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I64" s="43">
+      <c r="I64" s="41">
         <v>46066</v>
       </c>
     </row>
@@ -3380,10 +3523,10 @@
       <c r="B65" s="7">
         <v>46066</v>
       </c>
-      <c r="C65" s="25">
+      <c r="C65" s="23">
         <v>46076</v>
       </c>
-      <c r="D65" s="22">
+      <c r="D65" s="21">
         <v>136762270</v>
       </c>
       <c r="E65" s="17">
@@ -3392,13 +3535,13 @@
       <c r="F65" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="G65" s="42" t="s">
+      <c r="G65" s="40" t="s">
         <v>14</v>
       </c>
       <c r="H65" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I65" s="48">
+      <c r="I65" s="46">
         <v>46066</v>
       </c>
     </row>
@@ -3409,10 +3552,10 @@
       <c r="B66" s="7">
         <v>46066</v>
       </c>
-      <c r="C66" s="25">
+      <c r="C66" s="23">
         <v>46076</v>
       </c>
-      <c r="D66" s="22">
+      <c r="D66" s="21">
         <v>136762890</v>
       </c>
       <c r="E66" s="17" t="s">
@@ -3424,10 +3567,10 @@
       <c r="G66" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H66" s="47" t="s">
+      <c r="H66" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="I66" s="43">
+      <c r="I66" s="41">
         <v>46066</v>
       </c>
     </row>
@@ -3469,60 +3612,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="52" t="s">
+      <c r="D1" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="52" t="s">
+      <c r="E1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="G1" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="53" t="s">
+      <c r="H1" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="50" t="s">
+      <c r="I1" s="48" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="54">
+      <c r="A2" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="52">
         <v>46074</v>
       </c>
-      <c r="C2" s="55">
+      <c r="C2" s="53">
         <v>46077</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="E2" s="56">
+      <c r="E2" s="54">
         <v>3450257349</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="F2" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="G2" s="57" t="s">
+      <c r="G2" s="55" t="s">
         <v>22</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="I2" s="58" t="s">
+      <c r="I2" s="56" t="s">
         <v>100</v>
       </c>
     </row>
@@ -3533,25 +3676,25 @@
       <c r="B3" s="7">
         <v>46058</v>
       </c>
-      <c r="C3" s="55">
+      <c r="C3" s="53">
         <v>46077</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="E3" s="56">
+      <c r="E3" s="54">
         <v>3450242609</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="F3" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="42" t="s">
+      <c r="G3" s="40" t="s">
         <v>22</v>
       </c>
       <c r="H3" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="I3" s="43"/>
+      <c r="I3" s="41"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -3560,25 +3703,25 @@
       <c r="B4" s="7">
         <v>46062</v>
       </c>
-      <c r="C4" s="55">
+      <c r="C4" s="53">
         <v>46077</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="E4" s="56">
+      <c r="E4" s="54">
         <v>3450246261</v>
       </c>
-      <c r="F4" s="31" t="s">
+      <c r="F4" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="G4" s="42" t="s">
+      <c r="G4" s="40" t="s">
         <v>22</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="I4" s="43"/>
+      <c r="I4" s="41"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
@@ -3587,25 +3730,25 @@
       <c r="B5" s="7">
         <v>46064</v>
       </c>
-      <c r="C5" s="55">
+      <c r="C5" s="53">
         <v>46077</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="E5" s="56">
+      <c r="E5" s="54">
         <v>3450249374</v>
       </c>
-      <c r="F5" s="31" t="s">
+      <c r="F5" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="G5" s="42" t="s">
+      <c r="G5" s="40" t="s">
         <v>22</v>
       </c>
       <c r="H5" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="I5" s="43"/>
+      <c r="I5" s="41"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
@@ -3614,25 +3757,25 @@
       <c r="B6" s="7">
         <v>46071</v>
       </c>
-      <c r="C6" s="55">
+      <c r="C6" s="53">
         <v>46077</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="E6" s="56">
+      <c r="E6" s="54">
         <v>3450254654</v>
       </c>
-      <c r="F6" s="31" t="s">
+      <c r="F6" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="G6" s="42" t="s">
+      <c r="G6" s="40" t="s">
         <v>22</v>
       </c>
       <c r="H6" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="I6" s="43"/>
+      <c r="I6" s="41"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
@@ -3641,25 +3784,25 @@
       <c r="B7" s="7">
         <v>46068</v>
       </c>
-      <c r="C7" s="55">
+      <c r="C7" s="53">
         <v>46077</v>
       </c>
-      <c r="D7" s="90" t="s">
+      <c r="D7" s="81" t="s">
         <v>97</v>
       </c>
-      <c r="E7" s="63">
+      <c r="E7" s="59">
         <v>3450253543</v>
       </c>
-      <c r="F7" s="91" t="s">
+      <c r="F7" s="82" t="s">
         <v>105</v>
       </c>
-      <c r="G7" s="92" t="s">
+      <c r="G7" s="83" t="s">
         <v>22</v>
       </c>
       <c r="H7" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="I7" s="43"/>
+      <c r="I7" s="41"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
@@ -3668,10 +3811,10 @@
       <c r="B8" s="7">
         <v>46088</v>
       </c>
-      <c r="C8" s="55">
+      <c r="C8" s="53">
         <v>46077</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="21">
         <v>136838916</v>
       </c>
       <c r="E8" s="17">
@@ -3680,13 +3823,13 @@
       <c r="F8" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="G8" s="93" t="s">
+      <c r="G8" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="78" t="s">
+      <c r="H8" s="69" t="s">
         <v>107</v>
       </c>
-      <c r="I8" s="43">
+      <c r="I8" s="41">
         <v>46077</v>
       </c>
     </row>
@@ -3697,10 +3840,10 @@
       <c r="B9" s="7">
         <v>46077</v>
       </c>
-      <c r="C9" s="55">
+      <c r="C9" s="53">
         <v>46077</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="21">
         <v>136728307</v>
       </c>
       <c r="E9" s="17">
@@ -3709,13 +3852,13 @@
       <c r="F9" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="G9" s="93" t="s">
+      <c r="G9" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="78" t="s">
+      <c r="H9" s="69" t="s">
         <v>109</v>
       </c>
-      <c r="I9" s="43">
+      <c r="I9" s="41">
         <v>46077</v>
       </c>
     </row>
@@ -3726,10 +3869,10 @@
       <c r="B10" s="7">
         <v>46065</v>
       </c>
-      <c r="C10" s="55">
+      <c r="C10" s="53">
         <v>46077</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="21">
         <v>136734997</v>
       </c>
       <c r="E10" s="17">
@@ -3738,13 +3881,13 @@
       <c r="F10" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="G10" s="93" t="s">
+      <c r="G10" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="78" t="s">
+      <c r="H10" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="I10" s="43">
+      <c r="I10" s="41">
         <v>46065</v>
       </c>
     </row>
@@ -3755,10 +3898,10 @@
       <c r="B11" s="7">
         <v>46064</v>
       </c>
-      <c r="C11" s="55">
+      <c r="C11" s="53">
         <v>46077</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="21">
         <v>136722223</v>
       </c>
       <c r="E11" s="17">
@@ -3767,13 +3910,13 @@
       <c r="F11" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="G11" s="93" t="s">
+      <c r="G11" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="78" t="s">
+      <c r="H11" s="69" t="s">
         <v>113</v>
       </c>
-      <c r="I11" s="43">
+      <c r="I11" s="41">
         <v>46077</v>
       </c>
     </row>
@@ -3784,10 +3927,10 @@
       <c r="B12" s="7">
         <v>46063</v>
       </c>
-      <c r="C12" s="55">
+      <c r="C12" s="53">
         <v>46077</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="21">
         <v>136724519</v>
       </c>
       <c r="E12" s="17">
@@ -3796,13 +3939,13 @@
       <c r="F12" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="G12" s="93" t="s">
+      <c r="G12" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H12" s="78" t="s">
+      <c r="H12" s="69" t="s">
         <v>115</v>
       </c>
-      <c r="I12" s="43">
+      <c r="I12" s="41">
         <v>46077</v>
       </c>
     </row>
@@ -3813,10 +3956,10 @@
       <c r="B13" s="7">
         <v>46065</v>
       </c>
-      <c r="C13" s="55">
+      <c r="C13" s="53">
         <v>46077</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="21">
         <v>136735180</v>
       </c>
       <c r="E13" s="17">
@@ -3825,13 +3968,13 @@
       <c r="F13" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="G13" s="93" t="s">
+      <c r="G13" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="78" t="s">
+      <c r="H13" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="I13" s="43">
+      <c r="I13" s="41">
         <v>46065</v>
       </c>
     </row>
@@ -3842,10 +3985,10 @@
       <c r="B14" s="7">
         <v>46065</v>
       </c>
-      <c r="C14" s="55">
+      <c r="C14" s="53">
         <v>46077</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="21">
         <v>136723934</v>
       </c>
       <c r="E14" s="17">
@@ -3854,13 +3997,13 @@
       <c r="F14" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="G14" s="93" t="s">
+      <c r="G14" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="78" t="s">
+      <c r="H14" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="I14" s="43">
+      <c r="I14" s="41">
         <v>46065</v>
       </c>
     </row>
@@ -3871,10 +4014,10 @@
       <c r="B15" s="7">
         <v>46080</v>
       </c>
-      <c r="C15" s="55">
+      <c r="C15" s="53">
         <v>46077</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="21">
         <v>136729172</v>
       </c>
       <c r="E15" s="17">
@@ -3883,13 +4026,13 @@
       <c r="F15" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="G15" s="93" t="s">
+      <c r="G15" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="H15" s="78" t="s">
+      <c r="H15" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="I15" s="43">
+      <c r="I15" s="41">
         <v>46077</v>
       </c>
     </row>
@@ -3900,10 +4043,10 @@
       <c r="B16" s="7">
         <v>46059</v>
       </c>
-      <c r="C16" s="55">
+      <c r="C16" s="53">
         <v>46077</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="21">
         <v>136725270</v>
       </c>
       <c r="E16" s="17">
@@ -3912,13 +4055,13 @@
       <c r="F16" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="G16" s="93" t="s">
+      <c r="G16" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="H16" s="78" t="s">
+      <c r="H16" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="I16" s="43">
+      <c r="I16" s="41">
         <v>46059</v>
       </c>
     </row>
@@ -3929,10 +4072,10 @@
       <c r="B17" s="7">
         <v>46077</v>
       </c>
-      <c r="C17" s="55">
+      <c r="C17" s="53">
         <v>46077</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="21">
         <v>136723951</v>
       </c>
       <c r="E17" s="17">
@@ -3941,13 +4084,13 @@
       <c r="F17" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="G17" s="93" t="s">
+      <c r="G17" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="H17" s="78" t="s">
+      <c r="H17" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="I17" s="43">
+      <c r="I17" s="41">
         <v>46077</v>
       </c>
     </row>
@@ -3958,10 +4101,10 @@
       <c r="B18" s="7">
         <v>46065</v>
       </c>
-      <c r="C18" s="55">
+      <c r="C18" s="53">
         <v>46077</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="21">
         <v>136726576</v>
       </c>
       <c r="E18" s="17">
@@ -3970,13 +4113,13 @@
       <c r="F18" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="G18" s="93" t="s">
+      <c r="G18" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="H18" s="78" t="s">
+      <c r="H18" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="I18" s="43">
+      <c r="I18" s="41">
         <v>46065</v>
       </c>
     </row>
@@ -3987,10 +4130,10 @@
       <c r="B19" s="7">
         <v>46059</v>
       </c>
-      <c r="C19" s="55">
+      <c r="C19" s="53">
         <v>46077</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="21">
         <v>136724366</v>
       </c>
       <c r="E19" s="17">
@@ -3999,13 +4142,13 @@
       <c r="F19" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="G19" s="93" t="s">
+      <c r="G19" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="H19" s="78" t="s">
+      <c r="H19" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="I19" s="43">
+      <c r="I19" s="41">
         <v>46059</v>
       </c>
     </row>
@@ -4016,10 +4159,10 @@
       <c r="B20" s="7">
         <v>46062</v>
       </c>
-      <c r="C20" s="55">
+      <c r="C20" s="53">
         <v>46077</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="21">
         <v>136730089</v>
       </c>
       <c r="E20" s="17">
@@ -4028,13 +4171,13 @@
       <c r="F20" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="G20" s="93" t="s">
+      <c r="G20" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="H20" s="78" t="s">
+      <c r="H20" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="I20" s="43">
+      <c r="I20" s="41">
         <v>46062</v>
       </c>
     </row>
@@ -4045,10 +4188,10 @@
       <c r="B21" s="7">
         <v>46079</v>
       </c>
-      <c r="C21" s="55">
+      <c r="C21" s="53">
         <v>46077</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="21">
         <v>136724217</v>
       </c>
       <c r="E21" s="17">
@@ -4057,13 +4200,13 @@
       <c r="F21" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="G21" s="93" t="s">
+      <c r="G21" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="H21" s="78" t="s">
+      <c r="H21" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="I21" s="43">
+      <c r="I21" s="41">
         <v>46077</v>
       </c>
     </row>
@@ -4074,10 +4217,10 @@
       <c r="B22" s="7">
         <v>46065</v>
       </c>
-      <c r="C22" s="55">
+      <c r="C22" s="53">
         <v>46077</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="21">
         <v>136724245</v>
       </c>
       <c r="E22" s="17">
@@ -4086,13 +4229,13 @@
       <c r="F22" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="G22" s="93" t="s">
+      <c r="G22" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H22" s="78" t="s">
+      <c r="H22" s="69" t="s">
         <v>126</v>
       </c>
-      <c r="I22" s="43">
+      <c r="I22" s="41">
         <v>46077</v>
       </c>
     </row>
@@ -4103,10 +4246,10 @@
       <c r="B23" s="7">
         <v>46064</v>
       </c>
-      <c r="C23" s="55">
+      <c r="C23" s="53">
         <v>46077</v>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="21">
         <v>136673325</v>
       </c>
       <c r="E23" s="17">
@@ -4115,13 +4258,13 @@
       <c r="F23" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G23" s="93" t="s">
+      <c r="G23" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="H23" s="94" t="s">
+      <c r="H23" s="69" t="s">
         <v>128</v>
       </c>
-      <c r="I23" s="43">
+      <c r="I23" s="41">
         <v>46076</v>
       </c>
     </row>
@@ -4132,10 +4275,10 @@
       <c r="B24" s="7">
         <v>46072</v>
       </c>
-      <c r="C24" s="55">
+      <c r="C24" s="53">
         <v>46077</v>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="21">
         <v>136724805</v>
       </c>
       <c r="E24" s="17">
@@ -4144,13 +4287,13 @@
       <c r="F24" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="G24" s="93" t="s">
+      <c r="G24" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="H24" s="78" t="s">
+      <c r="H24" s="69" t="s">
         <v>130</v>
       </c>
-      <c r="I24" s="43">
+      <c r="I24" s="41">
         <v>46077</v>
       </c>
     </row>
@@ -4161,10 +4304,10 @@
       <c r="B25" s="7">
         <v>46087</v>
       </c>
-      <c r="C25" s="55">
+      <c r="C25" s="53">
         <v>46077</v>
       </c>
-      <c r="D25" s="22">
+      <c r="D25" s="21">
         <v>136679933</v>
       </c>
       <c r="E25" s="17">
@@ -4173,13 +4316,13 @@
       <c r="F25" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="G25" s="93" t="s">
+      <c r="G25" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="H25" s="94" t="s">
+      <c r="H25" s="69" t="s">
         <v>132</v>
       </c>
-      <c r="I25" s="43">
+      <c r="I25" s="41">
         <v>46076</v>
       </c>
     </row>
@@ -4190,10 +4333,10 @@
       <c r="B26" s="7">
         <v>46063</v>
       </c>
-      <c r="C26" s="55">
+      <c r="C26" s="53">
         <v>46077</v>
       </c>
-      <c r="D26" s="22">
+      <c r="D26" s="21">
         <v>136679581</v>
       </c>
       <c r="E26" s="17">
@@ -4202,13 +4345,13 @@
       <c r="F26" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="G26" s="93" t="s">
+      <c r="G26" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="H26" s="94" t="s">
+      <c r="H26" s="69" t="s">
         <v>134</v>
       </c>
-      <c r="I26" s="43">
+      <c r="I26" s="41">
         <v>46076</v>
       </c>
     </row>
@@ -4219,10 +4362,10 @@
       <c r="B27" s="7">
         <v>46068</v>
       </c>
-      <c r="C27" s="55">
+      <c r="C27" s="53">
         <v>46077</v>
       </c>
-      <c r="D27" s="22">
+      <c r="D27" s="21">
         <v>136681490</v>
       </c>
       <c r="E27" s="17">
@@ -4231,13 +4374,13 @@
       <c r="F27" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="G27" s="93" t="s">
+      <c r="G27" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="H27" s="94" t="s">
+      <c r="H27" s="69" t="s">
         <v>136</v>
       </c>
-      <c r="I27" s="43">
+      <c r="I27" s="41">
         <v>46076</v>
       </c>
     </row>
@@ -4248,10 +4391,10 @@
       <c r="B28" s="7">
         <v>46066</v>
       </c>
-      <c r="C28" s="55">
+      <c r="C28" s="53">
         <v>46077</v>
       </c>
-      <c r="D28" s="22">
+      <c r="D28" s="21">
         <v>136722921</v>
       </c>
       <c r="E28" s="17">
@@ -4260,13 +4403,13 @@
       <c r="F28" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="G28" s="93" t="s">
+      <c r="G28" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="H28" s="78" t="s">
+      <c r="H28" s="69" t="s">
         <v>130</v>
       </c>
-      <c r="I28" s="43">
+      <c r="I28" s="41">
         <v>46077</v>
       </c>
     </row>
@@ -4277,10 +4420,10 @@
       <c r="B29" s="7">
         <v>46065</v>
       </c>
-      <c r="C29" s="55">
+      <c r="C29" s="53">
         <v>46077</v>
       </c>
-      <c r="D29" s="22">
+      <c r="D29" s="21">
         <v>136733403</v>
       </c>
       <c r="E29" s="17">
@@ -4289,13 +4432,13 @@
       <c r="F29" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="G29" s="93" t="s">
+      <c r="G29" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="H29" s="78" t="s">
+      <c r="H29" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="I29" s="43">
+      <c r="I29" s="41">
         <v>46065</v>
       </c>
     </row>
@@ -4306,10 +4449,10 @@
       <c r="B30" s="7">
         <v>46063</v>
       </c>
-      <c r="C30" s="55">
+      <c r="C30" s="53">
         <v>46077</v>
       </c>
-      <c r="D30" s="22">
+      <c r="D30" s="21">
         <v>136733601</v>
       </c>
       <c r="E30" s="17">
@@ -4318,13 +4461,13 @@
       <c r="F30" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="G30" s="93" t="s">
+      <c r="G30" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="H30" s="78" t="s">
+      <c r="H30" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="I30" s="43">
+      <c r="I30" s="41">
         <v>46077</v>
       </c>
     </row>
@@ -4335,10 +4478,10 @@
       <c r="B31" s="7">
         <v>46065</v>
       </c>
-      <c r="C31" s="55">
+      <c r="C31" s="53">
         <v>46077</v>
       </c>
-      <c r="D31" s="22">
+      <c r="D31" s="21">
         <v>136733681</v>
       </c>
       <c r="E31" s="17">
@@ -4347,13 +4490,13 @@
       <c r="F31" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="G31" s="93" t="s">
+      <c r="G31" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="H31" s="78" t="s">
+      <c r="H31" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="I31" s="43">
+      <c r="I31" s="41">
         <v>46065</v>
       </c>
     </row>
@@ -4364,10 +4507,10 @@
       <c r="B32" s="7">
         <v>46065</v>
       </c>
-      <c r="C32" s="55">
+      <c r="C32" s="53">
         <v>46077</v>
       </c>
-      <c r="D32" s="22">
+      <c r="D32" s="21">
         <v>136733785</v>
       </c>
       <c r="E32" s="17">
@@ -4376,13 +4519,13 @@
       <c r="F32" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="G32" s="93" t="s">
+      <c r="G32" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="H32" s="78" t="s">
+      <c r="H32" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="I32" s="43">
+      <c r="I32" s="41">
         <v>46065</v>
       </c>
     </row>
@@ -4393,10 +4536,10 @@
       <c r="B33" s="7">
         <v>46065</v>
       </c>
-      <c r="C33" s="55">
+      <c r="C33" s="53">
         <v>46077</v>
       </c>
-      <c r="D33" s="22">
+      <c r="D33" s="21">
         <v>136727335</v>
       </c>
       <c r="E33" s="17">
@@ -4405,13 +4548,13 @@
       <c r="F33" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="G33" s="93" t="s">
+      <c r="G33" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="H33" s="78" t="s">
+      <c r="H33" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="I33" s="43">
+      <c r="I33" s="41">
         <v>46065</v>
       </c>
     </row>
@@ -4422,10 +4565,10 @@
       <c r="B34" s="7">
         <v>46065</v>
       </c>
-      <c r="C34" s="55">
+      <c r="C34" s="53">
         <v>46077</v>
       </c>
-      <c r="D34" s="22">
+      <c r="D34" s="21">
         <v>136734786</v>
       </c>
       <c r="E34" s="17">
@@ -4434,13 +4577,13 @@
       <c r="F34" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="G34" s="93" t="s">
+      <c r="G34" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="H34" s="78" t="s">
+      <c r="H34" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="I34" s="43">
+      <c r="I34" s="41">
         <v>46065</v>
       </c>
     </row>
@@ -4451,10 +4594,10 @@
       <c r="B35" s="7">
         <v>46066</v>
       </c>
-      <c r="C35" s="55">
+      <c r="C35" s="53">
         <v>46077</v>
       </c>
-      <c r="D35" s="22">
+      <c r="D35" s="21">
         <v>136736493</v>
       </c>
       <c r="E35" s="17">
@@ -4463,13 +4606,13 @@
       <c r="F35" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="G35" s="93" t="s">
+      <c r="G35" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="H35" s="78" t="s">
+      <c r="H35" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="I35" s="43">
+      <c r="I35" s="41">
         <v>46077</v>
       </c>
     </row>
@@ -4480,10 +4623,10 @@
       <c r="B36" s="7">
         <v>46065</v>
       </c>
-      <c r="C36" s="55">
+      <c r="C36" s="53">
         <v>46077</v>
       </c>
-      <c r="D36" s="22">
+      <c r="D36" s="21">
         <v>136735931</v>
       </c>
       <c r="E36" s="17">
@@ -4492,13 +4635,13 @@
       <c r="F36" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="G36" s="93" t="s">
+      <c r="G36" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="H36" s="78" t="s">
+      <c r="H36" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="I36" s="43">
+      <c r="I36" s="41">
         <v>46065</v>
       </c>
     </row>
@@ -4509,10 +4652,10 @@
       <c r="B37" s="7">
         <v>46065</v>
       </c>
-      <c r="C37" s="55">
+      <c r="C37" s="53">
         <v>46077</v>
       </c>
-      <c r="D37" s="22">
+      <c r="D37" s="21">
         <v>136727233</v>
       </c>
       <c r="E37" s="17">
@@ -4521,13 +4664,13 @@
       <c r="F37" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="G37" s="93" t="s">
+      <c r="G37" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="H37" s="78" t="s">
+      <c r="H37" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="I37" s="43">
+      <c r="I37" s="41">
         <v>46065</v>
       </c>
     </row>
@@ -4538,10 +4681,10 @@
       <c r="B38" s="7">
         <v>46065</v>
       </c>
-      <c r="C38" s="55">
+      <c r="C38" s="53">
         <v>46077</v>
       </c>
-      <c r="D38" s="22">
+      <c r="D38" s="21">
         <v>136730654</v>
       </c>
       <c r="E38" s="17">
@@ -4550,13 +4693,13 @@
       <c r="F38" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="G38" s="93" t="s">
+      <c r="G38" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="H38" s="78" t="s">
+      <c r="H38" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="I38" s="43">
+      <c r="I38" s="41">
         <v>46077</v>
       </c>
     </row>
@@ -4567,10 +4710,10 @@
       <c r="B39" s="7">
         <v>46067</v>
       </c>
-      <c r="C39" s="55">
+      <c r="C39" s="53">
         <v>46077</v>
       </c>
-      <c r="D39" s="22">
+      <c r="D39" s="21">
         <v>136730967</v>
       </c>
       <c r="E39" s="17">
@@ -4579,13 +4722,13 @@
       <c r="F39" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G39" s="93" t="s">
+      <c r="G39" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="H39" s="78" t="s">
+      <c r="H39" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="I39" s="43">
+      <c r="I39" s="41">
         <v>46077</v>
       </c>
     </row>
@@ -4596,10 +4739,10 @@
       <c r="B40" s="7">
         <v>46065</v>
       </c>
-      <c r="C40" s="55">
+      <c r="C40" s="53">
         <v>46077</v>
       </c>
-      <c r="D40" s="22">
+      <c r="D40" s="21">
         <v>136731705</v>
       </c>
       <c r="E40" s="17">
@@ -4608,13 +4751,13 @@
       <c r="F40" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="G40" s="93" t="s">
+      <c r="G40" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="H40" s="78" t="s">
+      <c r="H40" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="I40" s="43">
+      <c r="I40" s="41">
         <v>46065</v>
       </c>
     </row>
@@ -4625,10 +4768,10 @@
       <c r="B41" s="7">
         <v>46065</v>
       </c>
-      <c r="C41" s="55">
+      <c r="C41" s="53">
         <v>46077</v>
       </c>
-      <c r="D41" s="22">
+      <c r="D41" s="21">
         <v>136733115</v>
       </c>
       <c r="E41" s="17">
@@ -4637,13 +4780,13 @@
       <c r="F41" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="G41" s="93" t="s">
+      <c r="G41" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H41" s="78" t="s">
+      <c r="H41" s="69" t="s">
         <v>126</v>
       </c>
-      <c r="I41" s="43">
+      <c r="I41" s="41">
         <v>46077</v>
       </c>
     </row>
@@ -4654,10 +4797,10 @@
       <c r="B42" s="7">
         <v>46065</v>
       </c>
-      <c r="C42" s="55">
+      <c r="C42" s="53">
         <v>46077</v>
       </c>
-      <c r="D42" s="22">
+      <c r="D42" s="21">
         <v>136733202</v>
       </c>
       <c r="E42" s="17">
@@ -4666,13 +4809,13 @@
       <c r="F42" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="G42" s="93" t="s">
+      <c r="G42" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H42" s="78" t="s">
+      <c r="H42" s="69" t="s">
         <v>126</v>
       </c>
-      <c r="I42" s="43">
+      <c r="I42" s="41">
         <v>46077</v>
       </c>
     </row>
@@ -4683,10 +4826,10 @@
       <c r="B43" s="7">
         <v>46062</v>
       </c>
-      <c r="C43" s="55">
+      <c r="C43" s="53">
         <v>46077</v>
       </c>
-      <c r="D43" s="22">
+      <c r="D43" s="21">
         <v>136734975</v>
       </c>
       <c r="E43" s="17">
@@ -4695,13 +4838,13 @@
       <c r="F43" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="G43" s="93" t="s">
+      <c r="G43" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="H43" s="78" t="s">
+      <c r="H43" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="I43" s="43">
+      <c r="I43" s="41">
         <v>46062</v>
       </c>
     </row>
@@ -4712,10 +4855,10 @@
       <c r="B44" s="7">
         <v>46062</v>
       </c>
-      <c r="C44" s="55">
+      <c r="C44" s="53">
         <v>46077</v>
       </c>
-      <c r="D44" s="22">
+      <c r="D44" s="21">
         <v>136735098</v>
       </c>
       <c r="E44" s="17">
@@ -4724,13 +4867,13 @@
       <c r="F44" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="G44" s="93" t="s">
+      <c r="G44" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="H44" s="78" t="s">
+      <c r="H44" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="I44" s="43">
+      <c r="I44" s="41">
         <v>46062</v>
       </c>
     </row>
@@ -4741,10 +4884,10 @@
       <c r="B45" s="7">
         <v>46090</v>
       </c>
-      <c r="C45" s="55">
+      <c r="C45" s="53">
         <v>46077</v>
       </c>
-      <c r="D45" s="22">
+      <c r="D45" s="21">
         <v>136667128</v>
       </c>
       <c r="E45" s="17">
@@ -4753,13 +4896,13 @@
       <c r="F45" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="G45" s="93" t="s">
+      <c r="G45" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="H45" s="94" t="s">
+      <c r="H45" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="I45" s="43">
+      <c r="I45" s="41">
         <v>46076</v>
       </c>
     </row>
@@ -4770,10 +4913,10 @@
       <c r="B46" s="7">
         <v>46079</v>
       </c>
-      <c r="C46" s="55">
+      <c r="C46" s="53">
         <v>46077</v>
       </c>
-      <c r="D46" s="22">
+      <c r="D46" s="21">
         <v>136669978</v>
       </c>
       <c r="E46" s="17">
@@ -4782,13 +4925,13 @@
       <c r="F46" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="G46" s="93" t="s">
+      <c r="G46" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="H46" s="94" t="s">
+      <c r="H46" s="69" t="s">
         <v>136</v>
       </c>
-      <c r="I46" s="43">
+      <c r="I46" s="41">
         <v>46076</v>
       </c>
     </row>
@@ -4799,10 +4942,10 @@
       <c r="B47" s="7">
         <v>46063</v>
       </c>
-      <c r="C47" s="55">
+      <c r="C47" s="53">
         <v>46077</v>
       </c>
-      <c r="D47" s="22">
+      <c r="D47" s="21">
         <v>136689136</v>
       </c>
       <c r="E47" s="17">
@@ -4811,13 +4954,13 @@
       <c r="F47" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="G47" s="93" t="s">
+      <c r="G47" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="H47" s="94" t="s">
+      <c r="H47" s="69" t="s">
         <v>155</v>
       </c>
-      <c r="I47" s="43">
+      <c r="I47" s="41">
         <v>46076</v>
       </c>
     </row>
@@ -4828,10 +4971,10 @@
       <c r="B48" s="7">
         <v>46065</v>
       </c>
-      <c r="C48" s="55">
+      <c r="C48" s="53">
         <v>46077</v>
       </c>
-      <c r="D48" s="22">
+      <c r="D48" s="21">
         <v>136723546</v>
       </c>
       <c r="E48" s="17">
@@ -4840,13 +4983,13 @@
       <c r="F48" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="G48" s="93" t="s">
+      <c r="G48" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="H48" s="78" t="s">
+      <c r="H48" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="I48" s="43">
+      <c r="I48" s="41">
         <v>46077</v>
       </c>
     </row>
@@ -4857,10 +5000,10 @@
       <c r="B49" s="7">
         <v>46065</v>
       </c>
-      <c r="C49" s="55">
+      <c r="C49" s="53">
         <v>46077</v>
       </c>
-      <c r="D49" s="22">
+      <c r="D49" s="21">
         <v>136723669</v>
       </c>
       <c r="E49" s="17">
@@ -4869,13 +5012,13 @@
       <c r="F49" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="G49" s="93" t="s">
+      <c r="G49" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="H49" s="78" t="s">
+      <c r="H49" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="I49" s="43">
+      <c r="I49" s="41">
         <v>46065</v>
       </c>
     </row>
@@ -4886,10 +5029,10 @@
       <c r="B50" s="7">
         <v>46065</v>
       </c>
-      <c r="C50" s="55">
+      <c r="C50" s="53">
         <v>46077</v>
       </c>
-      <c r="D50" s="22">
+      <c r="D50" s="21">
         <v>136725436</v>
       </c>
       <c r="E50" s="17">
@@ -4898,13 +5041,13 @@
       <c r="F50" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="G50" s="93" t="s">
+      <c r="G50" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="H50" s="78" t="s">
+      <c r="H50" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="I50" s="43">
+      <c r="I50" s="41">
         <v>46065</v>
       </c>
     </row>
@@ -4915,10 +5058,10 @@
       <c r="B51" s="7">
         <v>46065</v>
       </c>
-      <c r="C51" s="55">
+      <c r="C51" s="53">
         <v>46077</v>
       </c>
-      <c r="D51" s="22">
+      <c r="D51" s="21">
         <v>136725702</v>
       </c>
       <c r="E51" s="17">
@@ -4927,13 +5070,13 @@
       <c r="F51" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="G51" s="93" t="s">
+      <c r="G51" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="H51" s="78" t="s">
+      <c r="H51" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="I51" s="43">
+      <c r="I51" s="41">
         <v>46065</v>
       </c>
     </row>
@@ -4944,10 +5087,10 @@
       <c r="B52" s="7">
         <v>46069</v>
       </c>
-      <c r="C52" s="55">
+      <c r="C52" s="53">
         <v>46077</v>
       </c>
-      <c r="D52" s="22">
+      <c r="D52" s="21">
         <v>136740470</v>
       </c>
       <c r="E52" s="17">
@@ -4956,13 +5099,13 @@
       <c r="F52" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="G52" s="93" t="s">
+      <c r="G52" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="H52" s="78" t="s">
+      <c r="H52" s="69" t="s">
         <v>161</v>
       </c>
-      <c r="I52" s="43">
+      <c r="I52" s="41">
         <v>46076</v>
       </c>
     </row>
@@ -4973,10 +5116,10 @@
       <c r="B53" s="7">
         <v>46073</v>
       </c>
-      <c r="C53" s="55">
+      <c r="C53" s="53">
         <v>46077</v>
       </c>
-      <c r="D53" s="22">
+      <c r="D53" s="21">
         <v>136823048</v>
       </c>
       <c r="E53" s="17">
@@ -4985,13 +5128,13 @@
       <c r="F53" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="G53" s="93" t="s">
+      <c r="G53" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="H53" s="78" t="s">
+      <c r="H53" s="69" t="s">
         <v>161</v>
       </c>
-      <c r="I53" s="43">
+      <c r="I53" s="41">
         <v>46076</v>
       </c>
     </row>
@@ -5002,10 +5145,10 @@
       <c r="B54" s="7">
         <v>46073</v>
       </c>
-      <c r="C54" s="55">
+      <c r="C54" s="53">
         <v>46077</v>
       </c>
-      <c r="D54" s="22">
+      <c r="D54" s="21">
         <v>136816299</v>
       </c>
       <c r="E54" s="17">
@@ -5014,13 +5157,13 @@
       <c r="F54" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="G54" s="93" t="s">
+      <c r="G54" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="H54" s="78" t="s">
+      <c r="H54" s="69" t="s">
         <v>161</v>
       </c>
-      <c r="I54" s="43">
+      <c r="I54" s="41">
         <v>46076</v>
       </c>
     </row>
@@ -5031,10 +5174,10 @@
       <c r="B55" s="7">
         <v>46078</v>
       </c>
-      <c r="C55" s="55">
+      <c r="C55" s="53">
         <v>46077</v>
       </c>
-      <c r="D55" s="22">
+      <c r="D55" s="21">
         <v>136825656</v>
       </c>
       <c r="E55" s="17">
@@ -5043,13 +5186,13 @@
       <c r="F55" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="G55" s="93" t="s">
+      <c r="G55" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="H55" s="78" t="s">
+      <c r="H55" s="69" t="s">
         <v>161</v>
       </c>
-      <c r="I55" s="43">
+      <c r="I55" s="41">
         <v>46076</v>
       </c>
     </row>
@@ -5060,10 +5203,10 @@
       <c r="B56" s="7">
         <v>46073</v>
       </c>
-      <c r="C56" s="55">
+      <c r="C56" s="53">
         <v>46077</v>
       </c>
-      <c r="D56" s="22">
+      <c r="D56" s="21">
         <v>136757414</v>
       </c>
       <c r="E56" s="17">
@@ -5072,13 +5215,13 @@
       <c r="F56" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="G56" s="93" t="s">
+      <c r="G56" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="H56" s="78" t="s">
+      <c r="H56" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="I56" s="43">
+      <c r="I56" s="41">
         <v>46073</v>
       </c>
     </row>
@@ -5089,10 +5232,10 @@
       <c r="B57" s="7">
         <v>46072</v>
       </c>
-      <c r="C57" s="55">
+      <c r="C57" s="53">
         <v>46077</v>
       </c>
-      <c r="D57" s="22">
+      <c r="D57" s="21">
         <v>136804031</v>
       </c>
       <c r="E57" s="17">
@@ -5101,13 +5244,13 @@
       <c r="F57" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="G57" s="93" t="s">
+      <c r="G57" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H57" s="94" t="s">
+      <c r="H57" s="69" t="s">
         <v>167</v>
       </c>
-      <c r="I57" s="43">
+      <c r="I57" s="41">
         <v>46077</v>
       </c>
     </row>
@@ -5131,17 +5274,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD26F43-5C8A-4C67-93F6-3B4E17ED8491}">
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="15.85546875" style="16" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" style="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" style="16" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" style="16" customWidth="1"/>
+    <col min="4" max="4" width="26" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.5703125" style="16" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="30.140625" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.5703125" customWidth="1"/>
-    <col min="9" max="9" width="21" style="24" customWidth="1"/>
+    <col min="9" max="9" width="21" style="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -5169,7 +5313,7 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="I1" s="26" t="s">
         <v>8</v>
       </c>
     </row>
@@ -5177,472 +5321,1016 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="43"/>
+      <c r="B2" s="57">
+        <v>46063</v>
+      </c>
+      <c r="C2" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D2" s="86">
+        <v>136739463</v>
+      </c>
+      <c r="E2" s="17">
+        <v>3450248000</v>
+      </c>
+      <c r="F2" s="85" t="s">
+        <v>168</v>
+      </c>
+      <c r="G2" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="41">
+        <v>46063</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="59"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="43"/>
+      <c r="B3" s="57">
+        <v>46087</v>
+      </c>
+      <c r="C3" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D3" s="86">
+        <v>136694861</v>
+      </c>
+      <c r="E3" s="17">
+        <v>3450248571</v>
+      </c>
+      <c r="F3" s="85" t="s">
+        <v>169</v>
+      </c>
+      <c r="G3" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="87" t="s">
+        <v>136</v>
+      </c>
+      <c r="I3" s="41">
+        <v>46077</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="43"/>
+      <c r="B4" s="57">
+        <v>46066</v>
+      </c>
+      <c r="C4" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D4" s="86">
+        <v>136754447</v>
+      </c>
+      <c r="E4" s="17">
+        <v>3450252740</v>
+      </c>
+      <c r="F4" s="85" t="s">
+        <v>170</v>
+      </c>
+      <c r="G4" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="87" t="s">
+        <v>171</v>
+      </c>
+      <c r="I4" s="41">
+        <v>46077</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="62"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="64"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="48"/>
+      <c r="B5" s="57">
+        <v>46076</v>
+      </c>
+      <c r="C5" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D5" s="86">
+        <v>136708451</v>
+      </c>
+      <c r="E5" s="17">
+        <v>3450249671</v>
+      </c>
+      <c r="F5" s="85" t="s">
+        <v>172</v>
+      </c>
+      <c r="G5" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="87" t="s">
+        <v>171</v>
+      </c>
+      <c r="I5" s="41">
+        <v>46073</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="59"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="43"/>
+      <c r="B6" s="88">
+        <v>46073</v>
+      </c>
+      <c r="C6" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D6" s="86">
+        <v>136698193</v>
+      </c>
+      <c r="E6" s="17">
+        <v>3450248824</v>
+      </c>
+      <c r="F6" s="85" t="s">
+        <v>173</v>
+      </c>
+      <c r="G6" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="87" t="s">
+        <v>136</v>
+      </c>
+      <c r="I6" s="41">
+        <v>46077</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="43"/>
+      <c r="B7" s="57">
+        <v>46091</v>
+      </c>
+      <c r="C7" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D7" s="86">
+        <v>136751455</v>
+      </c>
+      <c r="E7" s="17">
+        <v>3450252510</v>
+      </c>
+      <c r="F7" s="85" t="s">
+        <v>174</v>
+      </c>
+      <c r="G7" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="87" t="s">
+        <v>175</v>
+      </c>
+      <c r="I7" s="41">
+        <v>46077</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="59"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="43"/>
+      <c r="B8" s="57">
+        <v>46070</v>
+      </c>
+      <c r="C8" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D8" s="86">
+        <v>136742229</v>
+      </c>
+      <c r="E8" s="17">
+        <v>3450251728</v>
+      </c>
+      <c r="F8" s="85" t="s">
+        <v>176</v>
+      </c>
+      <c r="G8" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="87" t="s">
+        <v>177</v>
+      </c>
+      <c r="I8" s="41">
+        <v>46077</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="59"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="43"/>
+      <c r="B9" s="57">
+        <v>46063</v>
+      </c>
+      <c r="C9" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D9" s="86">
+        <v>136740126</v>
+      </c>
+      <c r="E9" s="17">
+        <v>3450247361</v>
+      </c>
+      <c r="F9" s="85" t="s">
+        <v>178</v>
+      </c>
+      <c r="G9" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="41">
+        <v>46063</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="59"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="61"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="43"/>
+      <c r="B10" s="57">
+        <v>46063</v>
+      </c>
+      <c r="C10" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D10" s="86">
+        <v>136740300</v>
+      </c>
+      <c r="E10" s="17">
+        <v>3450247240</v>
+      </c>
+      <c r="F10" s="85" t="s">
+        <v>179</v>
+      </c>
+      <c r="G10" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="41">
+        <v>46063</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="43"/>
+      <c r="B11" s="57">
+        <v>46066</v>
+      </c>
+      <c r="C11" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D11" s="86">
+        <v>136751006</v>
+      </c>
+      <c r="E11" s="17">
+        <v>3450252476</v>
+      </c>
+      <c r="F11" s="85" t="s">
+        <v>180</v>
+      </c>
+      <c r="G11" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="41">
+        <v>46066</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="59"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="61"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="43"/>
+      <c r="B12" s="57">
+        <v>46079</v>
+      </c>
+      <c r="C12" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D12" s="86">
+        <v>136755188</v>
+      </c>
+      <c r="E12" s="17">
+        <v>3450252850</v>
+      </c>
+      <c r="F12" s="85" t="s">
+        <v>181</v>
+      </c>
+      <c r="G12" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="89" t="s">
+        <v>182</v>
+      </c>
+      <c r="I12" s="41">
+        <v>46077</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="59"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="43"/>
+      <c r="B13" s="57">
+        <v>46077</v>
+      </c>
+      <c r="C13" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D13" s="86">
+        <v>136757699</v>
+      </c>
+      <c r="E13" s="17">
+        <v>3450253015</v>
+      </c>
+      <c r="F13" s="85" t="s">
+        <v>183</v>
+      </c>
+      <c r="G13" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I13" s="41">
+        <v>46078</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="59"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="43"/>
+      <c r="B14" s="57">
+        <v>46066</v>
+      </c>
+      <c r="C14" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D14" s="86">
+        <v>136762893</v>
+      </c>
+      <c r="E14" s="17">
+        <v>3450253477</v>
+      </c>
+      <c r="F14" s="85" t="s">
+        <v>185</v>
+      </c>
+      <c r="G14" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="41">
+        <v>46066</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="59"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="61"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="43"/>
+      <c r="B15" s="57">
+        <v>46064</v>
+      </c>
+      <c r="C15" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D15" s="86">
+        <v>136705225</v>
+      </c>
+      <c r="E15" s="17">
+        <v>3450249517</v>
+      </c>
+      <c r="F15" s="85" t="s">
+        <v>186</v>
+      </c>
+      <c r="G15" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="89" t="s">
+        <v>187</v>
+      </c>
+      <c r="I15" s="41">
+        <v>46077</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="59"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="43"/>
+      <c r="B16" s="57">
+        <v>46063</v>
+      </c>
+      <c r="C16" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D16" s="86">
+        <v>136739201</v>
+      </c>
+      <c r="E16" s="17">
+        <v>3450248384</v>
+      </c>
+      <c r="F16" s="85" t="s">
+        <v>188</v>
+      </c>
+      <c r="G16" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="41">
+        <v>46063</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="59"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="43"/>
+      <c r="B17" s="57">
+        <v>46063</v>
+      </c>
+      <c r="C17" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D17" s="86">
+        <v>136739218</v>
+      </c>
+      <c r="E17" s="17">
+        <v>3450248087</v>
+      </c>
+      <c r="F17" s="85" t="s">
+        <v>189</v>
+      </c>
+      <c r="G17" s="58" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="41">
+        <v>46063</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="43"/>
+      <c r="B18" s="57">
+        <v>46065</v>
+      </c>
+      <c r="C18" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D18" s="86">
+        <v>136723533</v>
+      </c>
+      <c r="E18" s="17">
+        <v>3450250276</v>
+      </c>
+      <c r="F18" s="85" t="s">
+        <v>174</v>
+      </c>
+      <c r="G18" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="I18" s="41">
+        <v>46077</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="43"/>
+      <c r="B19" s="57">
+        <v>46075</v>
+      </c>
+      <c r="C19" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D19" s="86">
+        <v>136806525</v>
+      </c>
+      <c r="E19" s="17">
+        <v>3450256030</v>
+      </c>
+      <c r="F19" s="85" t="s">
+        <v>190</v>
+      </c>
+      <c r="G19" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H19" s="87" t="s">
+        <v>191</v>
+      </c>
+      <c r="I19" s="41">
+        <v>46078</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="43"/>
+      <c r="B20" s="57">
+        <v>46072</v>
+      </c>
+      <c r="C20" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D20" s="86">
+        <v>136808710</v>
+      </c>
+      <c r="E20" s="17">
+        <v>3450256360</v>
+      </c>
+      <c r="F20" s="85" t="s">
+        <v>192</v>
+      </c>
+      <c r="G20" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" s="93" t="s">
+        <v>193</v>
+      </c>
+      <c r="I20" s="41">
+        <v>46078</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="61"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="43"/>
+      <c r="B21" s="57">
+        <v>46065</v>
+      </c>
+      <c r="C21" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D21" s="86">
+        <v>136730296</v>
+      </c>
+      <c r="E21" s="17">
+        <v>3450250980</v>
+      </c>
+      <c r="F21" s="85" t="s">
+        <v>194</v>
+      </c>
+      <c r="G21" s="90" t="s">
+        <v>11</v>
+      </c>
+      <c r="H21" s="87" t="s">
+        <v>195</v>
+      </c>
+      <c r="I21" s="92">
+        <v>46077</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="43"/>
+      <c r="B22" s="7">
+        <v>46076</v>
+      </c>
+      <c r="C22" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D22" s="86">
+        <v>136841851</v>
+      </c>
+      <c r="E22" s="17">
+        <v>3450258966</v>
+      </c>
+      <c r="F22" s="85" t="s">
+        <v>196</v>
+      </c>
+      <c r="G22" s="90" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="87" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" s="92">
+        <v>46076</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="67"/>
-      <c r="E23" s="56"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="68"/>
-      <c r="H23" s="14"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>46088</v>
+      </c>
+      <c r="C23" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D23" s="86">
+        <v>136832984</v>
+      </c>
+      <c r="E23" s="17">
+        <v>3450258438</v>
+      </c>
+      <c r="F23" s="85" t="s">
+        <v>197</v>
+      </c>
+      <c r="G23" s="90" t="s">
+        <v>11</v>
+      </c>
+      <c r="H23" s="87" t="s">
+        <v>198</v>
+      </c>
+      <c r="I23" s="92">
+        <v>46078</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="9"/>
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>46074</v>
+      </c>
+      <c r="C24" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D24" s="86">
+        <v>136809532</v>
+      </c>
+      <c r="E24" s="17">
+        <v>3450256458</v>
+      </c>
+      <c r="F24" s="85" t="s">
+        <v>199</v>
+      </c>
+      <c r="G24" s="90" t="s">
+        <v>11</v>
+      </c>
+      <c r="H24" s="87" t="s">
+        <v>200</v>
+      </c>
+      <c r="I24" s="92">
+        <v>46078</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="9"/>
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>46072</v>
+      </c>
+      <c r="C25" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D25" s="86">
+        <v>136798798</v>
+      </c>
+      <c r="E25" s="17">
+        <v>3450255270</v>
+      </c>
+      <c r="F25" s="85" t="s">
+        <v>201</v>
+      </c>
+      <c r="G25" s="91" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" s="87" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="92">
+        <v>46072</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="9"/>
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>46073</v>
+      </c>
+      <c r="C26" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D26" s="86">
+        <v>136821098</v>
+      </c>
+      <c r="E26" s="17">
+        <v>3450257305</v>
+      </c>
+      <c r="F26" s="85" t="s">
+        <v>202</v>
+      </c>
+      <c r="G26" s="90" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" s="87" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="92">
+        <v>46073</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="9"/>
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="7">
+        <v>46071</v>
+      </c>
+      <c r="C27" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D27" s="86">
+        <v>136786742</v>
+      </c>
+      <c r="E27" s="17">
+        <v>3450254478</v>
+      </c>
+      <c r="F27" s="85" t="s">
+        <v>203</v>
+      </c>
+      <c r="G27" s="90" t="s">
+        <v>74</v>
+      </c>
+      <c r="H27" s="87" t="s">
+        <v>204</v>
+      </c>
+      <c r="I27" s="92">
+        <v>46071</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="9"/>
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="7">
+        <v>46071</v>
+      </c>
+      <c r="C28" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D28" s="86">
+        <v>136784554</v>
+      </c>
+      <c r="E28" s="17">
+        <v>3450254269</v>
+      </c>
+      <c r="F28" s="85" t="s">
+        <v>205</v>
+      </c>
+      <c r="G28" s="90" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28" s="87" t="s">
+        <v>15</v>
+      </c>
+      <c r="I28" s="92">
+        <v>46071</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="9"/>
+      <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="7">
+        <v>46072</v>
+      </c>
+      <c r="C29" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D29" s="86">
+        <v>136799830</v>
+      </c>
+      <c r="E29" s="17">
+        <v>3450255435</v>
+      </c>
+      <c r="F29" s="85" t="s">
+        <v>206</v>
+      </c>
+      <c r="G29" s="91" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I29" s="92">
+        <v>46072</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="9"/>
+      <c r="A30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="7">
+        <v>46072</v>
+      </c>
+      <c r="C30" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D30" s="86">
+        <v>136803511</v>
+      </c>
+      <c r="E30" s="17">
+        <v>3450255765</v>
+      </c>
+      <c r="F30" s="85" t="s">
+        <v>207</v>
+      </c>
+      <c r="G30" s="91" t="s">
+        <v>14</v>
+      </c>
+      <c r="H30" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I30" s="92">
+        <v>46072</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="9"/>
+      <c r="A31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="7">
+        <v>46071</v>
+      </c>
+      <c r="C31" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D31" s="86">
+        <v>136784744</v>
+      </c>
+      <c r="E31" s="17">
+        <v>3450254270</v>
+      </c>
+      <c r="F31" s="85" t="s">
+        <v>208</v>
+      </c>
+      <c r="G31" s="58" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="I31" s="41">
+        <v>46071</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="9"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="6"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="9"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="6"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="9"/>
-    </row>
-    <row r="36" spans="1:8">
+      <c r="A32" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="7">
+        <v>46066</v>
+      </c>
+      <c r="C32" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D32" s="86">
+        <v>136798825</v>
+      </c>
+      <c r="E32" s="17">
+        <v>3450251838</v>
+      </c>
+      <c r="F32" s="85" t="s">
+        <v>209</v>
+      </c>
+      <c r="G32" s="58" t="s">
+        <v>14</v>
+      </c>
+      <c r="H32" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" s="41">
+        <v>46066</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="7">
+        <v>46072</v>
+      </c>
+      <c r="C33" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D33" s="86">
+        <v>136791856</v>
+      </c>
+      <c r="E33" s="17">
+        <v>3450254731</v>
+      </c>
+      <c r="F33" s="85" t="s">
+        <v>210</v>
+      </c>
+      <c r="G33" s="58" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" s="41">
+        <v>46072</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="7">
+        <v>46072</v>
+      </c>
+      <c r="C34" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D34" s="86">
+        <v>136795898</v>
+      </c>
+      <c r="E34" s="17">
+        <v>3450254951</v>
+      </c>
+      <c r="F34" s="85" t="s">
+        <v>211</v>
+      </c>
+      <c r="G34" s="58" t="s">
+        <v>14</v>
+      </c>
+      <c r="H34" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="41">
+        <v>46072</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="7">
+        <v>46072</v>
+      </c>
+      <c r="C35" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D35" s="86">
+        <v>136801483</v>
+      </c>
+      <c r="E35" s="17">
+        <v>3450255589</v>
+      </c>
+      <c r="F35" s="85" t="s">
+        <v>212</v>
+      </c>
+      <c r="G35" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="H35" s="87" t="s">
+        <v>27</v>
+      </c>
+      <c r="I35" s="41">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" s="6"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="9"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="6"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="9"/>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="6"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="9"/>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="6"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="9"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="6"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="9"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="58"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="41"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="3">
+    <cfRule type="notContainsBlanks" priority="4">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A23:A33" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A36" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G33" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B5 B7:B21" xr:uid="{7AD82A11-4EC7-4EF9-95FB-52EC6839A0E7}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G36" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A22" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A35" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B17" xr:uid="{7AD82A11-4EC7-4EF9-95FB-52EC6839A0E7}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5697,40 +6385,40 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="26"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="24"/>
       <c r="E2" s="8"/>
       <c r="F2" s="11"/>
-      <c r="G2" s="27"/>
+      <c r="G2" s="25"/>
       <c r="H2" s="9"/>
-      <c r="I2" s="24"/>
+      <c r="I2" s="22"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="26"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="24"/>
       <c r="E3" s="8"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="27"/>
+      <c r="G3" s="25"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="24"/>
+      <c r="I3" s="22"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="26"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="24"/>
       <c r="E4" s="8"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="27"/>
+      <c r="G4" s="25"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="24"/>
+      <c r="I4" s="22"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
@@ -5738,12 +6426,12 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
-      <c r="D5" s="26"/>
+      <c r="D5" s="24"/>
       <c r="E5" s="8"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="27"/>
+      <c r="G5" s="25"/>
       <c r="H5" s="9"/>
-      <c r="I5" s="24"/>
+      <c r="I5" s="22"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
@@ -5751,12 +6439,12 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="26"/>
+      <c r="D6" s="24"/>
       <c r="E6" s="8"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="27"/>
+      <c r="G6" s="25"/>
       <c r="H6" s="9"/>
-      <c r="I6" s="24"/>
+      <c r="I6" s="22"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
@@ -5764,12 +6452,12 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
-      <c r="D7" s="26"/>
+      <c r="D7" s="24"/>
       <c r="E7" s="8"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="27"/>
+      <c r="G7" s="25"/>
       <c r="H7" s="9"/>
-      <c r="I7" s="24"/>
+      <c r="I7" s="22"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
@@ -5777,12 +6465,12 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
-      <c r="D8" s="26"/>
+      <c r="D8" s="24"/>
       <c r="E8" s="8"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="27"/>
+      <c r="G8" s="25"/>
       <c r="H8" s="9"/>
-      <c r="I8" s="24"/>
+      <c r="I8" s="22"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
@@ -5790,12 +6478,12 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="26"/>
+      <c r="D9" s="24"/>
       <c r="E9" s="8"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="27"/>
+      <c r="G9" s="25"/>
       <c r="H9" s="9"/>
-      <c r="I9" s="24"/>
+      <c r="I9" s="22"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
@@ -5803,12 +6491,12 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="26"/>
+      <c r="D10" s="24"/>
       <c r="E10" s="8"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="27"/>
+      <c r="G10" s="25"/>
       <c r="H10" s="9"/>
-      <c r="I10" s="24"/>
+      <c r="I10" s="22"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
@@ -5816,12 +6504,12 @@
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
-      <c r="D11" s="26"/>
+      <c r="D11" s="24"/>
       <c r="E11" s="8"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="27"/>
+      <c r="G11" s="25"/>
       <c r="H11" s="9"/>
-      <c r="I11" s="24"/>
+      <c r="I11" s="22"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
@@ -5829,12 +6517,12 @@
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
-      <c r="D12" s="26"/>
+      <c r="D12" s="24"/>
       <c r="E12" s="8"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="27"/>
+      <c r="G12" s="25"/>
       <c r="H12" s="9"/>
-      <c r="I12" s="24"/>
+      <c r="I12" s="22"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
@@ -5842,12 +6530,12 @@
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
-      <c r="D13" s="26"/>
+      <c r="D13" s="24"/>
       <c r="E13" s="8"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="27"/>
+      <c r="G13" s="25"/>
       <c r="H13" s="9"/>
-      <c r="I13" s="24"/>
+      <c r="I13" s="22"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
@@ -5855,12 +6543,12 @@
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="26"/>
+      <c r="D14" s="24"/>
       <c r="E14" s="8"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="27"/>
+      <c r="G14" s="25"/>
       <c r="H14" s="9"/>
-      <c r="I14" s="24"/>
+      <c r="I14" s="22"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
@@ -5868,23 +6556,23 @@
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
-      <c r="D15" s="26"/>
+      <c r="D15" s="24"/>
       <c r="E15" s="8"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="27"/>
+      <c r="G15" s="25"/>
       <c r="H15" s="9"/>
-      <c r="I15" s="24"/>
+      <c r="I15" s="22"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="26"/>
+      <c r="D16" s="24"/>
       <c r="E16" s="8"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="27"/>
+      <c r="G16" s="25"/>
       <c r="H16" s="9"/>
-      <c r="I16" s="24"/>
+      <c r="I16" s="22"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6"/>
@@ -5895,7 +6583,7 @@
       <c r="F17" s="11"/>
       <c r="G17" s="6"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="24"/>
+      <c r="I17" s="22"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6"/>
@@ -5906,7 +6594,7 @@
       <c r="F18" s="11"/>
       <c r="G18" s="6"/>
       <c r="H18" s="9"/>
-      <c r="I18" s="24"/>
+      <c r="I18" s="22"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
@@ -5917,7 +6605,7 @@
       <c r="F19" s="12"/>
       <c r="G19" s="6"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="24"/>
+      <c r="I19" s="22"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -5928,7 +6616,7 @@
       <c r="F20" s="14"/>
       <c r="G20" s="6"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="24"/>
+      <c r="I20" s="22"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -6347,63 +7035,63 @@
         <v>9</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="22"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="17"/>
       <c r="F2" s="11"/>
       <c r="G2" s="19"/>
       <c r="H2" s="9"/>
-      <c r="I2" s="24"/>
+      <c r="I2" s="22"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="22"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="17"/>
       <c r="F3" s="11"/>
       <c r="G3" s="19"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="33"/>
+      <c r="I3" s="31"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="22"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="21"/>
       <c r="E4" s="17"/>
       <c r="F4" s="11"/>
       <c r="G4" s="19"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="24"/>
+      <c r="I4" s="22"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="22"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="17"/>
       <c r="F5" s="11"/>
       <c r="G5" s="19"/>
       <c r="H5" s="9"/>
-      <c r="I5" s="24"/>
+      <c r="I5" s="22"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="20"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="31"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="29"/>
       <c r="G6" s="6"/>
       <c r="H6" s="9"/>
-      <c r="I6" s="24"/>
+      <c r="I6" s="22"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6"/>
@@ -6930,7 +7618,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="39" t="s">
+      <c r="H1" s="37" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -6942,232 +7630,232 @@
         <v>9</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="22"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="17"/>
       <c r="F2" s="18"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="24"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="22"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="22"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="17"/>
       <c r="F3" s="18"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="24"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="22"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="22"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="21"/>
       <c r="E4" s="17"/>
       <c r="F4" s="18"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="24"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="22"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="22"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="17"/>
       <c r="F5" s="18"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="24"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="22"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="7"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="22"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="21"/>
       <c r="E6" s="17"/>
       <c r="F6" s="18"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="24"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="22"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="22"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="21"/>
       <c r="E7" s="17"/>
       <c r="F7" s="18"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="24"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="22"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="22"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="21"/>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="24"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="22"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="7"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="22"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="21"/>
       <c r="E9" s="17"/>
       <c r="F9" s="18"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="24"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="22"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="7"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="22"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="17"/>
       <c r="F10" s="18"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="24"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="22"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="7"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="22"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="21"/>
       <c r="E11" s="17"/>
       <c r="F11" s="18"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="24"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="22"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="7"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="22"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="21"/>
       <c r="E12" s="17"/>
       <c r="F12" s="18"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="24"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="22"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="7"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="22"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="21"/>
       <c r="E13" s="17"/>
       <c r="F13" s="18"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="24"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="22"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="7"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="22"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="21"/>
       <c r="E14" s="17"/>
       <c r="F14" s="18"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="24"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="22"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="7"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="22"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="21"/>
       <c r="E15" s="17"/>
       <c r="F15" s="18"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="24"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="22"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="7"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="22"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="21"/>
       <c r="E16" s="17"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="24"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="22"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="25" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="7"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="22"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="21"/>
       <c r="E17" s="17"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="24"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="22"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B18" s="7"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="22"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="21"/>
       <c r="E18" s="17"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="24"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="22"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
       <c r="B19" s="8"/>
       <c r="C19" s="7"/>
       <c r="D19" s="20"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="29"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="27"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="24"/>
+      <c r="I19" s="22"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -7176,9 +7864,9 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="14"/>
-      <c r="G20" s="29"/>
+      <c r="G20" s="27"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="24"/>
+      <c r="I20" s="22"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -7187,9 +7875,9 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="29"/>
+      <c r="G21" s="27"/>
       <c r="H21" s="9"/>
-      <c r="I21" s="24"/>
+      <c r="I21" s="22"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6"/>
@@ -7198,9 +7886,9 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
-      <c r="G22" s="29"/>
+      <c r="G22" s="27"/>
       <c r="H22" s="9"/>
-      <c r="I22" s="24"/>
+      <c r="I22" s="22"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6"/>
@@ -7209,9 +7897,9 @@
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
-      <c r="G23" s="29"/>
+      <c r="G23" s="27"/>
       <c r="H23" s="9"/>
-      <c r="I23" s="24"/>
+      <c r="I23" s="22"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6"/>
@@ -7220,9 +7908,9 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
-      <c r="G24" s="29"/>
+      <c r="G24" s="27"/>
       <c r="H24" s="9"/>
-      <c r="I24" s="24"/>
+      <c r="I24" s="22"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
@@ -7233,7 +7921,7 @@
       <c r="F25" s="9"/>
       <c r="G25" s="6"/>
       <c r="H25" s="9"/>
-      <c r="I25" s="24"/>
+      <c r="I25" s="22"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
@@ -7244,7 +7932,7 @@
       <c r="F26" s="9"/>
       <c r="G26" s="6"/>
       <c r="H26" s="9"/>
-      <c r="I26" s="24"/>
+      <c r="I26" s="22"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
@@ -7255,7 +7943,7 @@
       <c r="F27" s="9"/>
       <c r="G27" s="6"/>
       <c r="H27" s="9"/>
-      <c r="I27" s="24"/>
+      <c r="I27" s="22"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6"/>
@@ -7266,7 +7954,7 @@
       <c r="F28" s="9"/>
       <c r="G28" s="6"/>
       <c r="H28" s="9"/>
-      <c r="I28" s="24"/>
+      <c r="I28" s="22"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
@@ -7277,7 +7965,7 @@
       <c r="F29" s="9"/>
       <c r="G29" s="6"/>
       <c r="H29" s="9"/>
-      <c r="I29" s="24"/>
+      <c r="I29" s="22"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
@@ -7288,7 +7976,7 @@
       <c r="F30" s="9"/>
       <c r="G30" s="6"/>
       <c r="H30" s="9"/>
-      <c r="I30" s="24"/>
+      <c r="I30" s="22"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
@@ -7299,7 +7987,7 @@
       <c r="F31" s="9"/>
       <c r="G31" s="6"/>
       <c r="H31" s="9"/>
-      <c r="I31" s="24"/>
+      <c r="I31" s="22"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
@@ -7310,7 +7998,7 @@
       <c r="F32" s="9"/>
       <c r="G32" s="6"/>
       <c r="H32" s="9"/>
-      <c r="I32" s="24"/>
+      <c r="I32" s="22"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
@@ -7321,7 +8009,7 @@
       <c r="F33" s="9"/>
       <c r="G33" s="6"/>
       <c r="H33" s="9"/>
-      <c r="I33" s="24"/>
+      <c r="I33" s="22"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="6"/>
@@ -7332,7 +8020,7 @@
       <c r="F34" s="9"/>
       <c r="G34" s="6"/>
       <c r="H34" s="9"/>
-      <c r="I34" s="24"/>
+      <c r="I34" s="22"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
@@ -7343,7 +8031,7 @@
       <c r="F35" s="9"/>
       <c r="G35" s="6"/>
       <c r="H35" s="9"/>
-      <c r="I35" s="24"/>
+      <c r="I35" s="22"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
@@ -7600,923 +8288,923 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="52" t="s">
+      <c r="D1" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="52" t="s">
+      <c r="E1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="G1" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="74" t="s">
+      <c r="H1" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="50" t="s">
+      <c r="I1" s="48" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="22"/>
+      <c r="A2" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="17"/>
       <c r="F2" s="11"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="58"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="56"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="71"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="22"/>
+      <c r="A3" s="62"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="17"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="58"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="56"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="71"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="22"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="21"/>
       <c r="E4" s="17"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="58"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="56"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="71"/>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="22"/>
+      <c r="A5" s="62"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="17"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="58"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="56"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="71"/>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="22"/>
+      <c r="A6" s="62"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="21"/>
       <c r="E6" s="17"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="75"/>
-      <c r="I6" s="58"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="56"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="71"/>
-      <c r="B7" s="43"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="22"/>
+      <c r="A7" s="62"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="21"/>
       <c r="E7" s="17"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="75"/>
-      <c r="I7" s="58"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="56"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="71"/>
-      <c r="B8" s="43"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="22"/>
+      <c r="A8" s="62"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="21"/>
       <c r="E8" s="17"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="75"/>
-      <c r="I8" s="58"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="56"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="71"/>
-      <c r="B9" s="43"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="22"/>
+      <c r="A9" s="62"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="21"/>
       <c r="E9" s="17"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="75"/>
-      <c r="I9" s="58"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="66"/>
+      <c r="I9" s="56"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="71"/>
-      <c r="B10" s="43"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="22"/>
+      <c r="A10" s="62"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="17"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="75"/>
-      <c r="I10" s="58"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="56"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="71"/>
-      <c r="B11" s="43"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="22"/>
+      <c r="A11" s="62"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="21"/>
       <c r="E11" s="17"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="75"/>
-      <c r="I11" s="58"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="66"/>
+      <c r="I11" s="56"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="71"/>
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="22"/>
+      <c r="A12" s="62"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="21"/>
       <c r="E12" s="17"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="75"/>
-      <c r="I12" s="58"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="66"/>
+      <c r="I12" s="56"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="71"/>
-      <c r="B13" s="43"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="22"/>
+      <c r="A13" s="62"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="21"/>
       <c r="E13" s="17"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="75"/>
-      <c r="I13" s="58"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="66"/>
+      <c r="I13" s="56"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="71"/>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="22"/>
+      <c r="A14" s="62"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="21"/>
       <c r="E14" s="17"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="75"/>
-      <c r="I14" s="58"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="56"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="71"/>
-      <c r="B15" s="43"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="22"/>
+      <c r="A15" s="62"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="21"/>
       <c r="E15" s="17"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="75"/>
-      <c r="I15" s="58"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="66"/>
+      <c r="I15" s="56"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="71"/>
-      <c r="B16" s="43"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="22"/>
+      <c r="A16" s="62"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="21"/>
       <c r="E16" s="17"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="75"/>
-      <c r="I16" s="58"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="66"/>
+      <c r="I16" s="56"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="71"/>
-      <c r="B17" s="43"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="22"/>
+      <c r="A17" s="62"/>
+      <c r="B17" s="41"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="21"/>
       <c r="E17" s="17"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="75"/>
-      <c r="I17" s="58"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="66"/>
+      <c r="I17" s="56"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="71"/>
-      <c r="B18" s="43"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="22"/>
+      <c r="A18" s="62"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="21"/>
       <c r="E18" s="17"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="75"/>
-      <c r="I18" s="58"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="66"/>
+      <c r="I18" s="56"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="71"/>
-      <c r="B19" s="43"/>
-      <c r="C19" s="43"/>
-      <c r="D19" s="22"/>
+      <c r="A19" s="62"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="21"/>
       <c r="E19" s="17"/>
       <c r="F19" s="11"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="75"/>
-      <c r="I19" s="58"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="66"/>
+      <c r="I19" s="56"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="71"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="43"/>
-      <c r="D20" s="22"/>
+      <c r="A20" s="62"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="21"/>
       <c r="E20" s="17"/>
       <c r="F20" s="11"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="75"/>
-      <c r="I20" s="58"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="66"/>
+      <c r="I20" s="56"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="71"/>
-      <c r="B21" s="43"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="22"/>
+      <c r="A21" s="62"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="21"/>
       <c r="E21" s="17"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="75"/>
-      <c r="I21" s="58"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="66"/>
+      <c r="I21" s="56"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="71"/>
-      <c r="B22" s="43"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="22"/>
+      <c r="A22" s="62"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="21"/>
       <c r="E22" s="17"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="75"/>
-      <c r="I22" s="58"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="66"/>
+      <c r="I22" s="56"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="71"/>
-      <c r="B23" s="43"/>
-      <c r="C23" s="43"/>
-      <c r="D23" s="22"/>
+      <c r="A23" s="62"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="21"/>
       <c r="E23" s="17"/>
       <c r="F23" s="11"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="75"/>
-      <c r="I23" s="58"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="66"/>
+      <c r="I23" s="56"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="71"/>
-      <c r="B24" s="43"/>
-      <c r="C24" s="43"/>
-      <c r="D24" s="22"/>
+      <c r="A24" s="62"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="21"/>
       <c r="E24" s="17"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="42"/>
-      <c r="H24" s="75"/>
-      <c r="I24" s="58"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="66"/>
+      <c r="I24" s="56"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="71"/>
-      <c r="B25" s="43"/>
-      <c r="C25" s="43"/>
-      <c r="D25" s="22"/>
+      <c r="A25" s="62"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="21"/>
       <c r="E25" s="17"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="75"/>
-      <c r="I25" s="58"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="66"/>
+      <c r="I25" s="56"/>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="71"/>
-      <c r="B26" s="43"/>
-      <c r="C26" s="43"/>
-      <c r="D26" s="22"/>
+      <c r="A26" s="62"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="21"/>
       <c r="E26" s="17"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="75"/>
-      <c r="I26" s="58"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="66"/>
+      <c r="I26" s="56"/>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="71"/>
-      <c r="B27" s="43"/>
-      <c r="C27" s="43"/>
-      <c r="D27" s="22"/>
+      <c r="A27" s="62"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="21"/>
       <c r="E27" s="17"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="75"/>
-      <c r="I27" s="58"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="66"/>
+      <c r="I27" s="56"/>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="71"/>
-      <c r="B28" s="43"/>
-      <c r="C28" s="43"/>
-      <c r="D28" s="22"/>
+      <c r="A28" s="62"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="21"/>
       <c r="E28" s="17"/>
       <c r="F28" s="11"/>
-      <c r="G28" s="42"/>
-      <c r="H28" s="75"/>
-      <c r="I28" s="58"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="66"/>
+      <c r="I28" s="56"/>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="71"/>
-      <c r="B29" s="43"/>
-      <c r="C29" s="43"/>
-      <c r="D29" s="22"/>
+      <c r="A29" s="62"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="21"/>
       <c r="E29" s="17"/>
       <c r="F29" s="11"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="75"/>
-      <c r="I29" s="58"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="66"/>
+      <c r="I29" s="56"/>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="71"/>
-      <c r="B30" s="43"/>
-      <c r="C30" s="43"/>
-      <c r="D30" s="22"/>
+      <c r="A30" s="62"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="21"/>
       <c r="E30" s="17"/>
       <c r="F30" s="11"/>
-      <c r="G30" s="42"/>
-      <c r="H30" s="75"/>
-      <c r="I30" s="58"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="66"/>
+      <c r="I30" s="56"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="71"/>
-      <c r="B31" s="43"/>
-      <c r="C31" s="43"/>
-      <c r="D31" s="22"/>
+      <c r="A31" s="62"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="21"/>
       <c r="E31" s="17"/>
       <c r="F31" s="11"/>
-      <c r="G31" s="42"/>
-      <c r="H31" s="75"/>
-      <c r="I31" s="58"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="66"/>
+      <c r="I31" s="56"/>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="71"/>
-      <c r="B32" s="43"/>
-      <c r="C32" s="43"/>
-      <c r="D32" s="22"/>
+      <c r="A32" s="62"/>
+      <c r="B32" s="41"/>
+      <c r="C32" s="41"/>
+      <c r="D32" s="21"/>
       <c r="E32" s="17"/>
       <c r="F32" s="11"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="75"/>
-      <c r="I32" s="58"/>
+      <c r="G32" s="40"/>
+      <c r="H32" s="66"/>
+      <c r="I32" s="56"/>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="71"/>
-      <c r="B33" s="43"/>
-      <c r="C33" s="43"/>
-      <c r="D33" s="22"/>
+      <c r="A33" s="62"/>
+      <c r="B33" s="41"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="21"/>
       <c r="E33" s="17"/>
       <c r="F33" s="11"/>
-      <c r="G33" s="42"/>
-      <c r="H33" s="75"/>
-      <c r="I33" s="58"/>
+      <c r="G33" s="40"/>
+      <c r="H33" s="66"/>
+      <c r="I33" s="56"/>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="71"/>
-      <c r="B34" s="43"/>
-      <c r="C34" s="43"/>
-      <c r="D34" s="22"/>
+      <c r="A34" s="62"/>
+      <c r="B34" s="41"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="21"/>
       <c r="E34" s="17"/>
       <c r="F34" s="11"/>
-      <c r="G34" s="42"/>
-      <c r="H34" s="75"/>
-      <c r="I34" s="58"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="66"/>
+      <c r="I34" s="56"/>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="71"/>
-      <c r="B35" s="43"/>
-      <c r="C35" s="43"/>
-      <c r="D35" s="22"/>
+      <c r="A35" s="62"/>
+      <c r="B35" s="41"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="21"/>
       <c r="E35" s="17"/>
       <c r="F35" s="11"/>
-      <c r="G35" s="42"/>
-      <c r="H35" s="75"/>
-      <c r="I35" s="58"/>
+      <c r="G35" s="40"/>
+      <c r="H35" s="66"/>
+      <c r="I35" s="56"/>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="71"/>
-      <c r="B36" s="43"/>
-      <c r="C36" s="43"/>
-      <c r="D36" s="22"/>
+      <c r="A36" s="62"/>
+      <c r="B36" s="41"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="21"/>
       <c r="E36" s="17"/>
       <c r="F36" s="11"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="75"/>
-      <c r="I36" s="58"/>
+      <c r="G36" s="40"/>
+      <c r="H36" s="66"/>
+      <c r="I36" s="56"/>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" s="71"/>
-      <c r="B37" s="43"/>
-      <c r="C37" s="43"/>
-      <c r="D37" s="22"/>
+      <c r="A37" s="62"/>
+      <c r="B37" s="41"/>
+      <c r="C37" s="41"/>
+      <c r="D37" s="21"/>
       <c r="E37" s="17"/>
       <c r="F37" s="11"/>
-      <c r="G37" s="42"/>
-      <c r="H37" s="75"/>
-      <c r="I37" s="58"/>
+      <c r="G37" s="40"/>
+      <c r="H37" s="66"/>
+      <c r="I37" s="56"/>
     </row>
     <row r="38" spans="1:9">
-      <c r="A38" s="71"/>
-      <c r="B38" s="43"/>
-      <c r="C38" s="43"/>
-      <c r="D38" s="22"/>
+      <c r="A38" s="62"/>
+      <c r="B38" s="41"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="21"/>
       <c r="E38" s="17"/>
       <c r="F38" s="11"/>
-      <c r="G38" s="42"/>
-      <c r="H38" s="75"/>
-      <c r="I38" s="58"/>
+      <c r="G38" s="40"/>
+      <c r="H38" s="66"/>
+      <c r="I38" s="56"/>
     </row>
     <row r="39" spans="1:9">
-      <c r="A39" s="71"/>
-      <c r="B39" s="43"/>
-      <c r="C39" s="43"/>
-      <c r="D39" s="22"/>
+      <c r="A39" s="62"/>
+      <c r="B39" s="41"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="21"/>
       <c r="E39" s="17"/>
       <c r="F39" s="11"/>
-      <c r="G39" s="42"/>
-      <c r="H39" s="75"/>
-      <c r="I39" s="58"/>
+      <c r="G39" s="40"/>
+      <c r="H39" s="66"/>
+      <c r="I39" s="56"/>
     </row>
     <row r="40" spans="1:9">
-      <c r="A40" s="71"/>
-      <c r="B40" s="43"/>
-      <c r="C40" s="43"/>
-      <c r="D40" s="22"/>
+      <c r="A40" s="62"/>
+      <c r="B40" s="41"/>
+      <c r="C40" s="41"/>
+      <c r="D40" s="21"/>
       <c r="E40" s="17"/>
       <c r="F40" s="11"/>
-      <c r="G40" s="42"/>
-      <c r="H40" s="75"/>
-      <c r="I40" s="58"/>
+      <c r="G40" s="40"/>
+      <c r="H40" s="66"/>
+      <c r="I40" s="56"/>
     </row>
     <row r="41" spans="1:9">
-      <c r="A41" s="71"/>
-      <c r="B41" s="43"/>
-      <c r="C41" s="43"/>
-      <c r="D41" s="22"/>
+      <c r="A41" s="62"/>
+      <c r="B41" s="41"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="21"/>
       <c r="E41" s="17"/>
       <c r="F41" s="11"/>
-      <c r="G41" s="42"/>
-      <c r="H41" s="75"/>
-      <c r="I41" s="58"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="66"/>
+      <c r="I41" s="56"/>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="71"/>
-      <c r="B42" s="43"/>
-      <c r="C42" s="43"/>
-      <c r="D42" s="22"/>
+      <c r="A42" s="62"/>
+      <c r="B42" s="41"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="21"/>
       <c r="E42" s="17"/>
       <c r="F42" s="11"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="75"/>
-      <c r="I42" s="58"/>
+      <c r="G42" s="40"/>
+      <c r="H42" s="66"/>
+      <c r="I42" s="56"/>
     </row>
     <row r="43" spans="1:9">
-      <c r="A43" s="71"/>
-      <c r="B43" s="43"/>
-      <c r="C43" s="43"/>
-      <c r="D43" s="22"/>
+      <c r="A43" s="62"/>
+      <c r="B43" s="41"/>
+      <c r="C43" s="41"/>
+      <c r="D43" s="21"/>
       <c r="E43" s="17"/>
       <c r="F43" s="11"/>
-      <c r="G43" s="42"/>
-      <c r="H43" s="75"/>
-      <c r="I43" s="58"/>
+      <c r="G43" s="40"/>
+      <c r="H43" s="66"/>
+      <c r="I43" s="56"/>
     </row>
     <row r="44" spans="1:9">
-      <c r="A44" s="71"/>
-      <c r="B44" s="43"/>
-      <c r="C44" s="43"/>
-      <c r="D44" s="22"/>
+      <c r="A44" s="62"/>
+      <c r="B44" s="41"/>
+      <c r="C44" s="41"/>
+      <c r="D44" s="21"/>
       <c r="E44" s="17"/>
       <c r="F44" s="11"/>
-      <c r="G44" s="42"/>
-      <c r="H44" s="75"/>
-      <c r="I44" s="58"/>
+      <c r="G44" s="40"/>
+      <c r="H44" s="66"/>
+      <c r="I44" s="56"/>
     </row>
     <row r="45" spans="1:9">
-      <c r="A45" s="71"/>
-      <c r="B45" s="43"/>
-      <c r="C45" s="43"/>
-      <c r="D45" s="22"/>
+      <c r="A45" s="62"/>
+      <c r="B45" s="41"/>
+      <c r="C45" s="41"/>
+      <c r="D45" s="21"/>
       <c r="E45" s="17"/>
       <c r="F45" s="11"/>
-      <c r="G45" s="42"/>
-      <c r="H45" s="75"/>
-      <c r="I45" s="58"/>
+      <c r="G45" s="40"/>
+      <c r="H45" s="66"/>
+      <c r="I45" s="56"/>
     </row>
     <row r="46" spans="1:9">
-      <c r="A46" s="71"/>
-      <c r="B46" s="43"/>
-      <c r="C46" s="43"/>
-      <c r="D46" s="22"/>
+      <c r="A46" s="62"/>
+      <c r="B46" s="41"/>
+      <c r="C46" s="41"/>
+      <c r="D46" s="21"/>
       <c r="E46" s="17"/>
       <c r="F46" s="11"/>
-      <c r="G46" s="42"/>
-      <c r="H46" s="75"/>
-      <c r="I46" s="58"/>
+      <c r="G46" s="40"/>
+      <c r="H46" s="66"/>
+      <c r="I46" s="56"/>
     </row>
     <row r="47" spans="1:9">
-      <c r="A47" s="71"/>
-      <c r="B47" s="43"/>
-      <c r="C47" s="43"/>
-      <c r="D47" s="22"/>
+      <c r="A47" s="62"/>
+      <c r="B47" s="41"/>
+      <c r="C47" s="41"/>
+      <c r="D47" s="21"/>
       <c r="E47" s="17"/>
       <c r="F47" s="11"/>
-      <c r="G47" s="42"/>
-      <c r="H47" s="75"/>
-      <c r="I47" s="58"/>
+      <c r="G47" s="40"/>
+      <c r="H47" s="66"/>
+      <c r="I47" s="56"/>
     </row>
     <row r="48" spans="1:9">
-      <c r="A48" s="71"/>
-      <c r="B48" s="43"/>
-      <c r="C48" s="43"/>
-      <c r="D48" s="22"/>
+      <c r="A48" s="62"/>
+      <c r="B48" s="41"/>
+      <c r="C48" s="41"/>
+      <c r="D48" s="21"/>
       <c r="E48" s="17"/>
       <c r="F48" s="11"/>
-      <c r="G48" s="42"/>
-      <c r="H48" s="75"/>
-      <c r="I48" s="58"/>
+      <c r="G48" s="40"/>
+      <c r="H48" s="66"/>
+      <c r="I48" s="56"/>
     </row>
     <row r="49" spans="1:9">
-      <c r="A49" s="71"/>
-      <c r="B49" s="43"/>
-      <c r="C49" s="43"/>
-      <c r="D49" s="22"/>
+      <c r="A49" s="62"/>
+      <c r="B49" s="41"/>
+      <c r="C49" s="41"/>
+      <c r="D49" s="21"/>
       <c r="E49" s="17"/>
       <c r="F49" s="11"/>
-      <c r="G49" s="42"/>
-      <c r="H49" s="75"/>
-      <c r="I49" s="58"/>
+      <c r="G49" s="40"/>
+      <c r="H49" s="66"/>
+      <c r="I49" s="56"/>
     </row>
     <row r="50" spans="1:9">
-      <c r="A50" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="B50" s="43"/>
-      <c r="C50" s="43"/>
-      <c r="D50" s="22"/>
+      <c r="A50" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="41"/>
+      <c r="C50" s="41"/>
+      <c r="D50" s="21"/>
       <c r="E50" s="17"/>
       <c r="F50" s="11"/>
-      <c r="G50" s="42"/>
-      <c r="H50" s="76"/>
-      <c r="I50" s="43"/>
+      <c r="G50" s="40"/>
+      <c r="H50" s="67"/>
+      <c r="I50" s="41"/>
     </row>
     <row r="51" spans="1:9">
-      <c r="A51" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="B51" s="43"/>
-      <c r="C51" s="43"/>
-      <c r="D51" s="22"/>
+      <c r="A51" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="B51" s="41"/>
+      <c r="C51" s="41"/>
+      <c r="D51" s="21"/>
       <c r="E51" s="17"/>
       <c r="F51" s="11"/>
-      <c r="G51" s="42"/>
-      <c r="H51" s="76"/>
-      <c r="I51" s="43"/>
+      <c r="G51" s="40"/>
+      <c r="H51" s="67"/>
+      <c r="I51" s="41"/>
     </row>
     <row r="52" spans="1:9">
-      <c r="A52" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="B52" s="43"/>
-      <c r="C52" s="43"/>
-      <c r="D52" s="22"/>
+      <c r="A52" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" s="41"/>
+      <c r="C52" s="41"/>
+      <c r="D52" s="21"/>
       <c r="E52" s="17"/>
       <c r="F52" s="11"/>
-      <c r="G52" s="42"/>
-      <c r="H52" s="76"/>
-      <c r="I52" s="43"/>
+      <c r="G52" s="40"/>
+      <c r="H52" s="67"/>
+      <c r="I52" s="41"/>
     </row>
     <row r="53" spans="1:9">
-      <c r="A53" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="B53" s="43"/>
-      <c r="C53" s="43"/>
-      <c r="D53" s="22"/>
+      <c r="A53" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="B53" s="41"/>
+      <c r="C53" s="41"/>
+      <c r="D53" s="21"/>
       <c r="E53" s="17"/>
       <c r="F53" s="11"/>
-      <c r="G53" s="42"/>
-      <c r="H53" s="77"/>
-      <c r="I53" s="43"/>
+      <c r="G53" s="40"/>
+      <c r="H53" s="68"/>
+      <c r="I53" s="41"/>
     </row>
     <row r="54" spans="1:9">
-      <c r="A54" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="B54" s="43"/>
-      <c r="C54" s="43"/>
-      <c r="D54" s="22"/>
+      <c r="A54" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="B54" s="41"/>
+      <c r="C54" s="41"/>
+      <c r="D54" s="21"/>
       <c r="E54" s="17"/>
       <c r="F54" s="11"/>
-      <c r="G54" s="42"/>
-      <c r="H54" s="76"/>
-      <c r="I54" s="43"/>
+      <c r="G54" s="40"/>
+      <c r="H54" s="67"/>
+      <c r="I54" s="41"/>
     </row>
     <row r="55" spans="1:9">
-      <c r="A55" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="B55" s="43"/>
-      <c r="C55" s="43"/>
-      <c r="D55" s="22"/>
+      <c r="A55" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="B55" s="41"/>
+      <c r="C55" s="41"/>
+      <c r="D55" s="21"/>
       <c r="E55" s="17"/>
       <c r="F55" s="11"/>
-      <c r="G55" s="42"/>
-      <c r="H55" s="76"/>
-      <c r="I55" s="43"/>
+      <c r="G55" s="40"/>
+      <c r="H55" s="67"/>
+      <c r="I55" s="41"/>
     </row>
     <row r="56" spans="1:9">
-      <c r="A56" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="B56" s="43"/>
-      <c r="C56" s="43"/>
-      <c r="D56" s="22"/>
+      <c r="A56" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="B56" s="41"/>
+      <c r="C56" s="41"/>
+      <c r="D56" s="21"/>
       <c r="E56" s="17"/>
       <c r="F56" s="11"/>
-      <c r="G56" s="42"/>
-      <c r="H56" s="76"/>
-      <c r="I56" s="43"/>
+      <c r="G56" s="40"/>
+      <c r="H56" s="67"/>
+      <c r="I56" s="41"/>
     </row>
     <row r="57" spans="1:9">
-      <c r="A57" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="B57" s="43"/>
-      <c r="C57" s="43"/>
-      <c r="D57" s="22"/>
+      <c r="A57" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="B57" s="41"/>
+      <c r="C57" s="41"/>
+      <c r="D57" s="21"/>
       <c r="E57" s="17"/>
       <c r="F57" s="11"/>
-      <c r="G57" s="42"/>
-      <c r="H57" s="76"/>
-      <c r="I57" s="43"/>
+      <c r="G57" s="40"/>
+      <c r="H57" s="67"/>
+      <c r="I57" s="41"/>
     </row>
     <row r="58" spans="1:9">
-      <c r="A58" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="B58" s="43"/>
-      <c r="C58" s="43"/>
-      <c r="D58" s="22"/>
+      <c r="A58" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="B58" s="41"/>
+      <c r="C58" s="41"/>
+      <c r="D58" s="21"/>
       <c r="E58" s="17"/>
       <c r="F58" s="11"/>
-      <c r="G58" s="42"/>
-      <c r="H58" s="76"/>
-      <c r="I58" s="43"/>
+      <c r="G58" s="40"/>
+      <c r="H58" s="67"/>
+      <c r="I58" s="41"/>
     </row>
     <row r="59" spans="1:9">
-      <c r="A59" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="B59" s="43"/>
-      <c r="C59" s="43"/>
-      <c r="D59" s="22"/>
+      <c r="A59" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="B59" s="41"/>
+      <c r="C59" s="41"/>
+      <c r="D59" s="21"/>
       <c r="E59" s="17"/>
       <c r="F59" s="11"/>
-      <c r="G59" s="42"/>
-      <c r="H59" s="76"/>
-      <c r="I59" s="43"/>
+      <c r="G59" s="40"/>
+      <c r="H59" s="67"/>
+      <c r="I59" s="41"/>
     </row>
     <row r="60" spans="1:9">
-      <c r="A60" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="B60" s="43"/>
-      <c r="C60" s="43"/>
-      <c r="D60" s="22"/>
+      <c r="A60" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="B60" s="41"/>
+      <c r="C60" s="41"/>
+      <c r="D60" s="21"/>
       <c r="E60" s="17"/>
       <c r="F60" s="11"/>
-      <c r="G60" s="42"/>
-      <c r="H60" s="76"/>
-      <c r="I60" s="43"/>
+      <c r="G60" s="40"/>
+      <c r="H60" s="67"/>
+      <c r="I60" s="41"/>
     </row>
     <row r="61" spans="1:9">
-      <c r="A61" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="B61" s="43"/>
-      <c r="C61" s="43"/>
-      <c r="D61" s="22"/>
+      <c r="A61" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="B61" s="41"/>
+      <c r="C61" s="41"/>
+      <c r="D61" s="21"/>
       <c r="E61" s="17"/>
       <c r="F61" s="11"/>
-      <c r="G61" s="42"/>
-      <c r="H61" s="76"/>
-      <c r="I61" s="43"/>
+      <c r="G61" s="40"/>
+      <c r="H61" s="67"/>
+      <c r="I61" s="41"/>
     </row>
     <row r="62" spans="1:9">
-      <c r="A62" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="B62" s="43"/>
-      <c r="C62" s="43"/>
-      <c r="D62" s="22"/>
+      <c r="A62" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="B62" s="41"/>
+      <c r="C62" s="41"/>
+      <c r="D62" s="21"/>
       <c r="E62" s="17"/>
       <c r="F62" s="11"/>
-      <c r="G62" s="42"/>
-      <c r="H62" s="76"/>
-      <c r="I62" s="43"/>
+      <c r="G62" s="40"/>
+      <c r="H62" s="67"/>
+      <c r="I62" s="41"/>
     </row>
     <row r="63" spans="1:9">
-      <c r="A63" s="72"/>
-      <c r="B63" s="43"/>
-      <c r="C63" s="43"/>
-      <c r="D63" s="22"/>
+      <c r="A63" s="63"/>
+      <c r="B63" s="41"/>
+      <c r="C63" s="41"/>
+      <c r="D63" s="21"/>
       <c r="E63" s="12"/>
       <c r="F63" s="11"/>
-      <c r="G63" s="42"/>
-      <c r="H63" s="78"/>
-      <c r="I63" s="43"/>
+      <c r="G63" s="40"/>
+      <c r="H63" s="69"/>
+      <c r="I63" s="41"/>
     </row>
     <row r="64" spans="1:9">
-      <c r="A64" s="72"/>
-      <c r="B64" s="43"/>
-      <c r="C64" s="43"/>
-      <c r="D64" s="22"/>
+      <c r="A64" s="63"/>
+      <c r="B64" s="41"/>
+      <c r="C64" s="41"/>
+      <c r="D64" s="21"/>
       <c r="E64" s="12"/>
       <c r="F64" s="11"/>
-      <c r="G64" s="42"/>
-      <c r="H64" s="78"/>
-      <c r="I64" s="43"/>
+      <c r="G64" s="40"/>
+      <c r="H64" s="69"/>
+      <c r="I64" s="41"/>
     </row>
     <row r="65" spans="1:9">
-      <c r="A65" s="72"/>
-      <c r="B65" s="43"/>
-      <c r="C65" s="43"/>
-      <c r="D65" s="22"/>
+      <c r="A65" s="63"/>
+      <c r="B65" s="41"/>
+      <c r="C65" s="41"/>
+      <c r="D65" s="21"/>
       <c r="E65" s="12"/>
       <c r="F65" s="11"/>
-      <c r="G65" s="42"/>
-      <c r="H65" s="78"/>
-      <c r="I65" s="43"/>
+      <c r="G65" s="40"/>
+      <c r="H65" s="69"/>
+      <c r="I65" s="41"/>
     </row>
     <row r="66" spans="1:9">
-      <c r="A66" s="72"/>
-      <c r="B66" s="43"/>
-      <c r="C66" s="43"/>
-      <c r="D66" s="22"/>
+      <c r="A66" s="63"/>
+      <c r="B66" s="41"/>
+      <c r="C66" s="41"/>
+      <c r="D66" s="21"/>
       <c r="E66" s="12"/>
       <c r="F66" s="11"/>
-      <c r="G66" s="42"/>
-      <c r="H66" s="78"/>
-      <c r="I66" s="43"/>
+      <c r="G66" s="40"/>
+      <c r="H66" s="69"/>
+      <c r="I66" s="41"/>
     </row>
     <row r="67" spans="1:9">
-      <c r="A67" s="72"/>
-      <c r="B67" s="43"/>
-      <c r="C67" s="43"/>
-      <c r="D67" s="22"/>
+      <c r="A67" s="63"/>
+      <c r="B67" s="41"/>
+      <c r="C67" s="41"/>
+      <c r="D67" s="21"/>
       <c r="E67" s="12"/>
       <c r="F67" s="11"/>
-      <c r="G67" s="42"/>
-      <c r="H67" s="78"/>
-      <c r="I67" s="43"/>
+      <c r="G67" s="40"/>
+      <c r="H67" s="69"/>
+      <c r="I67" s="41"/>
     </row>
     <row r="68" spans="1:9">
-      <c r="A68" s="72"/>
-      <c r="B68" s="43"/>
-      <c r="C68" s="43"/>
-      <c r="D68" s="22"/>
+      <c r="A68" s="63"/>
+      <c r="B68" s="41"/>
+      <c r="C68" s="41"/>
+      <c r="D68" s="21"/>
       <c r="E68" s="12"/>
       <c r="F68" s="11"/>
-      <c r="G68" s="42"/>
-      <c r="H68" s="78"/>
-      <c r="I68" s="43"/>
+      <c r="G68" s="40"/>
+      <c r="H68" s="69"/>
+      <c r="I68" s="41"/>
     </row>
     <row r="69" spans="1:9">
-      <c r="A69" s="72"/>
-      <c r="B69" s="43"/>
-      <c r="C69" s="43"/>
-      <c r="D69" s="22"/>
+      <c r="A69" s="63"/>
+      <c r="B69" s="41"/>
+      <c r="C69" s="41"/>
+      <c r="D69" s="21"/>
       <c r="E69" s="12"/>
       <c r="F69" s="11"/>
-      <c r="G69" s="42"/>
-      <c r="H69" s="78"/>
-      <c r="I69" s="43"/>
+      <c r="G69" s="40"/>
+      <c r="H69" s="69"/>
+      <c r="I69" s="41"/>
     </row>
     <row r="70" spans="1:9">
-      <c r="A70" s="72"/>
-      <c r="B70" s="43"/>
-      <c r="C70" s="43"/>
-      <c r="D70" s="22"/>
+      <c r="A70" s="63"/>
+      <c r="B70" s="41"/>
+      <c r="C70" s="41"/>
+      <c r="D70" s="21"/>
       <c r="E70" s="12"/>
       <c r="F70" s="11"/>
-      <c r="G70" s="42"/>
-      <c r="H70" s="78"/>
-      <c r="I70" s="43"/>
+      <c r="G70" s="40"/>
+      <c r="H70" s="69"/>
+      <c r="I70" s="41"/>
     </row>
     <row r="71" spans="1:9">
-      <c r="A71" s="72"/>
-      <c r="B71" s="43"/>
-      <c r="C71" s="43"/>
-      <c r="D71" s="22"/>
+      <c r="A71" s="63"/>
+      <c r="B71" s="41"/>
+      <c r="C71" s="41"/>
+      <c r="D71" s="21"/>
       <c r="E71" s="12"/>
       <c r="F71" s="11"/>
-      <c r="G71" s="42"/>
-      <c r="H71" s="78"/>
-      <c r="I71" s="43"/>
+      <c r="G71" s="40"/>
+      <c r="H71" s="69"/>
+      <c r="I71" s="41"/>
     </row>
     <row r="72" spans="1:9">
-      <c r="A72" s="72"/>
-      <c r="B72" s="43"/>
-      <c r="C72" s="43"/>
-      <c r="D72" s="22"/>
+      <c r="A72" s="63"/>
+      <c r="B72" s="41"/>
+      <c r="C72" s="41"/>
+      <c r="D72" s="21"/>
       <c r="E72" s="12"/>
       <c r="F72" s="11"/>
-      <c r="G72" s="42"/>
-      <c r="H72" s="78"/>
-      <c r="I72" s="43"/>
+      <c r="G72" s="40"/>
+      <c r="H72" s="69"/>
+      <c r="I72" s="41"/>
     </row>
     <row r="73" spans="1:9">
-      <c r="A73" s="72"/>
-      <c r="B73" s="43"/>
-      <c r="C73" s="43"/>
-      <c r="D73" s="22"/>
+      <c r="A73" s="63"/>
+      <c r="B73" s="41"/>
+      <c r="C73" s="41"/>
+      <c r="D73" s="21"/>
       <c r="E73" s="12"/>
       <c r="F73" s="11"/>
-      <c r="G73" s="42"/>
-      <c r="H73" s="78"/>
-      <c r="I73" s="43"/>
+      <c r="G73" s="40"/>
+      <c r="H73" s="69"/>
+      <c r="I73" s="41"/>
     </row>
     <row r="74" spans="1:9">
-      <c r="A74" s="72"/>
-      <c r="B74" s="43"/>
-      <c r="C74" s="43"/>
-      <c r="D74" s="22"/>
+      <c r="A74" s="63"/>
+      <c r="B74" s="41"/>
+      <c r="C74" s="41"/>
+      <c r="D74" s="21"/>
       <c r="E74" s="12"/>
       <c r="F74" s="11"/>
-      <c r="G74" s="42"/>
-      <c r="H74" s="78"/>
-      <c r="I74" s="43"/>
+      <c r="G74" s="40"/>
+      <c r="H74" s="69"/>
+      <c r="I74" s="41"/>
     </row>
     <row r="75" spans="1:9">
-      <c r="A75" s="72"/>
+      <c r="A75" s="63"/>
       <c r="B75" s="17"/>
-      <c r="C75" s="43"/>
-      <c r="D75" s="22"/>
+      <c r="C75" s="41"/>
+      <c r="D75" s="21"/>
       <c r="E75" s="17"/>
       <c r="F75" s="11"/>
-      <c r="G75" s="42"/>
-      <c r="H75" s="78"/>
+      <c r="G75" s="40"/>
+      <c r="H75" s="69"/>
       <c r="I75" s="12"/>
     </row>
     <row r="76" spans="1:9">
-      <c r="D76" s="79"/>
-      <c r="F76" s="69"/>
+      <c r="D76" s="70"/>
+      <c r="F76" s="60"/>
     </row>
     <row r="77" spans="1:9">
-      <c r="D77" s="79"/>
-      <c r="F77" s="69"/>
+      <c r="D77" s="70"/>
+      <c r="F77" s="60"/>
     </row>
     <row r="78" spans="1:9">
-      <c r="D78" s="79"/>
-      <c r="F78" s="69"/>
+      <c r="D78" s="70"/>
+      <c r="F78" s="60"/>
     </row>
     <row r="79" spans="1:9">
-      <c r="D79" s="79"/>
-      <c r="F79" s="69"/>
+      <c r="D79" s="70"/>
+      <c r="F79" s="60"/>
     </row>
     <row r="80" spans="1:9">
-      <c r="D80" s="79"/>
-      <c r="F80" s="69"/>
+      <c r="D80" s="70"/>
+      <c r="F80" s="60"/>
     </row>
     <row r="81" spans="4:6">
-      <c r="D81" s="79"/>
-      <c r="F81" s="69"/>
+      <c r="D81" s="70"/>
+      <c r="F81" s="60"/>
     </row>
     <row r="82" spans="4:6">
-      <c r="D82" s="79"/>
-      <c r="F82" s="69"/>
+      <c r="D82" s="70"/>
+      <c r="F82" s="60"/>
     </row>
     <row r="83" spans="4:6">
-      <c r="D83" s="79"/>
-      <c r="F83" s="69"/>
+      <c r="D83" s="70"/>
+      <c r="F83" s="60"/>
     </row>
     <row r="84" spans="4:6">
-      <c r="D84" s="79"/>
-      <c r="F84" s="69"/>
+      <c r="D84" s="70"/>
+      <c r="F84" s="60"/>
     </row>
     <row r="85" spans="4:6">
-      <c r="D85" s="79"/>
-      <c r="F85" s="69"/>
+      <c r="D85" s="70"/>
+      <c r="F85" s="60"/>
     </row>
     <row r="86" spans="4:6">
-      <c r="D86" s="79"/>
-      <c r="F86" s="69"/>
+      <c r="D86" s="70"/>
+      <c r="F86" s="60"/>
     </row>
     <row r="87" spans="4:6">
-      <c r="D87" s="79"/>
-      <c r="F87" s="69"/>
+      <c r="D87" s="70"/>
+      <c r="F87" s="60"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
@@ -8595,65 +9283,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="45" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="489f8e21b9a70c9d7a16fa4497d5b683">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2f3b4a981d4ba54fcf1b71789fe9b31f" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -9037,12 +9666,71 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{085BABE9-4E2E-49DF-BDAB-445AA4DA56A3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9050,5 +9738,5 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{085BABE9-4E2E-49DF-BDAB-445AA4DA56A3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
--- a/Treinamento/Index/Relatório de Recusas 23.02.2026 a 01.03.2026.xlsx
+++ b/Treinamento/Index/Relatório de Recusas 23.02.2026 a 01.03.2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29819"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29825"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/shirlei_witkowski_allianz_com_br/Documents/Planilha de recusa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BE62940-F149-4817-A5E8-0CDE7F85C401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{63651F40-1C14-4A60-95CF-E1740CDC17C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="23.02" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="249">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -773,6 +773,119 @@
   </si>
   <si>
     <t xml:space="preserve">RENATA GOMES COSTANTINI                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGINALDO MENDES AUGUSTO                     </t>
+  </si>
+  <si>
+    <t>PRAZO EXPIRADO - REPIQUE (foto da frente e lt d / frente e lt es.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATRICIA MUSSI SIMIC                         </t>
+  </si>
+  <si>
+    <t>Divergências na Central de Bônus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA TATIANA LUCENA ALVES                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favor enviar cópia completa da apólice referente 2025/2026 (Não
+será aceito a CI, uma vez em que a CBE não retorna os dados).
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCELY DE FATIMA MENEZES                     </t>
+  </si>
+  <si>
+    <t>Faltou endosso de cancelamento da apólice 2026/2027.
+Proposta j
+a se encontra recusada, mas podem nos enviar o documento faltante
+que realizaremos a reentrada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIRCEU LANUTTO                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUBAL SUCUPIRA SANTOS                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CILENE LUCIANO DO PRADO DE PAIVA             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDILTON FERREIRA LIMA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATHEUS DE OLIVEIRA DIAS                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANICETO BOSCHESI NETO                        </t>
+  </si>
+  <si>
+    <t>PARA CHOQUE DIANTEIRO MAL ENCAIXADO. VISTORIA A FRUSTRAR COM FOTOS INCORRETAS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALESSANDRA ROSSELLI ALENCAR BOERI            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">WILSON GELAMOS CARQUEIJEIRO                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCINETE DE MOURA SILVA                    </t>
+  </si>
+  <si>
+    <t>KM INDISPONIVEL | VISTORIA COM FOTOS INCORRETAS - PRAZO EXPIRADO: FOTO DO HODOMETRO MAL ENQUADADA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WILLIAMS FLAVIO GOMES                        </t>
+  </si>
+  <si>
+    <t>VISTORIA A FRUSTRAR COM FOTOS INCORRETAS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIDNEIA APARECIDA DAMASCENO DE OLIVEIRA      </t>
+  </si>
+  <si>
+    <t>**FRUSTRADO** CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELIETE MARIA DE SANTANA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADRIANA DA SILVA                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALEX SEBENELLO DE OLIVEIRA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGIANE TRONFINO PESSOA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALEXANDRE DE QUEIROZ PEREIRA                 </t>
+  </si>
+  <si>
+    <t>VISTORIA A FRUSTRAR COM FOTOS INCORRETAS: DOCUMENTO ILEGÍVEL (EMBAÇADO) | OBS: LUZ DE INJEÇÃO ACESA NO PAINEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JESSICA BRUNA DE SOUZA                       </t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 25.02.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROBSON ROLIM                                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BALIMAX ENGENHARIA LTDA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDREA CORDEIRO ARNAUD                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FELIPPE EMMANUEL DA CRUZ ALVES DE BRITTO     </t>
+  </si>
+  <si>
+    <t>LUZINETE MOREIRA DE BARROS TEIXEIRA DOS SANTO</t>
   </si>
 </sst>
 </file>
@@ -1061,7 +1174,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1121,9 +1234,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1271,15 +1381,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1289,7 +1393,12 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1708,13 +1817,13 @@
       <c r="F2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="G2" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="42" t="s">
+      <c r="H2" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="41">
+      <c r="I2" s="40">
         <v>46066</v>
       </c>
     </row>
@@ -1737,13 +1846,13 @@
       <c r="F3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="40" t="s">
+      <c r="G3" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="42" t="s">
+      <c r="H3" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="41">
+      <c r="I3" s="40">
         <v>46064</v>
       </c>
     </row>
@@ -1766,13 +1875,13 @@
       <c r="F4" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="40" t="s">
+      <c r="G4" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="42" t="s">
+      <c r="H4" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="41">
+      <c r="I4" s="40">
         <v>46076</v>
       </c>
     </row>
@@ -1795,13 +1904,13 @@
       <c r="F5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="40" t="s">
+      <c r="G5" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="42" t="s">
+      <c r="H5" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="41">
+      <c r="I5" s="40">
         <v>46076</v>
       </c>
     </row>
@@ -1824,13 +1933,13 @@
       <c r="F6" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="40" t="s">
+      <c r="G6" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="42" t="s">
+      <c r="H6" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="I6" s="41">
+      <c r="I6" s="40">
         <v>46064</v>
       </c>
     </row>
@@ -1853,13 +1962,13 @@
       <c r="F7" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="40" t="s">
+      <c r="G7" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="42" t="s">
+      <c r="H7" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="41">
+      <c r="I7" s="40">
         <v>46072</v>
       </c>
     </row>
@@ -1882,13 +1991,13 @@
       <c r="F8" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="40" t="s">
+      <c r="G8" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="42" t="s">
+      <c r="H8" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="I8" s="41">
+      <c r="I8" s="40">
         <v>46073</v>
       </c>
     </row>
@@ -1911,13 +2020,13 @@
       <c r="F9" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="40" t="s">
+      <c r="G9" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="42" t="s">
+      <c r="H9" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="41">
+      <c r="I9" s="40">
         <v>46076</v>
       </c>
     </row>
@@ -1940,13 +2049,13 @@
       <c r="F10" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="G10" s="40" t="s">
+      <c r="G10" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="42" t="s">
+      <c r="H10" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I10" s="41">
+      <c r="I10" s="40">
         <v>46064</v>
       </c>
     </row>
@@ -1969,13 +2078,13 @@
       <c r="F11" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G11" s="40" t="s">
+      <c r="G11" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="42" t="s">
+      <c r="H11" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="I11" s="41">
+      <c r="I11" s="40">
         <v>46076</v>
       </c>
     </row>
@@ -1998,13 +2107,13 @@
       <c r="F12" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="40" t="s">
+      <c r="G12" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H12" s="42" t="s">
+      <c r="H12" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I12" s="41">
+      <c r="I12" s="40">
         <v>46064</v>
       </c>
     </row>
@@ -2027,13 +2136,13 @@
       <c r="F13" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="G13" s="40" t="s">
+      <c r="G13" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="42" t="s">
+      <c r="H13" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="41">
+      <c r="I13" s="40">
         <v>46064</v>
       </c>
     </row>
@@ -2056,13 +2165,13 @@
       <c r="F14" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="40" t="s">
+      <c r="G14" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="42" t="s">
+      <c r="H14" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="41">
+      <c r="I14" s="40">
         <v>46058</v>
       </c>
     </row>
@@ -2085,13 +2194,13 @@
       <c r="F15" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="G15" s="40" t="s">
+      <c r="G15" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H15" s="42" t="s">
+      <c r="H15" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I15" s="41">
+      <c r="I15" s="40">
         <v>46064</v>
       </c>
     </row>
@@ -2114,13 +2223,13 @@
       <c r="F16" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="G16" s="40" t="s">
+      <c r="G16" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="H16" s="42" t="s">
+      <c r="H16" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="I16" s="41">
+      <c r="I16" s="40">
         <v>46072</v>
       </c>
     </row>
@@ -2143,13 +2252,13 @@
       <c r="F17" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G17" s="40" t="s">
+      <c r="G17" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="H17" s="42" t="s">
+      <c r="H17" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="I17" s="41">
+      <c r="I17" s="40">
         <v>46076</v>
       </c>
     </row>
@@ -2172,13 +2281,13 @@
       <c r="F18" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G18" s="40" t="s">
+      <c r="G18" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H18" s="42" t="s">
+      <c r="H18" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I18" s="41">
+      <c r="I18" s="40">
         <v>46064</v>
       </c>
     </row>
@@ -2201,13 +2310,13 @@
       <c r="F19" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="G19" s="40" t="s">
+      <c r="G19" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H19" s="42" t="s">
+      <c r="H19" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="41">
+      <c r="I19" s="40">
         <v>46064</v>
       </c>
     </row>
@@ -2230,13 +2339,13 @@
       <c r="F20" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="G20" s="40" t="s">
+      <c r="G20" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H20" s="42" t="s">
+      <c r="H20" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="41">
+      <c r="I20" s="40">
         <v>46064</v>
       </c>
     </row>
@@ -2259,13 +2368,13 @@
       <c r="F21" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="G21" s="40" t="s">
+      <c r="G21" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="H21" s="42" t="s">
+      <c r="H21" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="I21" s="41">
+      <c r="I21" s="40">
         <v>46073</v>
       </c>
     </row>
@@ -2288,13 +2397,13 @@
       <c r="F22" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G22" s="40" t="s">
+      <c r="G22" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H22" s="42" t="s">
+      <c r="H22" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="41">
+      <c r="I22" s="40">
         <v>11</v>
       </c>
     </row>
@@ -2317,13 +2426,13 @@
       <c r="F23" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="G23" s="40" t="s">
+      <c r="G23" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H23" s="42" t="s">
+      <c r="H23" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I23" s="41">
+      <c r="I23" s="40">
         <v>46064</v>
       </c>
     </row>
@@ -2346,13 +2455,13 @@
       <c r="F24" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="G24" s="40" t="s">
+      <c r="G24" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H24" s="42" t="s">
+      <c r="H24" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I24" s="41">
+      <c r="I24" s="40">
         <v>46064</v>
       </c>
     </row>
@@ -2375,13 +2484,13 @@
       <c r="F25" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G25" s="40" t="s">
+      <c r="G25" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="H25" s="42" t="s">
+      <c r="H25" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="I25" s="41">
+      <c r="I25" s="40">
         <v>46076</v>
       </c>
     </row>
@@ -2404,13 +2513,13 @@
       <c r="F26" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G26" s="40" t="s">
+      <c r="G26" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H26" s="42" t="s">
+      <c r="H26" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="I26" s="41">
+      <c r="I26" s="40">
         <v>46076</v>
       </c>
     </row>
@@ -2433,13 +2542,13 @@
       <c r="F27" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="G27" s="40" t="s">
+      <c r="G27" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="H27" s="42" t="s">
+      <c r="H27" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="I27" s="41">
+      <c r="I27" s="40">
         <v>46071</v>
       </c>
     </row>
@@ -2462,13 +2571,13 @@
       <c r="F28" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="G28" s="40" t="s">
+      <c r="G28" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="H28" s="42" t="s">
+      <c r="H28" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="I28" s="41">
+      <c r="I28" s="40">
         <v>46073</v>
       </c>
     </row>
@@ -2491,13 +2600,13 @@
       <c r="F29" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="G29" s="40" t="s">
+      <c r="G29" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="H29" s="42" t="s">
+      <c r="H29" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="I29" s="41">
+      <c r="I29" s="40">
         <v>46073</v>
       </c>
     </row>
@@ -2520,42 +2629,42 @@
       <c r="F30" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G30" s="40" t="s">
+      <c r="G30" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="H30" s="43" t="s">
+      <c r="H30" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="I30" s="41">
+      <c r="I30" s="40">
         <v>46073</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="80" customFormat="1">
-      <c r="A31" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" s="72">
+    <row r="31" spans="1:9" s="79" customFormat="1">
+      <c r="A31" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="71">
         <v>46066</v>
       </c>
-      <c r="C31" s="73">
+      <c r="C31" s="72">
         <v>46076</v>
       </c>
-      <c r="D31" s="74">
+      <c r="D31" s="73">
         <v>136751753</v>
       </c>
-      <c r="E31" s="75">
+      <c r="E31" s="74">
         <v>3450252531</v>
       </c>
-      <c r="F31" s="76" t="s">
+      <c r="F31" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="G31" s="77" t="s">
+      <c r="G31" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="H31" s="78" t="s">
+      <c r="H31" s="77" t="s">
         <v>55</v>
       </c>
-      <c r="I31" s="79">
+      <c r="I31" s="78">
         <v>46073</v>
       </c>
     </row>
@@ -2578,13 +2687,13 @@
       <c r="F32" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G32" s="40" t="s">
+      <c r="G32" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H32" s="42" t="s">
+      <c r="H32" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I32" s="41">
+      <c r="I32" s="40">
         <v>46066</v>
       </c>
     </row>
@@ -2607,13 +2716,13 @@
       <c r="F33" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="G33" s="40" t="s">
+      <c r="G33" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H33" s="42" t="s">
+      <c r="H33" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I33" s="41">
+      <c r="I33" s="40">
         <v>46066</v>
       </c>
     </row>
@@ -2636,13 +2745,13 @@
       <c r="F34" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="G34" s="40" t="s">
+      <c r="G34" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H34" s="42" t="s">
+      <c r="H34" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I34" s="41">
+      <c r="I34" s="40">
         <v>46063</v>
       </c>
     </row>
@@ -2665,13 +2774,13 @@
       <c r="F35" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="G35" s="40" t="s">
+      <c r="G35" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H35" s="42" t="s">
+      <c r="H35" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I35" s="41">
+      <c r="I35" s="40">
         <v>46066</v>
       </c>
     </row>
@@ -2694,13 +2803,13 @@
       <c r="F36" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G36" s="40" t="s">
+      <c r="G36" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H36" s="42" t="s">
+      <c r="H36" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I36" s="41">
+      <c r="I36" s="40">
         <v>46066</v>
       </c>
     </row>
@@ -2723,13 +2832,13 @@
       <c r="F37" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="G37" s="40" t="s">
+      <c r="G37" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H37" s="42" t="s">
+      <c r="H37" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I37" s="41">
+      <c r="I37" s="40">
         <v>46066</v>
       </c>
     </row>
@@ -2752,13 +2861,13 @@
       <c r="F38" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="G38" s="40" t="s">
+      <c r="G38" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H38" s="42" t="s">
+      <c r="H38" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I38" s="41">
+      <c r="I38" s="40">
         <v>46066</v>
       </c>
     </row>
@@ -2781,13 +2890,13 @@
       <c r="F39" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="G39" s="40" t="s">
+      <c r="G39" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H39" s="42" t="s">
+      <c r="H39" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I39" s="41">
+      <c r="I39" s="40">
         <v>46064</v>
       </c>
     </row>
@@ -2810,13 +2919,13 @@
       <c r="F40" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="G40" s="40" t="s">
+      <c r="G40" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H40" s="42" t="s">
+      <c r="H40" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I40" s="41">
+      <c r="I40" s="40">
         <v>46066</v>
       </c>
     </row>
@@ -2839,13 +2948,13 @@
       <c r="F41" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="G41" s="40" t="s">
+      <c r="G41" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H41" s="42" t="s">
+      <c r="H41" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I41" s="41">
+      <c r="I41" s="40">
         <v>46066</v>
       </c>
     </row>
@@ -2868,13 +2977,13 @@
       <c r="F42" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="G42" s="40" t="s">
+      <c r="G42" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H42" s="42" t="s">
+      <c r="H42" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I42" s="41">
+      <c r="I42" s="40">
         <v>46066</v>
       </c>
     </row>
@@ -2897,13 +3006,13 @@
       <c r="F43" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="G43" s="40" t="s">
+      <c r="G43" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H43" s="42" t="s">
+      <c r="H43" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I43" s="41">
+      <c r="I43" s="40">
         <v>46064</v>
       </c>
     </row>
@@ -2926,13 +3035,13 @@
       <c r="F44" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="G44" s="40" t="s">
+      <c r="G44" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H44" s="42" t="s">
+      <c r="H44" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I44" s="41">
+      <c r="I44" s="40">
         <v>46066</v>
       </c>
     </row>
@@ -2955,13 +3064,13 @@
       <c r="F45" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="G45" s="40" t="s">
+      <c r="G45" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H45" s="42" t="s">
+      <c r="H45" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I45" s="41">
+      <c r="I45" s="40">
         <v>46066</v>
       </c>
     </row>
@@ -2984,13 +3093,13 @@
       <c r="F46" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="G46" s="40" t="s">
+      <c r="G46" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="H46" s="42" t="s">
+      <c r="H46" s="41" t="s">
         <v>75</v>
       </c>
-      <c r="I46" s="41">
+      <c r="I46" s="40">
         <v>46066</v>
       </c>
     </row>
@@ -3013,13 +3122,13 @@
       <c r="F47" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="G47" s="40" t="s">
+      <c r="G47" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H47" s="42" t="s">
+      <c r="H47" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I47" s="41">
+      <c r="I47" s="40">
         <v>46064</v>
       </c>
     </row>
@@ -3042,13 +3151,13 @@
       <c r="F48" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="G48" s="40" t="s">
+      <c r="G48" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H48" s="42" t="s">
+      <c r="H48" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I48" s="41">
+      <c r="I48" s="40">
         <v>46066</v>
       </c>
     </row>
@@ -3071,13 +3180,13 @@
       <c r="F49" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="G49" s="40" t="s">
+      <c r="G49" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H49" s="42" t="s">
+      <c r="H49" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I49" s="41">
+      <c r="I49" s="40">
         <v>46066</v>
       </c>
     </row>
@@ -3100,13 +3209,13 @@
       <c r="F50" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="G50" s="40" t="s">
+      <c r="G50" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H50" s="42" t="s">
+      <c r="H50" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I50" s="41">
+      <c r="I50" s="40">
         <v>46066</v>
       </c>
     </row>
@@ -3129,13 +3238,13 @@
       <c r="F51" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="G51" s="40" t="s">
+      <c r="G51" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H51" s="42" t="s">
+      <c r="H51" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I51" s="41">
+      <c r="I51" s="40">
         <v>46066</v>
       </c>
     </row>
@@ -3143,7 +3252,7 @@
       <c r="A52" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B52" s="44">
+      <c r="B52" s="43">
         <v>46066</v>
       </c>
       <c r="C52" s="23">
@@ -3158,13 +3267,13 @@
       <c r="F52" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="G52" s="40" t="s">
+      <c r="G52" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H52" s="42" t="s">
+      <c r="H52" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I52" s="41">
+      <c r="I52" s="40">
         <v>46066</v>
       </c>
     </row>
@@ -3187,13 +3296,13 @@
       <c r="F53" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="G53" s="40" t="s">
+      <c r="G53" s="39" t="s">
         <v>14</v>
       </c>
       <c r="H53" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I53" s="41">
+      <c r="I53" s="40">
         <v>46066</v>
       </c>
     </row>
@@ -3216,13 +3325,13 @@
       <c r="F54" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="G54" s="40" t="s">
+      <c r="G54" s="39" t="s">
         <v>14</v>
       </c>
       <c r="H54" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I54" s="41">
+      <c r="I54" s="40">
         <v>46065</v>
       </c>
     </row>
@@ -3245,13 +3354,13 @@
       <c r="F55" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="G55" s="40" t="s">
+      <c r="G55" s="39" t="s">
         <v>14</v>
       </c>
       <c r="H55" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I55" s="41">
+      <c r="I55" s="40">
         <v>46066</v>
       </c>
     </row>
@@ -3274,13 +3383,13 @@
       <c r="F56" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="G56" s="40" t="s">
+      <c r="G56" s="39" t="s">
         <v>14</v>
       </c>
       <c r="H56" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I56" s="41">
+      <c r="I56" s="40">
         <v>46065</v>
       </c>
     </row>
@@ -3303,13 +3412,13 @@
       <c r="F57" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="G57" s="40" t="s">
+      <c r="G57" s="39" t="s">
         <v>14</v>
       </c>
       <c r="H57" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I57" s="41">
+      <c r="I57" s="40">
         <v>46066</v>
       </c>
     </row>
@@ -3332,13 +3441,13 @@
       <c r="F58" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="G58" s="40" t="s">
+      <c r="G58" s="39" t="s">
         <v>14</v>
       </c>
       <c r="H58" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I58" s="41">
+      <c r="I58" s="40">
         <v>46066</v>
       </c>
     </row>
@@ -3361,13 +3470,13 @@
       <c r="F59" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="G59" s="40" t="s">
+      <c r="G59" s="39" t="s">
         <v>14</v>
       </c>
       <c r="H59" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I59" s="41">
+      <c r="I59" s="40">
         <v>46066</v>
       </c>
     </row>
@@ -3390,13 +3499,13 @@
       <c r="F60" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="G60" s="40" t="s">
+      <c r="G60" s="39" t="s">
         <v>14</v>
       </c>
       <c r="H60" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I60" s="41">
+      <c r="I60" s="40">
         <v>46066</v>
       </c>
     </row>
@@ -3419,13 +3528,13 @@
       <c r="F61" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="G61" s="40" t="s">
+      <c r="G61" s="39" t="s">
         <v>14</v>
       </c>
       <c r="H61" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I61" s="41">
+      <c r="I61" s="40">
         <v>46066</v>
       </c>
     </row>
@@ -3448,13 +3557,13 @@
       <c r="F62" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="G62" s="40" t="s">
+      <c r="G62" s="39" t="s">
         <v>14</v>
       </c>
       <c r="H62" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I62" s="41">
+      <c r="I62" s="40">
         <v>46066</v>
       </c>
     </row>
@@ -3477,13 +3586,13 @@
       <c r="F63" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="G63" s="40" t="s">
+      <c r="G63" s="39" t="s">
         <v>14</v>
       </c>
       <c r="H63" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I63" s="41">
+      <c r="I63" s="40">
         <v>46066</v>
       </c>
     </row>
@@ -3506,13 +3615,13 @@
       <c r="F64" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="G64" s="40" t="s">
+      <c r="G64" s="39" t="s">
         <v>14</v>
       </c>
       <c r="H64" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I64" s="41">
+      <c r="I64" s="40">
         <v>46066</v>
       </c>
     </row>
@@ -3535,13 +3644,13 @@
       <c r="F65" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="G65" s="40" t="s">
+      <c r="G65" s="39" t="s">
         <v>14</v>
       </c>
       <c r="H65" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I65" s="46">
+      <c r="I65" s="45">
         <v>46066</v>
       </c>
     </row>
@@ -3567,10 +3676,10 @@
       <c r="G66" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H66" s="45" t="s">
+      <c r="H66" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="I66" s="41">
+      <c r="I66" s="40">
         <v>46066</v>
       </c>
     </row>
@@ -3612,60 +3721,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="49" t="s">
+      <c r="C1" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="E1" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="48" t="s">
+      <c r="F1" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="48" t="s">
+      <c r="G1" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="51" t="s">
+      <c r="H1" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="48" t="s">
+      <c r="I1" s="47" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="52">
+      <c r="A2" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="51">
         <v>46074</v>
       </c>
-      <c r="C2" s="53">
+      <c r="C2" s="52">
         <v>46077</v>
       </c>
       <c r="D2" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="E2" s="54">
+      <c r="E2" s="53">
         <v>3450257349</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="G2" s="55" t="s">
+      <c r="G2" s="54" t="s">
         <v>22</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="I2" s="56" t="s">
+      <c r="I2" s="55" t="s">
         <v>100</v>
       </c>
     </row>
@@ -3676,25 +3785,25 @@
       <c r="B3" s="7">
         <v>46058</v>
       </c>
-      <c r="C3" s="53">
+      <c r="C3" s="52">
         <v>46077</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="E3" s="54">
+      <c r="E3" s="53">
         <v>3450242609</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="F3" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="40" t="s">
+      <c r="G3" s="39" t="s">
         <v>22</v>
       </c>
       <c r="H3" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="I3" s="41"/>
+      <c r="I3" s="40"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -3703,25 +3812,25 @@
       <c r="B4" s="7">
         <v>46062</v>
       </c>
-      <c r="C4" s="53">
+      <c r="C4" s="52">
         <v>46077</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="E4" s="54">
+      <c r="E4" s="53">
         <v>3450246261</v>
       </c>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="G4" s="40" t="s">
+      <c r="G4" s="39" t="s">
         <v>22</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="I4" s="41"/>
+      <c r="I4" s="40"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
@@ -3730,25 +3839,25 @@
       <c r="B5" s="7">
         <v>46064</v>
       </c>
-      <c r="C5" s="53">
+      <c r="C5" s="52">
         <v>46077</v>
       </c>
       <c r="D5" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="E5" s="54">
+      <c r="E5" s="53">
         <v>3450249374</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="F5" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="G5" s="40" t="s">
+      <c r="G5" s="39" t="s">
         <v>22</v>
       </c>
       <c r="H5" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="I5" s="41"/>
+      <c r="I5" s="40"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
@@ -3757,25 +3866,25 @@
       <c r="B6" s="7">
         <v>46071</v>
       </c>
-      <c r="C6" s="53">
+      <c r="C6" s="52">
         <v>46077</v>
       </c>
       <c r="D6" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="E6" s="54">
+      <c r="E6" s="53">
         <v>3450254654</v>
       </c>
-      <c r="F6" s="29" t="s">
+      <c r="F6" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="G6" s="40" t="s">
+      <c r="G6" s="39" t="s">
         <v>22</v>
       </c>
       <c r="H6" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="I6" s="41"/>
+      <c r="I6" s="40"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
@@ -3784,25 +3893,25 @@
       <c r="B7" s="7">
         <v>46068</v>
       </c>
-      <c r="C7" s="53">
+      <c r="C7" s="52">
         <v>46077</v>
       </c>
-      <c r="D7" s="81" t="s">
+      <c r="D7" s="80" t="s">
         <v>97</v>
       </c>
-      <c r="E7" s="59">
+      <c r="E7" s="58">
         <v>3450253543</v>
       </c>
-      <c r="F7" s="82" t="s">
+      <c r="F7" s="81" t="s">
         <v>105</v>
       </c>
-      <c r="G7" s="83" t="s">
+      <c r="G7" s="82" t="s">
         <v>22</v>
       </c>
       <c r="H7" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="I7" s="41"/>
+      <c r="I7" s="40"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
@@ -3811,7 +3920,7 @@
       <c r="B8" s="7">
         <v>46088</v>
       </c>
-      <c r="C8" s="53">
+      <c r="C8" s="52">
         <v>46077</v>
       </c>
       <c r="D8" s="21">
@@ -3823,13 +3932,13 @@
       <c r="F8" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="G8" s="84" t="s">
+      <c r="G8" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="69" t="s">
+      <c r="H8" s="68" t="s">
         <v>107</v>
       </c>
-      <c r="I8" s="41">
+      <c r="I8" s="40">
         <v>46077</v>
       </c>
     </row>
@@ -3840,7 +3949,7 @@
       <c r="B9" s="7">
         <v>46077</v>
       </c>
-      <c r="C9" s="53">
+      <c r="C9" s="52">
         <v>46077</v>
       </c>
       <c r="D9" s="21">
@@ -3852,13 +3961,13 @@
       <c r="F9" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="G9" s="84" t="s">
+      <c r="G9" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="69" t="s">
+      <c r="H9" s="68" t="s">
         <v>109</v>
       </c>
-      <c r="I9" s="41">
+      <c r="I9" s="40">
         <v>46077</v>
       </c>
     </row>
@@ -3869,7 +3978,7 @@
       <c r="B10" s="7">
         <v>46065</v>
       </c>
-      <c r="C10" s="53">
+      <c r="C10" s="52">
         <v>46077</v>
       </c>
       <c r="D10" s="21">
@@ -3881,13 +3990,13 @@
       <c r="F10" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="G10" s="84" t="s">
+      <c r="G10" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="69" t="s">
+      <c r="H10" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="I10" s="41">
+      <c r="I10" s="40">
         <v>46065</v>
       </c>
     </row>
@@ -3898,7 +4007,7 @@
       <c r="B11" s="7">
         <v>46064</v>
       </c>
-      <c r="C11" s="53">
+      <c r="C11" s="52">
         <v>46077</v>
       </c>
       <c r="D11" s="21">
@@ -3910,13 +4019,13 @@
       <c r="F11" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="G11" s="84" t="s">
+      <c r="G11" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="69" t="s">
+      <c r="H11" s="68" t="s">
         <v>113</v>
       </c>
-      <c r="I11" s="41">
+      <c r="I11" s="40">
         <v>46077</v>
       </c>
     </row>
@@ -3927,7 +4036,7 @@
       <c r="B12" s="7">
         <v>46063</v>
       </c>
-      <c r="C12" s="53">
+      <c r="C12" s="52">
         <v>46077</v>
       </c>
       <c r="D12" s="21">
@@ -3939,13 +4048,13 @@
       <c r="F12" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="G12" s="84" t="s">
+      <c r="G12" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="H12" s="69" t="s">
+      <c r="H12" s="68" t="s">
         <v>115</v>
       </c>
-      <c r="I12" s="41">
+      <c r="I12" s="40">
         <v>46077</v>
       </c>
     </row>
@@ -3956,7 +4065,7 @@
       <c r="B13" s="7">
         <v>46065</v>
       </c>
-      <c r="C13" s="53">
+      <c r="C13" s="52">
         <v>46077</v>
       </c>
       <c r="D13" s="21">
@@ -3968,13 +4077,13 @@
       <c r="F13" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="G13" s="84" t="s">
+      <c r="G13" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="69" t="s">
+      <c r="H13" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="I13" s="41">
+      <c r="I13" s="40">
         <v>46065</v>
       </c>
     </row>
@@ -3985,7 +4094,7 @@
       <c r="B14" s="7">
         <v>46065</v>
       </c>
-      <c r="C14" s="53">
+      <c r="C14" s="52">
         <v>46077</v>
       </c>
       <c r="D14" s="21">
@@ -3997,13 +4106,13 @@
       <c r="F14" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="G14" s="84" t="s">
+      <c r="G14" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="69" t="s">
+      <c r="H14" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="I14" s="41">
+      <c r="I14" s="40">
         <v>46065</v>
       </c>
     </row>
@@ -4014,7 +4123,7 @@
       <c r="B15" s="7">
         <v>46080</v>
       </c>
-      <c r="C15" s="53">
+      <c r="C15" s="52">
         <v>46077</v>
       </c>
       <c r="D15" s="21">
@@ -4026,13 +4135,13 @@
       <c r="F15" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="G15" s="84" t="s">
+      <c r="G15" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="H15" s="69" t="s">
+      <c r="H15" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="I15" s="41">
+      <c r="I15" s="40">
         <v>46077</v>
       </c>
     </row>
@@ -4043,7 +4152,7 @@
       <c r="B16" s="7">
         <v>46059</v>
       </c>
-      <c r="C16" s="53">
+      <c r="C16" s="52">
         <v>46077</v>
       </c>
       <c r="D16" s="21">
@@ -4055,13 +4164,13 @@
       <c r="F16" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="G16" s="84" t="s">
+      <c r="G16" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="H16" s="69" t="s">
+      <c r="H16" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="I16" s="41">
+      <c r="I16" s="40">
         <v>46059</v>
       </c>
     </row>
@@ -4072,7 +4181,7 @@
       <c r="B17" s="7">
         <v>46077</v>
       </c>
-      <c r="C17" s="53">
+      <c r="C17" s="52">
         <v>46077</v>
       </c>
       <c r="D17" s="21">
@@ -4084,13 +4193,13 @@
       <c r="F17" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="G17" s="84" t="s">
+      <c r="G17" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="H17" s="69" t="s">
+      <c r="H17" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="I17" s="41">
+      <c r="I17" s="40">
         <v>46077</v>
       </c>
     </row>
@@ -4101,7 +4210,7 @@
       <c r="B18" s="7">
         <v>46065</v>
       </c>
-      <c r="C18" s="53">
+      <c r="C18" s="52">
         <v>46077</v>
       </c>
       <c r="D18" s="21">
@@ -4113,13 +4222,13 @@
       <c r="F18" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="G18" s="84" t="s">
+      <c r="G18" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="H18" s="69" t="s">
+      <c r="H18" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="I18" s="41">
+      <c r="I18" s="40">
         <v>46065</v>
       </c>
     </row>
@@ -4130,7 +4239,7 @@
       <c r="B19" s="7">
         <v>46059</v>
       </c>
-      <c r="C19" s="53">
+      <c r="C19" s="52">
         <v>46077</v>
       </c>
       <c r="D19" s="21">
@@ -4142,13 +4251,13 @@
       <c r="F19" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="G19" s="84" t="s">
+      <c r="G19" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="H19" s="69" t="s">
+      <c r="H19" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="I19" s="41">
+      <c r="I19" s="40">
         <v>46059</v>
       </c>
     </row>
@@ -4159,7 +4268,7 @@
       <c r="B20" s="7">
         <v>46062</v>
       </c>
-      <c r="C20" s="53">
+      <c r="C20" s="52">
         <v>46077</v>
       </c>
       <c r="D20" s="21">
@@ -4171,13 +4280,13 @@
       <c r="F20" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="G20" s="84" t="s">
+      <c r="G20" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="H20" s="69" t="s">
+      <c r="H20" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="I20" s="41">
+      <c r="I20" s="40">
         <v>46062</v>
       </c>
     </row>
@@ -4188,7 +4297,7 @@
       <c r="B21" s="7">
         <v>46079</v>
       </c>
-      <c r="C21" s="53">
+      <c r="C21" s="52">
         <v>46077</v>
       </c>
       <c r="D21" s="21">
@@ -4200,13 +4309,13 @@
       <c r="F21" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="G21" s="84" t="s">
+      <c r="G21" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="H21" s="69" t="s">
+      <c r="H21" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="I21" s="41">
+      <c r="I21" s="40">
         <v>46077</v>
       </c>
     </row>
@@ -4217,7 +4326,7 @@
       <c r="B22" s="7">
         <v>46065</v>
       </c>
-      <c r="C22" s="53">
+      <c r="C22" s="52">
         <v>46077</v>
       </c>
       <c r="D22" s="21">
@@ -4229,13 +4338,13 @@
       <c r="F22" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="G22" s="84" t="s">
+      <c r="G22" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="H22" s="69" t="s">
+      <c r="H22" s="68" t="s">
         <v>126</v>
       </c>
-      <c r="I22" s="41">
+      <c r="I22" s="40">
         <v>46077</v>
       </c>
     </row>
@@ -4246,7 +4355,7 @@
       <c r="B23" s="7">
         <v>46064</v>
       </c>
-      <c r="C23" s="53">
+      <c r="C23" s="52">
         <v>46077</v>
       </c>
       <c r="D23" s="21">
@@ -4258,13 +4367,13 @@
       <c r="F23" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G23" s="84" t="s">
+      <c r="G23" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="H23" s="69" t="s">
+      <c r="H23" s="68" t="s">
         <v>128</v>
       </c>
-      <c r="I23" s="41">
+      <c r="I23" s="40">
         <v>46076</v>
       </c>
     </row>
@@ -4275,7 +4384,7 @@
       <c r="B24" s="7">
         <v>46072</v>
       </c>
-      <c r="C24" s="53">
+      <c r="C24" s="52">
         <v>46077</v>
       </c>
       <c r="D24" s="21">
@@ -4287,13 +4396,13 @@
       <c r="F24" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="G24" s="84" t="s">
+      <c r="G24" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="H24" s="69" t="s">
+      <c r="H24" s="68" t="s">
         <v>130</v>
       </c>
-      <c r="I24" s="41">
+      <c r="I24" s="40">
         <v>46077</v>
       </c>
     </row>
@@ -4304,7 +4413,7 @@
       <c r="B25" s="7">
         <v>46087</v>
       </c>
-      <c r="C25" s="53">
+      <c r="C25" s="52">
         <v>46077</v>
       </c>
       <c r="D25" s="21">
@@ -4316,13 +4425,13 @@
       <c r="F25" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="G25" s="84" t="s">
+      <c r="G25" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="H25" s="69" t="s">
+      <c r="H25" s="68" t="s">
         <v>132</v>
       </c>
-      <c r="I25" s="41">
+      <c r="I25" s="40">
         <v>46076</v>
       </c>
     </row>
@@ -4333,7 +4442,7 @@
       <c r="B26" s="7">
         <v>46063</v>
       </c>
-      <c r="C26" s="53">
+      <c r="C26" s="52">
         <v>46077</v>
       </c>
       <c r="D26" s="21">
@@ -4345,13 +4454,13 @@
       <c r="F26" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="G26" s="84" t="s">
+      <c r="G26" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="H26" s="69" t="s">
+      <c r="H26" s="68" t="s">
         <v>134</v>
       </c>
-      <c r="I26" s="41">
+      <c r="I26" s="40">
         <v>46076</v>
       </c>
     </row>
@@ -4362,7 +4471,7 @@
       <c r="B27" s="7">
         <v>46068</v>
       </c>
-      <c r="C27" s="53">
+      <c r="C27" s="52">
         <v>46077</v>
       </c>
       <c r="D27" s="21">
@@ -4374,13 +4483,13 @@
       <c r="F27" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="G27" s="84" t="s">
+      <c r="G27" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="H27" s="69" t="s">
+      <c r="H27" s="68" t="s">
         <v>136</v>
       </c>
-      <c r="I27" s="41">
+      <c r="I27" s="40">
         <v>46076</v>
       </c>
     </row>
@@ -4391,7 +4500,7 @@
       <c r="B28" s="7">
         <v>46066</v>
       </c>
-      <c r="C28" s="53">
+      <c r="C28" s="52">
         <v>46077</v>
       </c>
       <c r="D28" s="21">
@@ -4403,13 +4512,13 @@
       <c r="F28" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="G28" s="84" t="s">
+      <c r="G28" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="H28" s="69" t="s">
+      <c r="H28" s="68" t="s">
         <v>130</v>
       </c>
-      <c r="I28" s="41">
+      <c r="I28" s="40">
         <v>46077</v>
       </c>
     </row>
@@ -4420,7 +4529,7 @@
       <c r="B29" s="7">
         <v>46065</v>
       </c>
-      <c r="C29" s="53">
+      <c r="C29" s="52">
         <v>46077</v>
       </c>
       <c r="D29" s="21">
@@ -4432,13 +4541,13 @@
       <c r="F29" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="G29" s="84" t="s">
+      <c r="G29" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="H29" s="69" t="s">
+      <c r="H29" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="I29" s="41">
+      <c r="I29" s="40">
         <v>46065</v>
       </c>
     </row>
@@ -4449,7 +4558,7 @@
       <c r="B30" s="7">
         <v>46063</v>
       </c>
-      <c r="C30" s="53">
+      <c r="C30" s="52">
         <v>46077</v>
       </c>
       <c r="D30" s="21">
@@ -4461,13 +4570,13 @@
       <c r="F30" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="G30" s="84" t="s">
+      <c r="G30" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="H30" s="69" t="s">
+      <c r="H30" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="I30" s="41">
+      <c r="I30" s="40">
         <v>46077</v>
       </c>
     </row>
@@ -4478,7 +4587,7 @@
       <c r="B31" s="7">
         <v>46065</v>
       </c>
-      <c r="C31" s="53">
+      <c r="C31" s="52">
         <v>46077</v>
       </c>
       <c r="D31" s="21">
@@ -4490,13 +4599,13 @@
       <c r="F31" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="G31" s="84" t="s">
+      <c r="G31" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="H31" s="69" t="s">
+      <c r="H31" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="I31" s="41">
+      <c r="I31" s="40">
         <v>46065</v>
       </c>
     </row>
@@ -4507,7 +4616,7 @@
       <c r="B32" s="7">
         <v>46065</v>
       </c>
-      <c r="C32" s="53">
+      <c r="C32" s="52">
         <v>46077</v>
       </c>
       <c r="D32" s="21">
@@ -4519,13 +4628,13 @@
       <c r="F32" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="G32" s="84" t="s">
+      <c r="G32" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="H32" s="69" t="s">
+      <c r="H32" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="I32" s="41">
+      <c r="I32" s="40">
         <v>46065</v>
       </c>
     </row>
@@ -4536,7 +4645,7 @@
       <c r="B33" s="7">
         <v>46065</v>
       </c>
-      <c r="C33" s="53">
+      <c r="C33" s="52">
         <v>46077</v>
       </c>
       <c r="D33" s="21">
@@ -4548,13 +4657,13 @@
       <c r="F33" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="G33" s="84" t="s">
+      <c r="G33" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="H33" s="69" t="s">
+      <c r="H33" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="I33" s="41">
+      <c r="I33" s="40">
         <v>46065</v>
       </c>
     </row>
@@ -4565,7 +4674,7 @@
       <c r="B34" s="7">
         <v>46065</v>
       </c>
-      <c r="C34" s="53">
+      <c r="C34" s="52">
         <v>46077</v>
       </c>
       <c r="D34" s="21">
@@ -4577,13 +4686,13 @@
       <c r="F34" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="G34" s="84" t="s">
+      <c r="G34" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="H34" s="69" t="s">
+      <c r="H34" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="I34" s="41">
+      <c r="I34" s="40">
         <v>46065</v>
       </c>
     </row>
@@ -4594,7 +4703,7 @@
       <c r="B35" s="7">
         <v>46066</v>
       </c>
-      <c r="C35" s="53">
+      <c r="C35" s="52">
         <v>46077</v>
       </c>
       <c r="D35" s="21">
@@ -4606,13 +4715,13 @@
       <c r="F35" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="G35" s="84" t="s">
+      <c r="G35" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="H35" s="69" t="s">
+      <c r="H35" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="I35" s="41">
+      <c r="I35" s="40">
         <v>46077</v>
       </c>
     </row>
@@ -4623,7 +4732,7 @@
       <c r="B36" s="7">
         <v>46065</v>
       </c>
-      <c r="C36" s="53">
+      <c r="C36" s="52">
         <v>46077</v>
       </c>
       <c r="D36" s="21">
@@ -4635,13 +4744,13 @@
       <c r="F36" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="G36" s="84" t="s">
+      <c r="G36" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="H36" s="69" t="s">
+      <c r="H36" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="I36" s="41">
+      <c r="I36" s="40">
         <v>46065</v>
       </c>
     </row>
@@ -4652,7 +4761,7 @@
       <c r="B37" s="7">
         <v>46065</v>
       </c>
-      <c r="C37" s="53">
+      <c r="C37" s="52">
         <v>46077</v>
       </c>
       <c r="D37" s="21">
@@ -4664,13 +4773,13 @@
       <c r="F37" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="G37" s="84" t="s">
+      <c r="G37" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="H37" s="69" t="s">
+      <c r="H37" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="I37" s="41">
+      <c r="I37" s="40">
         <v>46065</v>
       </c>
     </row>
@@ -4681,7 +4790,7 @@
       <c r="B38" s="7">
         <v>46065</v>
       </c>
-      <c r="C38" s="53">
+      <c r="C38" s="52">
         <v>46077</v>
       </c>
       <c r="D38" s="21">
@@ -4693,13 +4802,13 @@
       <c r="F38" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="G38" s="84" t="s">
+      <c r="G38" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="H38" s="69" t="s">
+      <c r="H38" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="I38" s="41">
+      <c r="I38" s="40">
         <v>46077</v>
       </c>
     </row>
@@ -4710,7 +4819,7 @@
       <c r="B39" s="7">
         <v>46067</v>
       </c>
-      <c r="C39" s="53">
+      <c r="C39" s="52">
         <v>46077</v>
       </c>
       <c r="D39" s="21">
@@ -4722,13 +4831,13 @@
       <c r="F39" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G39" s="84" t="s">
+      <c r="G39" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="H39" s="69" t="s">
+      <c r="H39" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="I39" s="41">
+      <c r="I39" s="40">
         <v>46077</v>
       </c>
     </row>
@@ -4739,7 +4848,7 @@
       <c r="B40" s="7">
         <v>46065</v>
       </c>
-      <c r="C40" s="53">
+      <c r="C40" s="52">
         <v>46077</v>
       </c>
       <c r="D40" s="21">
@@ -4751,13 +4860,13 @@
       <c r="F40" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="G40" s="84" t="s">
+      <c r="G40" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="H40" s="69" t="s">
+      <c r="H40" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="I40" s="41">
+      <c r="I40" s="40">
         <v>46065</v>
       </c>
     </row>
@@ -4768,7 +4877,7 @@
       <c r="B41" s="7">
         <v>46065</v>
       </c>
-      <c r="C41" s="53">
+      <c r="C41" s="52">
         <v>46077</v>
       </c>
       <c r="D41" s="21">
@@ -4780,13 +4889,13 @@
       <c r="F41" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="G41" s="84" t="s">
+      <c r="G41" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="H41" s="69" t="s">
+      <c r="H41" s="68" t="s">
         <v>126</v>
       </c>
-      <c r="I41" s="41">
+      <c r="I41" s="40">
         <v>46077</v>
       </c>
     </row>
@@ -4797,7 +4906,7 @@
       <c r="B42" s="7">
         <v>46065</v>
       </c>
-      <c r="C42" s="53">
+      <c r="C42" s="52">
         <v>46077</v>
       </c>
       <c r="D42" s="21">
@@ -4809,13 +4918,13 @@
       <c r="F42" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="G42" s="84" t="s">
+      <c r="G42" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="H42" s="69" t="s">
+      <c r="H42" s="68" t="s">
         <v>126</v>
       </c>
-      <c r="I42" s="41">
+      <c r="I42" s="40">
         <v>46077</v>
       </c>
     </row>
@@ -4826,7 +4935,7 @@
       <c r="B43" s="7">
         <v>46062</v>
       </c>
-      <c r="C43" s="53">
+      <c r="C43" s="52">
         <v>46077</v>
       </c>
       <c r="D43" s="21">
@@ -4838,13 +4947,13 @@
       <c r="F43" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="G43" s="84" t="s">
+      <c r="G43" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="H43" s="69" t="s">
+      <c r="H43" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="I43" s="41">
+      <c r="I43" s="40">
         <v>46062</v>
       </c>
     </row>
@@ -4855,7 +4964,7 @@
       <c r="B44" s="7">
         <v>46062</v>
       </c>
-      <c r="C44" s="53">
+      <c r="C44" s="52">
         <v>46077</v>
       </c>
       <c r="D44" s="21">
@@ -4867,13 +4976,13 @@
       <c r="F44" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="G44" s="84" t="s">
+      <c r="G44" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="H44" s="69" t="s">
+      <c r="H44" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="I44" s="41">
+      <c r="I44" s="40">
         <v>46062</v>
       </c>
     </row>
@@ -4884,7 +4993,7 @@
       <c r="B45" s="7">
         <v>46090</v>
       </c>
-      <c r="C45" s="53">
+      <c r="C45" s="52">
         <v>46077</v>
       </c>
       <c r="D45" s="21">
@@ -4896,13 +5005,13 @@
       <c r="F45" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="G45" s="84" t="s">
+      <c r="G45" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="H45" s="69" t="s">
+      <c r="H45" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="I45" s="41">
+      <c r="I45" s="40">
         <v>46076</v>
       </c>
     </row>
@@ -4913,7 +5022,7 @@
       <c r="B46" s="7">
         <v>46079</v>
       </c>
-      <c r="C46" s="53">
+      <c r="C46" s="52">
         <v>46077</v>
       </c>
       <c r="D46" s="21">
@@ -4925,13 +5034,13 @@
       <c r="F46" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="G46" s="84" t="s">
+      <c r="G46" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="H46" s="69" t="s">
+      <c r="H46" s="68" t="s">
         <v>136</v>
       </c>
-      <c r="I46" s="41">
+      <c r="I46" s="40">
         <v>46076</v>
       </c>
     </row>
@@ -4942,7 +5051,7 @@
       <c r="B47" s="7">
         <v>46063</v>
       </c>
-      <c r="C47" s="53">
+      <c r="C47" s="52">
         <v>46077</v>
       </c>
       <c r="D47" s="21">
@@ -4954,13 +5063,13 @@
       <c r="F47" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="G47" s="84" t="s">
+      <c r="G47" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="H47" s="69" t="s">
+      <c r="H47" s="68" t="s">
         <v>155</v>
       </c>
-      <c r="I47" s="41">
+      <c r="I47" s="40">
         <v>46076</v>
       </c>
     </row>
@@ -4971,7 +5080,7 @@
       <c r="B48" s="7">
         <v>46065</v>
       </c>
-      <c r="C48" s="53">
+      <c r="C48" s="52">
         <v>46077</v>
       </c>
       <c r="D48" s="21">
@@ -4983,13 +5092,13 @@
       <c r="F48" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="G48" s="84" t="s">
+      <c r="G48" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="H48" s="69" t="s">
+      <c r="H48" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="I48" s="41">
+      <c r="I48" s="40">
         <v>46077</v>
       </c>
     </row>
@@ -5000,7 +5109,7 @@
       <c r="B49" s="7">
         <v>46065</v>
       </c>
-      <c r="C49" s="53">
+      <c r="C49" s="52">
         <v>46077</v>
       </c>
       <c r="D49" s="21">
@@ -5012,13 +5121,13 @@
       <c r="F49" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="G49" s="84" t="s">
+      <c r="G49" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="H49" s="69" t="s">
+      <c r="H49" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="I49" s="41">
+      <c r="I49" s="40">
         <v>46065</v>
       </c>
     </row>
@@ -5029,7 +5138,7 @@
       <c r="B50" s="7">
         <v>46065</v>
       </c>
-      <c r="C50" s="53">
+      <c r="C50" s="52">
         <v>46077</v>
       </c>
       <c r="D50" s="21">
@@ -5041,13 +5150,13 @@
       <c r="F50" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="G50" s="84" t="s">
+      <c r="G50" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="H50" s="69" t="s">
+      <c r="H50" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="I50" s="41">
+      <c r="I50" s="40">
         <v>46065</v>
       </c>
     </row>
@@ -5058,7 +5167,7 @@
       <c r="B51" s="7">
         <v>46065</v>
       </c>
-      <c r="C51" s="53">
+      <c r="C51" s="52">
         <v>46077</v>
       </c>
       <c r="D51" s="21">
@@ -5070,13 +5179,13 @@
       <c r="F51" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="G51" s="84" t="s">
+      <c r="G51" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="H51" s="69" t="s">
+      <c r="H51" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="I51" s="41">
+      <c r="I51" s="40">
         <v>46065</v>
       </c>
     </row>
@@ -5087,7 +5196,7 @@
       <c r="B52" s="7">
         <v>46069</v>
       </c>
-      <c r="C52" s="53">
+      <c r="C52" s="52">
         <v>46077</v>
       </c>
       <c r="D52" s="21">
@@ -5099,13 +5208,13 @@
       <c r="F52" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="G52" s="84" t="s">
+      <c r="G52" s="83" t="s">
         <v>37</v>
       </c>
-      <c r="H52" s="69" t="s">
+      <c r="H52" s="68" t="s">
         <v>161</v>
       </c>
-      <c r="I52" s="41">
+      <c r="I52" s="40">
         <v>46076</v>
       </c>
     </row>
@@ -5116,7 +5225,7 @@
       <c r="B53" s="7">
         <v>46073</v>
       </c>
-      <c r="C53" s="53">
+      <c r="C53" s="52">
         <v>46077</v>
       </c>
       <c r="D53" s="21">
@@ -5128,13 +5237,13 @@
       <c r="F53" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="G53" s="84" t="s">
+      <c r="G53" s="83" t="s">
         <v>37</v>
       </c>
-      <c r="H53" s="69" t="s">
+      <c r="H53" s="68" t="s">
         <v>161</v>
       </c>
-      <c r="I53" s="41">
+      <c r="I53" s="40">
         <v>46076</v>
       </c>
     </row>
@@ -5145,7 +5254,7 @@
       <c r="B54" s="7">
         <v>46073</v>
       </c>
-      <c r="C54" s="53">
+      <c r="C54" s="52">
         <v>46077</v>
       </c>
       <c r="D54" s="21">
@@ -5157,13 +5266,13 @@
       <c r="F54" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="G54" s="84" t="s">
+      <c r="G54" s="83" t="s">
         <v>37</v>
       </c>
-      <c r="H54" s="69" t="s">
+      <c r="H54" s="68" t="s">
         <v>161</v>
       </c>
-      <c r="I54" s="41">
+      <c r="I54" s="40">
         <v>46076</v>
       </c>
     </row>
@@ -5174,7 +5283,7 @@
       <c r="B55" s="7">
         <v>46078</v>
       </c>
-      <c r="C55" s="53">
+      <c r="C55" s="52">
         <v>46077</v>
       </c>
       <c r="D55" s="21">
@@ -5186,13 +5295,13 @@
       <c r="F55" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="G55" s="84" t="s">
+      <c r="G55" s="83" t="s">
         <v>37</v>
       </c>
-      <c r="H55" s="69" t="s">
+      <c r="H55" s="68" t="s">
         <v>161</v>
       </c>
-      <c r="I55" s="41">
+      <c r="I55" s="40">
         <v>46076</v>
       </c>
     </row>
@@ -5203,7 +5312,7 @@
       <c r="B56" s="7">
         <v>46073</v>
       </c>
-      <c r="C56" s="53">
+      <c r="C56" s="52">
         <v>46077</v>
       </c>
       <c r="D56" s="21">
@@ -5215,13 +5324,13 @@
       <c r="F56" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="G56" s="84" t="s">
+      <c r="G56" s="83" t="s">
         <v>37</v>
       </c>
-      <c r="H56" s="69" t="s">
+      <c r="H56" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="I56" s="41">
+      <c r="I56" s="40">
         <v>46073</v>
       </c>
     </row>
@@ -5232,7 +5341,7 @@
       <c r="B57" s="7">
         <v>46072</v>
       </c>
-      <c r="C57" s="53">
+      <c r="C57" s="52">
         <v>46077</v>
       </c>
       <c r="D57" s="21">
@@ -5244,13 +5353,13 @@
       <c r="F57" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="G57" s="84" t="s">
+      <c r="G57" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="H57" s="69" t="s">
+      <c r="H57" s="68" t="s">
         <v>167</v>
       </c>
-      <c r="I57" s="41">
+      <c r="I57" s="40">
         <v>46077</v>
       </c>
     </row>
@@ -5313,7 +5422,7 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="26" t="s">
+      <c r="I1" s="25" t="s">
         <v>8</v>
       </c>
     </row>
@@ -5321,28 +5430,28 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="57">
+      <c r="B2" s="56">
         <v>46063</v>
       </c>
       <c r="C2" s="23">
         <v>46078</v>
       </c>
-      <c r="D2" s="86">
+      <c r="D2" s="21">
         <v>136739463</v>
       </c>
       <c r="E2" s="17">
         <v>3450248000</v>
       </c>
-      <c r="F2" s="85" t="s">
+      <c r="F2" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="G2" s="39" t="s">
         <v>14</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="41">
+      <c r="I2" s="40">
         <v>46063</v>
       </c>
     </row>
@@ -5350,28 +5459,28 @@
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="57">
+      <c r="B3" s="56">
         <v>46087</v>
       </c>
       <c r="C3" s="23">
         <v>46078</v>
       </c>
-      <c r="D3" s="86">
+      <c r="D3" s="21">
         <v>136694861</v>
       </c>
       <c r="E3" s="17">
         <v>3450248571</v>
       </c>
-      <c r="F3" s="85" t="s">
+      <c r="F3" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="G3" s="40" t="s">
+      <c r="G3" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="87" t="s">
+      <c r="H3" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="I3" s="41">
+      <c r="I3" s="40">
         <v>46077</v>
       </c>
     </row>
@@ -5379,28 +5488,28 @@
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="57">
+      <c r="B4" s="56">
         <v>46066</v>
       </c>
       <c r="C4" s="23">
         <v>46078</v>
       </c>
-      <c r="D4" s="86">
+      <c r="D4" s="21">
         <v>136754447</v>
       </c>
       <c r="E4" s="17">
         <v>3450252740</v>
       </c>
-      <c r="F4" s="85" t="s">
+      <c r="F4" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="G4" s="40" t="s">
+      <c r="G4" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="87" t="s">
+      <c r="H4" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="I4" s="41">
+      <c r="I4" s="40">
         <v>46077</v>
       </c>
     </row>
@@ -5408,28 +5517,28 @@
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="57">
+      <c r="B5" s="56">
         <v>46076</v>
       </c>
       <c r="C5" s="23">
         <v>46078</v>
       </c>
-      <c r="D5" s="86">
+      <c r="D5" s="21">
         <v>136708451</v>
       </c>
       <c r="E5" s="17">
         <v>3450249671</v>
       </c>
-      <c r="F5" s="85" t="s">
+      <c r="F5" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="G5" s="40" t="s">
+      <c r="G5" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="87" t="s">
+      <c r="H5" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="I5" s="41">
+      <c r="I5" s="40">
         <v>46073</v>
       </c>
     </row>
@@ -5437,28 +5546,28 @@
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="88">
+      <c r="B6" s="84">
         <v>46073</v>
       </c>
       <c r="C6" s="23">
         <v>46078</v>
       </c>
-      <c r="D6" s="86">
+      <c r="D6" s="21">
         <v>136698193</v>
       </c>
       <c r="E6" s="17">
         <v>3450248824</v>
       </c>
-      <c r="F6" s="85" t="s">
+      <c r="F6" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="G6" s="40" t="s">
+      <c r="G6" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="87" t="s">
+      <c r="H6" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="I6" s="41">
+      <c r="I6" s="40">
         <v>46077</v>
       </c>
     </row>
@@ -5466,28 +5575,28 @@
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="57">
+      <c r="B7" s="56">
         <v>46091</v>
       </c>
       <c r="C7" s="23">
         <v>46078</v>
       </c>
-      <c r="D7" s="86">
+      <c r="D7" s="21">
         <v>136751455</v>
       </c>
       <c r="E7" s="17">
         <v>3450252510</v>
       </c>
-      <c r="F7" s="85" t="s">
+      <c r="F7" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="G7" s="40" t="s">
+      <c r="G7" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="87" t="s">
+      <c r="H7" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="I7" s="41">
+      <c r="I7" s="40">
         <v>46077</v>
       </c>
     </row>
@@ -5495,28 +5604,28 @@
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="57">
+      <c r="B8" s="56">
         <v>46070</v>
       </c>
       <c r="C8" s="23">
         <v>46078</v>
       </c>
-      <c r="D8" s="86">
+      <c r="D8" s="21">
         <v>136742229</v>
       </c>
       <c r="E8" s="17">
         <v>3450251728</v>
       </c>
-      <c r="F8" s="85" t="s">
+      <c r="F8" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="G8" s="40" t="s">
+      <c r="G8" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="87" t="s">
+      <c r="H8" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="I8" s="41">
+      <c r="I8" s="40">
         <v>46077</v>
       </c>
     </row>
@@ -5524,28 +5633,28 @@
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="57">
+      <c r="B9" s="56">
         <v>46063</v>
       </c>
       <c r="C9" s="23">
         <v>46078</v>
       </c>
-      <c r="D9" s="86">
+      <c r="D9" s="21">
         <v>136740126</v>
       </c>
       <c r="E9" s="17">
         <v>3450247361</v>
       </c>
-      <c r="F9" s="85" t="s">
+      <c r="F9" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="G9" s="40" t="s">
+      <c r="G9" s="39" t="s">
         <v>14</v>
       </c>
       <c r="H9" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="41">
+      <c r="I9" s="40">
         <v>46063</v>
       </c>
     </row>
@@ -5553,28 +5662,28 @@
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="57">
+      <c r="B10" s="56">
         <v>46063</v>
       </c>
       <c r="C10" s="23">
         <v>46078</v>
       </c>
-      <c r="D10" s="86">
+      <c r="D10" s="21">
         <v>136740300</v>
       </c>
       <c r="E10" s="17">
         <v>3450247240</v>
       </c>
-      <c r="F10" s="85" t="s">
+      <c r="F10" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="G10" s="40" t="s">
+      <c r="G10" s="39" t="s">
         <v>14</v>
       </c>
       <c r="H10" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I10" s="41">
+      <c r="I10" s="40">
         <v>46063</v>
       </c>
     </row>
@@ -5582,28 +5691,28 @@
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="57">
+      <c r="B11" s="56">
         <v>46066</v>
       </c>
       <c r="C11" s="23">
         <v>46078</v>
       </c>
-      <c r="D11" s="86">
+      <c r="D11" s="21">
         <v>136751006</v>
       </c>
       <c r="E11" s="17">
         <v>3450252476</v>
       </c>
-      <c r="F11" s="85" t="s">
+      <c r="F11" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="G11" s="40" t="s">
+      <c r="G11" s="39" t="s">
         <v>14</v>
       </c>
       <c r="H11" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I11" s="41">
+      <c r="I11" s="40">
         <v>46066</v>
       </c>
     </row>
@@ -5611,28 +5720,28 @@
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="57">
+      <c r="B12" s="56">
         <v>46079</v>
       </c>
       <c r="C12" s="23">
         <v>46078</v>
       </c>
-      <c r="D12" s="86">
+      <c r="D12" s="21">
         <v>136755188</v>
       </c>
       <c r="E12" s="17">
         <v>3450252850</v>
       </c>
-      <c r="F12" s="85" t="s">
+      <c r="F12" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="G12" s="40" t="s">
+      <c r="G12" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="89" t="s">
+      <c r="H12" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="I12" s="41">
+      <c r="I12" s="40">
         <v>46077</v>
       </c>
     </row>
@@ -5640,28 +5749,28 @@
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="57">
+      <c r="B13" s="56">
         <v>46077</v>
       </c>
       <c r="C13" s="23">
         <v>46078</v>
       </c>
-      <c r="D13" s="86">
+      <c r="D13" s="21">
         <v>136757699</v>
       </c>
       <c r="E13" s="17">
         <v>3450253015</v>
       </c>
-      <c r="F13" s="85" t="s">
+      <c r="F13" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="G13" s="40" t="s">
+      <c r="G13" s="39" t="s">
         <v>22</v>
       </c>
       <c r="H13" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="I13" s="41">
+      <c r="I13" s="40">
         <v>46078</v>
       </c>
     </row>
@@ -5669,28 +5778,28 @@
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="57">
+      <c r="B14" s="56">
         <v>46066</v>
       </c>
       <c r="C14" s="23">
         <v>46078</v>
       </c>
-      <c r="D14" s="86">
+      <c r="D14" s="21">
         <v>136762893</v>
       </c>
       <c r="E14" s="17">
         <v>3450253477</v>
       </c>
-      <c r="F14" s="85" t="s">
+      <c r="F14" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="G14" s="40" t="s">
+      <c r="G14" s="39" t="s">
         <v>14</v>
       </c>
       <c r="H14" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="41">
+      <c r="I14" s="40">
         <v>46066</v>
       </c>
     </row>
@@ -5698,28 +5807,28 @@
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="57">
+      <c r="B15" s="56">
         <v>46064</v>
       </c>
       <c r="C15" s="23">
         <v>46078</v>
       </c>
-      <c r="D15" s="86">
+      <c r="D15" s="21">
         <v>136705225</v>
       </c>
       <c r="E15" s="17">
         <v>3450249517</v>
       </c>
-      <c r="F15" s="85" t="s">
+      <c r="F15" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="G15" s="40" t="s">
+      <c r="G15" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H15" s="89" t="s">
+      <c r="H15" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="I15" s="41">
+      <c r="I15" s="40">
         <v>46077</v>
       </c>
     </row>
@@ -5727,28 +5836,28 @@
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="57">
+      <c r="B16" s="56">
         <v>46063</v>
       </c>
       <c r="C16" s="23">
         <v>46078</v>
       </c>
-      <c r="D16" s="86">
+      <c r="D16" s="21">
         <v>136739201</v>
       </c>
       <c r="E16" s="17">
         <v>3450248384</v>
       </c>
-      <c r="F16" s="85" t="s">
+      <c r="F16" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="G16" s="40" t="s">
+      <c r="G16" s="39" t="s">
         <v>14</v>
       </c>
       <c r="H16" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I16" s="41">
+      <c r="I16" s="40">
         <v>46063</v>
       </c>
     </row>
@@ -5756,28 +5865,28 @@
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="57">
+      <c r="B17" s="56">
         <v>46063</v>
       </c>
       <c r="C17" s="23">
         <v>46078</v>
       </c>
-      <c r="D17" s="86">
+      <c r="D17" s="21">
         <v>136739218</v>
       </c>
       <c r="E17" s="17">
         <v>3450248087</v>
       </c>
-      <c r="F17" s="85" t="s">
+      <c r="F17" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="G17" s="58" t="s">
+      <c r="G17" s="57" t="s">
         <v>14</v>
       </c>
       <c r="H17" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I17" s="41">
+      <c r="I17" s="40">
         <v>46063</v>
       </c>
     </row>
@@ -5785,28 +5894,28 @@
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="57">
+      <c r="B18" s="56">
         <v>46065</v>
       </c>
       <c r="C18" s="23">
         <v>46078</v>
       </c>
-      <c r="D18" s="86">
+      <c r="D18" s="21">
         <v>136723533</v>
       </c>
       <c r="E18" s="17">
         <v>3450250276</v>
       </c>
-      <c r="F18" s="85" t="s">
+      <c r="F18" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="G18" s="40" t="s">
+      <c r="G18" s="39" t="s">
         <v>37</v>
       </c>
       <c r="H18" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="I18" s="41">
+      <c r="I18" s="40">
         <v>46077</v>
       </c>
     </row>
@@ -5814,28 +5923,28 @@
       <c r="A19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="57">
+      <c r="B19" s="56">
         <v>46075</v>
       </c>
       <c r="C19" s="23">
         <v>46078</v>
       </c>
-      <c r="D19" s="86">
+      <c r="D19" s="21">
         <v>136806525</v>
       </c>
       <c r="E19" s="17">
         <v>3450256030</v>
       </c>
-      <c r="F19" s="85" t="s">
+      <c r="F19" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="G19" s="40" t="s">
+      <c r="G19" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H19" s="87" t="s">
+      <c r="H19" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="I19" s="41">
+      <c r="I19" s="40">
         <v>46078</v>
       </c>
     </row>
@@ -5843,28 +5952,28 @@
       <c r="A20" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="57">
+      <c r="B20" s="56">
         <v>46072</v>
       </c>
       <c r="C20" s="23">
         <v>46078</v>
       </c>
-      <c r="D20" s="86">
+      <c r="D20" s="21">
         <v>136808710</v>
       </c>
       <c r="E20" s="17">
         <v>3450256360</v>
       </c>
-      <c r="F20" s="85" t="s">
+      <c r="F20" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="G20" s="40" t="s">
+      <c r="G20" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H20" s="93" t="s">
+      <c r="H20" s="88" t="s">
         <v>193</v>
       </c>
-      <c r="I20" s="41">
+      <c r="I20" s="40">
         <v>46078</v>
       </c>
     </row>
@@ -5872,28 +5981,28 @@
       <c r="A21" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="57">
+      <c r="B21" s="56">
         <v>46065</v>
       </c>
       <c r="C21" s="23">
         <v>46078</v>
       </c>
-      <c r="D21" s="86">
+      <c r="D21" s="21">
         <v>136730296</v>
       </c>
       <c r="E21" s="17">
         <v>3450250980</v>
       </c>
-      <c r="F21" s="85" t="s">
+      <c r="F21" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="G21" s="90" t="s">
+      <c r="G21" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="H21" s="87" t="s">
+      <c r="H21" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="I21" s="92">
+      <c r="I21" s="87">
         <v>46077</v>
       </c>
     </row>
@@ -5907,22 +6016,22 @@
       <c r="C22" s="23">
         <v>46078</v>
       </c>
-      <c r="D22" s="86">
+      <c r="D22" s="21">
         <v>136841851</v>
       </c>
       <c r="E22" s="17">
         <v>3450258966</v>
       </c>
-      <c r="F22" s="85" t="s">
+      <c r="F22" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="G22" s="90" t="s">
+      <c r="G22" s="85" t="s">
         <v>14</v>
       </c>
-      <c r="H22" s="87" t="s">
+      <c r="H22" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="92">
+      <c r="I22" s="87">
         <v>46076</v>
       </c>
     </row>
@@ -5936,22 +6045,22 @@
       <c r="C23" s="23">
         <v>46078</v>
       </c>
-      <c r="D23" s="86">
+      <c r="D23" s="21">
         <v>136832984</v>
       </c>
       <c r="E23" s="17">
         <v>3450258438</v>
       </c>
-      <c r="F23" s="85" t="s">
+      <c r="F23" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="G23" s="90" t="s">
+      <c r="G23" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="H23" s="87" t="s">
+      <c r="H23" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="I23" s="92">
+      <c r="I23" s="87">
         <v>46078</v>
       </c>
     </row>
@@ -5965,22 +6074,22 @@
       <c r="C24" s="23">
         <v>46078</v>
       </c>
-      <c r="D24" s="86">
+      <c r="D24" s="21">
         <v>136809532</v>
       </c>
       <c r="E24" s="17">
         <v>3450256458</v>
       </c>
-      <c r="F24" s="85" t="s">
+      <c r="F24" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="G24" s="90" t="s">
+      <c r="G24" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="H24" s="87" t="s">
+      <c r="H24" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="I24" s="92">
+      <c r="I24" s="87">
         <v>46078</v>
       </c>
     </row>
@@ -5994,22 +6103,22 @@
       <c r="C25" s="23">
         <v>46078</v>
       </c>
-      <c r="D25" s="86">
+      <c r="D25" s="21">
         <v>136798798</v>
       </c>
       <c r="E25" s="17">
         <v>3450255270</v>
       </c>
-      <c r="F25" s="85" t="s">
+      <c r="F25" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="G25" s="91" t="s">
+      <c r="G25" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="H25" s="87" t="s">
+      <c r="H25" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I25" s="92">
+      <c r="I25" s="87">
         <v>46072</v>
       </c>
     </row>
@@ -6023,22 +6132,22 @@
       <c r="C26" s="23">
         <v>46078</v>
       </c>
-      <c r="D26" s="86">
+      <c r="D26" s="21">
         <v>136821098</v>
       </c>
       <c r="E26" s="17">
         <v>3450257305</v>
       </c>
-      <c r="F26" s="85" t="s">
+      <c r="F26" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="G26" s="90" t="s">
+      <c r="G26" s="85" t="s">
         <v>14</v>
       </c>
-      <c r="H26" s="87" t="s">
+      <c r="H26" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I26" s="92">
+      <c r="I26" s="87">
         <v>46073</v>
       </c>
     </row>
@@ -6052,22 +6161,22 @@
       <c r="C27" s="23">
         <v>46078</v>
       </c>
-      <c r="D27" s="86">
+      <c r="D27" s="21">
         <v>136786742</v>
       </c>
       <c r="E27" s="17">
         <v>3450254478</v>
       </c>
-      <c r="F27" s="85" t="s">
+      <c r="F27" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="G27" s="90" t="s">
+      <c r="G27" s="85" t="s">
         <v>74</v>
       </c>
-      <c r="H27" s="87" t="s">
+      <c r="H27" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="I27" s="92">
+      <c r="I27" s="87">
         <v>46071</v>
       </c>
     </row>
@@ -6081,22 +6190,22 @@
       <c r="C28" s="23">
         <v>46078</v>
       </c>
-      <c r="D28" s="86">
+      <c r="D28" s="21">
         <v>136784554</v>
       </c>
       <c r="E28" s="17">
         <v>3450254269</v>
       </c>
-      <c r="F28" s="85" t="s">
+      <c r="F28" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="G28" s="90" t="s">
+      <c r="G28" s="85" t="s">
         <v>14</v>
       </c>
-      <c r="H28" s="87" t="s">
+      <c r="H28" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I28" s="92">
+      <c r="I28" s="87">
         <v>46071</v>
       </c>
     </row>
@@ -6110,22 +6219,22 @@
       <c r="C29" s="23">
         <v>46078</v>
       </c>
-      <c r="D29" s="86">
+      <c r="D29" s="21">
         <v>136799830</v>
       </c>
       <c r="E29" s="17">
         <v>3450255435</v>
       </c>
-      <c r="F29" s="85" t="s">
+      <c r="F29" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="G29" s="91" t="s">
+      <c r="G29" s="86" t="s">
         <v>14</v>
       </c>
       <c r="H29" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I29" s="92">
+      <c r="I29" s="87">
         <v>46072</v>
       </c>
     </row>
@@ -6139,22 +6248,22 @@
       <c r="C30" s="23">
         <v>46078</v>
       </c>
-      <c r="D30" s="86">
+      <c r="D30" s="21">
         <v>136803511</v>
       </c>
       <c r="E30" s="17">
         <v>3450255765</v>
       </c>
-      <c r="F30" s="85" t="s">
+      <c r="F30" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="G30" s="91" t="s">
+      <c r="G30" s="86" t="s">
         <v>14</v>
       </c>
       <c r="H30" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I30" s="92">
+      <c r="I30" s="87">
         <v>46072</v>
       </c>
     </row>
@@ -6168,22 +6277,22 @@
       <c r="C31" s="23">
         <v>46078</v>
       </c>
-      <c r="D31" s="86">
+      <c r="D31" s="21">
         <v>136784744</v>
       </c>
       <c r="E31" s="17">
         <v>3450254270</v>
       </c>
-      <c r="F31" s="85" t="s">
+      <c r="F31" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="G31" s="58" t="s">
+      <c r="G31" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="H31" s="30" t="s">
+      <c r="H31" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="I31" s="41">
+      <c r="I31" s="40">
         <v>46071</v>
       </c>
     </row>
@@ -6197,22 +6306,22 @@
       <c r="C32" s="23">
         <v>46078</v>
       </c>
-      <c r="D32" s="86">
+      <c r="D32" s="21">
         <v>136798825</v>
       </c>
       <c r="E32" s="17">
         <v>3450251838</v>
       </c>
-      <c r="F32" s="85" t="s">
+      <c r="F32" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="G32" s="58" t="s">
+      <c r="G32" s="57" t="s">
         <v>14</v>
       </c>
       <c r="H32" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I32" s="41">
+      <c r="I32" s="40">
         <v>46066</v>
       </c>
     </row>
@@ -6226,22 +6335,22 @@
       <c r="C33" s="23">
         <v>46078</v>
       </c>
-      <c r="D33" s="86">
+      <c r="D33" s="21">
         <v>136791856</v>
       </c>
       <c r="E33" s="17">
         <v>3450254731</v>
       </c>
-      <c r="F33" s="85" t="s">
+      <c r="F33" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="G33" s="58" t="s">
+      <c r="G33" s="57" t="s">
         <v>14</v>
       </c>
       <c r="H33" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I33" s="41">
+      <c r="I33" s="40">
         <v>46072</v>
       </c>
     </row>
@@ -6255,22 +6364,22 @@
       <c r="C34" s="23">
         <v>46078</v>
       </c>
-      <c r="D34" s="86">
+      <c r="D34" s="21">
         <v>136795898</v>
       </c>
       <c r="E34" s="17">
         <v>3450254951</v>
       </c>
-      <c r="F34" s="85" t="s">
+      <c r="F34" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="G34" s="58" t="s">
+      <c r="G34" s="57" t="s">
         <v>14</v>
       </c>
       <c r="H34" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I34" s="41">
+      <c r="I34" s="40">
         <v>46072</v>
       </c>
     </row>
@@ -6284,22 +6393,22 @@
       <c r="C35" s="23">
         <v>46078</v>
       </c>
-      <c r="D35" s="86">
+      <c r="D35" s="21">
         <v>136801483</v>
       </c>
       <c r="E35" s="17">
         <v>3450255589</v>
       </c>
-      <c r="F35" s="85" t="s">
+      <c r="F35" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="G35" s="58" t="s">
+      <c r="G35" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="H35" s="87" t="s">
+      <c r="H35" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I35" s="41">
+      <c r="I35" s="40">
         <v>46078</v>
       </c>
     </row>
@@ -6310,9 +6419,9 @@
       <c r="D36" s="21"/>
       <c r="E36" s="17"/>
       <c r="F36" s="11"/>
-      <c r="G36" s="58"/>
+      <c r="G36" s="57"/>
       <c r="H36" s="12"/>
-      <c r="I36" s="41"/>
+      <c r="I36" s="40"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
@@ -6338,647 +6447,883 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BF216D7-F2B3-4C54-A7B9-7048B06C2C75}">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26" style="16" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="29.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="36.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="47" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="22"/>
+      <c r="A2" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="40">
+        <v>46066</v>
+      </c>
+      <c r="C2" s="40">
+        <v>46079</v>
+      </c>
+      <c r="D2" s="91">
+        <v>136798731</v>
+      </c>
+      <c r="E2" s="17">
+        <v>3450252058</v>
+      </c>
+      <c r="F2" s="89" t="s">
+        <v>213</v>
+      </c>
+      <c r="G2" s="57" t="s">
+        <v>52</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="I2" s="40">
+        <v>46066</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="22"/>
+      <c r="A3" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="40">
+        <v>46065</v>
+      </c>
+      <c r="C3" s="40">
+        <v>46079</v>
+      </c>
+      <c r="D3" s="91">
+        <v>136722239</v>
+      </c>
+      <c r="E3" s="17">
+        <v>3450250177</v>
+      </c>
+      <c r="F3" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="G3" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="I3" s="40">
+        <v>46079</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="22"/>
+      <c r="A4" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="40">
+        <v>46065</v>
+      </c>
+      <c r="C4" s="40">
+        <v>46079</v>
+      </c>
+      <c r="D4" s="91">
+        <v>136731087</v>
+      </c>
+      <c r="E4" s="17">
+        <v>3450251046</v>
+      </c>
+      <c r="F4" s="89" t="s">
+        <v>217</v>
+      </c>
+      <c r="G4" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="90" t="s">
+        <v>218</v>
+      </c>
+      <c r="I4" s="40">
+        <v>46077</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="22"/>
+      <c r="A5" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="40">
+        <v>46092</v>
+      </c>
+      <c r="C5" s="40">
+        <v>46079</v>
+      </c>
+      <c r="D5" s="91">
+        <v>136736113</v>
+      </c>
+      <c r="E5" s="17">
+        <v>3450251464</v>
+      </c>
+      <c r="F5" s="89" t="s">
+        <v>219</v>
+      </c>
+      <c r="G5" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="90" t="s">
+        <v>220</v>
+      </c>
+      <c r="I5" s="40">
+        <v>46077</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="22"/>
+      <c r="A6" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="40">
+        <v>46073</v>
+      </c>
+      <c r="C6" s="40">
+        <v>46079</v>
+      </c>
+      <c r="D6" s="91">
+        <v>136728596</v>
+      </c>
+      <c r="E6" s="17">
+        <v>3450250815</v>
+      </c>
+      <c r="F6" s="89" t="s">
+        <v>221</v>
+      </c>
+      <c r="G6" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="90" t="s">
+        <v>136</v>
+      </c>
+      <c r="I6" s="40">
+        <v>46077</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="22"/>
+      <c r="A7" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="40">
+        <v>46067</v>
+      </c>
+      <c r="C7" s="40">
+        <v>46079</v>
+      </c>
+      <c r="D7" s="91">
+        <v>136793825</v>
+      </c>
+      <c r="E7" s="17">
+        <v>3450253521</v>
+      </c>
+      <c r="F7" s="89" t="s">
+        <v>222</v>
+      </c>
+      <c r="G7" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="40">
+        <v>46067</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="22"/>
+      <c r="A8" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="40">
+        <v>46072</v>
+      </c>
+      <c r="C8" s="40">
+        <v>46079</v>
+      </c>
+      <c r="D8" s="91">
+        <v>136803786</v>
+      </c>
+      <c r="E8" s="17">
+        <v>3450255798</v>
+      </c>
+      <c r="F8" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="G8" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="40">
+        <v>46072</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="22"/>
+      <c r="A9" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="40">
+        <v>46072</v>
+      </c>
+      <c r="C9" s="40">
+        <v>46079</v>
+      </c>
+      <c r="D9" s="91">
+        <v>136791849</v>
+      </c>
+      <c r="E9" s="17">
+        <v>3450254720</v>
+      </c>
+      <c r="F9" s="89" t="s">
+        <v>224</v>
+      </c>
+      <c r="G9" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="40">
+        <v>46072</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="22"/>
+      <c r="A10" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="40">
+        <v>46071</v>
+      </c>
+      <c r="C10" s="40">
+        <v>46079</v>
+      </c>
+      <c r="D10" s="91">
+        <v>136781844</v>
+      </c>
+      <c r="E10" s="17">
+        <v>3450254093</v>
+      </c>
+      <c r="F10" s="89" t="s">
+        <v>225</v>
+      </c>
+      <c r="G10" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="40">
+        <v>46071</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="22"/>
+      <c r="A11" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="40">
+        <v>46072</v>
+      </c>
+      <c r="C11" s="40">
+        <v>46079</v>
+      </c>
+      <c r="D11" s="91">
+        <v>136804304</v>
+      </c>
+      <c r="E11" s="17">
+        <v>3450255842</v>
+      </c>
+      <c r="F11" s="89" t="s">
+        <v>226</v>
+      </c>
+      <c r="G11" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="I11" s="40">
+        <v>46072</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="22"/>
+      <c r="A12" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="40">
+        <v>46072</v>
+      </c>
+      <c r="C12" s="40">
+        <v>46079</v>
+      </c>
+      <c r="D12" s="91">
+        <v>136798866</v>
+      </c>
+      <c r="E12" s="17">
+        <v>3450255303</v>
+      </c>
+      <c r="F12" s="89" t="s">
+        <v>228</v>
+      </c>
+      <c r="G12" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="40">
+        <v>46072</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="22"/>
+      <c r="A13" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="40">
+        <v>46071</v>
+      </c>
+      <c r="C13" s="40">
+        <v>46079</v>
+      </c>
+      <c r="D13" s="91">
+        <v>136787620</v>
+      </c>
+      <c r="E13" s="17">
+        <v>3450254577</v>
+      </c>
+      <c r="F13" s="89" t="s">
+        <v>229</v>
+      </c>
+      <c r="G13" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="I13" s="40">
+        <v>46071</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="22"/>
+      <c r="A14" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="40">
+        <v>46066</v>
+      </c>
+      <c r="C14" s="40">
+        <v>46079</v>
+      </c>
+      <c r="D14" s="91">
+        <v>136756475</v>
+      </c>
+      <c r="E14" s="17">
+        <v>3450252960</v>
+      </c>
+      <c r="F14" s="89" t="s">
+        <v>230</v>
+      </c>
+      <c r="G14" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" s="90" t="s">
+        <v>171</v>
+      </c>
+      <c r="I14" s="40">
+        <v>46073</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="22"/>
+      <c r="A15" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="40">
+        <v>46073</v>
+      </c>
+      <c r="C15" s="40">
+        <v>46079</v>
+      </c>
+      <c r="D15" s="91">
+        <v>136821256</v>
+      </c>
+      <c r="E15" s="17">
+        <v>3450257360</v>
+      </c>
+      <c r="F15" s="89" t="s">
+        <v>163</v>
+      </c>
+      <c r="G15" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="I15" s="40">
+        <v>46073</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="22"/>
+      <c r="A16" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="40">
+        <v>46073</v>
+      </c>
+      <c r="C16" s="40">
+        <v>46079</v>
+      </c>
+      <c r="D16" s="91">
+        <v>136815577</v>
+      </c>
+      <c r="E16" s="17">
+        <v>3450256645</v>
+      </c>
+      <c r="F16" s="89" t="s">
+        <v>232</v>
+      </c>
+      <c r="G16" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="I16" s="40">
+        <v>46073</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="22"/>
+      <c r="A17" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="40">
+        <v>46073</v>
+      </c>
+      <c r="C17" s="40">
+        <v>46079</v>
+      </c>
+      <c r="D17" s="91">
+        <v>136831227</v>
+      </c>
+      <c r="E17" s="17">
+        <v>3450258262</v>
+      </c>
+      <c r="F17" s="89" t="s">
+        <v>234</v>
+      </c>
+      <c r="G17" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="I17" s="40">
+        <v>46073</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="22"/>
+      <c r="A18" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="40">
+        <v>46073</v>
+      </c>
+      <c r="C18" s="40">
+        <v>46079</v>
+      </c>
+      <c r="D18" s="91">
+        <v>136828937</v>
+      </c>
+      <c r="E18" s="17">
+        <v>3450258086</v>
+      </c>
+      <c r="F18" s="89" t="s">
+        <v>236</v>
+      </c>
+      <c r="G18" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="40">
+        <v>46073</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="22"/>
+      <c r="A19" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="40">
+        <v>46073</v>
+      </c>
+      <c r="C19" s="40">
+        <v>46079</v>
+      </c>
+      <c r="D19" s="91">
+        <v>136823111</v>
+      </c>
+      <c r="E19" s="17">
+        <v>3450257492</v>
+      </c>
+      <c r="F19" s="89" t="s">
+        <v>237</v>
+      </c>
+      <c r="G19" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="40">
+        <v>46073</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="22"/>
+      <c r="A20" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="40">
+        <v>46073</v>
+      </c>
+      <c r="C20" s="40">
+        <v>46079</v>
+      </c>
+      <c r="D20" s="91">
+        <v>136823219</v>
+      </c>
+      <c r="E20" s="17">
+        <v>3450257525</v>
+      </c>
+      <c r="F20" s="89" t="s">
+        <v>238</v>
+      </c>
+      <c r="G20" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="40">
+        <v>46073</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="9"/>
+      <c r="A21" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="40">
+        <v>46073</v>
+      </c>
+      <c r="C21" s="40">
+        <v>46079</v>
+      </c>
+      <c r="D21" s="91">
+        <v>136823783</v>
+      </c>
+      <c r="E21" s="17">
+        <v>3450257570</v>
+      </c>
+      <c r="F21" s="89" t="s">
+        <v>239</v>
+      </c>
+      <c r="G21" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" s="40">
+        <v>46073</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="9"/>
+      <c r="A22" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="40">
+        <v>46101</v>
+      </c>
+      <c r="C22" s="40">
+        <v>46079</v>
+      </c>
+      <c r="D22" s="91">
+        <v>136832828</v>
+      </c>
+      <c r="E22" s="17">
+        <v>3450258405</v>
+      </c>
+      <c r="F22" s="89" t="s">
+        <v>240</v>
+      </c>
+      <c r="G22" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="I22" s="40">
+        <v>46073</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="9"/>
+      <c r="A23" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="40">
+        <v>46077</v>
+      </c>
+      <c r="C23" s="40">
+        <v>46079</v>
+      </c>
+      <c r="D23" s="91">
+        <v>136878558</v>
+      </c>
+      <c r="E23" s="17">
+        <v>3450261331</v>
+      </c>
+      <c r="F23" s="89" t="s">
+        <v>242</v>
+      </c>
+      <c r="G23" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H23" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="I23" s="40">
+        <v>46078</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="9"/>
+      <c r="A24" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="40">
+        <v>46073</v>
+      </c>
+      <c r="C24" s="40">
+        <v>46079</v>
+      </c>
+      <c r="D24" s="91">
+        <v>136831744</v>
+      </c>
+      <c r="E24" s="17">
+        <v>3450258317</v>
+      </c>
+      <c r="F24" s="89" t="s">
+        <v>244</v>
+      </c>
+      <c r="G24" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H24" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="I24" s="40">
+        <v>46078</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="9"/>
+      <c r="A25" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="40">
+        <v>46073</v>
+      </c>
+      <c r="C25" s="40">
+        <v>46079</v>
+      </c>
+      <c r="D25" s="91">
+        <v>136833555</v>
+      </c>
+      <c r="E25" s="17">
+        <v>3450258504</v>
+      </c>
+      <c r="F25" s="89" t="s">
+        <v>245</v>
+      </c>
+      <c r="G25" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="40">
+        <v>46073</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="9"/>
+      <c r="A26" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="40">
+        <v>46077</v>
+      </c>
+      <c r="C26" s="40">
+        <v>46079</v>
+      </c>
+      <c r="D26" s="91">
+        <v>136872045</v>
+      </c>
+      <c r="E26" s="17">
+        <v>3450261386</v>
+      </c>
+      <c r="F26" s="89" t="s">
+        <v>246</v>
+      </c>
+      <c r="G26" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="40">
+        <v>46077</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="9"/>
+      <c r="A27" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="40">
+        <v>46077</v>
+      </c>
+      <c r="C27" s="40">
+        <v>46079</v>
+      </c>
+      <c r="D27" s="91">
+        <v>136860566</v>
+      </c>
+      <c r="E27" s="17">
+        <v>3450260429</v>
+      </c>
+      <c r="F27" s="89" t="s">
+        <v>247</v>
+      </c>
+      <c r="G27" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" s="40">
+        <v>46077</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="9"/>
+      <c r="A28" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="40">
+        <v>46065</v>
+      </c>
+      <c r="C28" s="40">
+        <v>46079</v>
+      </c>
+      <c r="D28" s="91">
+        <v>136821297</v>
+      </c>
+      <c r="E28" s="17">
+        <v>3450249440</v>
+      </c>
+      <c r="F28" s="89" t="s">
+        <v>248</v>
+      </c>
+      <c r="G28" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I28" s="40">
+        <v>46065</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="9"/>
+      <c r="A29" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="40">
+        <v>46073</v>
+      </c>
+      <c r="C29" s="40">
+        <v>46079</v>
+      </c>
+      <c r="D29" s="91">
+        <v>136833725</v>
+      </c>
+      <c r="E29" s="17">
+        <v>3450258526</v>
+      </c>
+      <c r="F29" s="89" t="s">
+        <v>245</v>
+      </c>
+      <c r="G29" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I29" s="40">
+        <v>46073</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="9"/>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="9"/>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="9"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="6"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="6"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="9"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="6"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="9"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="6"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="9"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="6"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="9"/>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="6"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="9"/>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="6"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="9"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="6"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="9"/>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="6"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="9"/>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="6"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="9"/>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="6"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="9"/>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="6"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="9"/>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="6"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="9"/>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="6"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="9"/>
-    </row>
-    <row r="47" spans="1:8">
-      <c r="A47" s="6"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="9"/>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="6"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="9"/>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="6"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="9"/>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="6"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="9"/>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="6"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="9"/>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="6"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="9"/>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="6"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="9"/>
-    </row>
-    <row r="54" spans="1:8">
-      <c r="A54" s="6"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="9"/>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="6"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="9"/>
+      <c r="A30" s="39"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A29" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G30" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7054,7 +7399,7 @@
       <c r="F3" s="11"/>
       <c r="G3" s="19"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="31"/>
+      <c r="I3" s="30"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -7087,8 +7432,8 @@
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="20"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="29"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="28"/>
       <c r="G6" s="6"/>
       <c r="H6" s="9"/>
       <c r="I6" s="22"/>
@@ -7618,7 +7963,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="37" t="s">
+      <c r="H1" s="36" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -7634,8 +7979,8 @@
       <c r="D2" s="21"/>
       <c r="E2" s="17"/>
       <c r="F2" s="18"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="32"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="31"/>
       <c r="I2" s="22"/>
     </row>
     <row r="3" spans="1:9">
@@ -7647,8 +7992,8 @@
       <c r="D3" s="21"/>
       <c r="E3" s="17"/>
       <c r="F3" s="18"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="32"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="31"/>
       <c r="I3" s="22"/>
     </row>
     <row r="4" spans="1:9">
@@ -7660,8 +8005,8 @@
       <c r="D4" s="21"/>
       <c r="E4" s="17"/>
       <c r="F4" s="18"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="32"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="31"/>
       <c r="I4" s="22"/>
     </row>
     <row r="5" spans="1:9">
@@ -7673,8 +8018,8 @@
       <c r="D5" s="21"/>
       <c r="E5" s="17"/>
       <c r="F5" s="18"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="33"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="32"/>
       <c r="I5" s="22"/>
     </row>
     <row r="6" spans="1:9">
@@ -7686,8 +8031,8 @@
       <c r="D6" s="21"/>
       <c r="E6" s="17"/>
       <c r="F6" s="18"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="34"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="33"/>
       <c r="I6" s="22"/>
     </row>
     <row r="7" spans="1:9">
@@ -7699,8 +8044,8 @@
       <c r="D7" s="21"/>
       <c r="E7" s="17"/>
       <c r="F7" s="18"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="34"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="33"/>
       <c r="I7" s="22"/>
     </row>
     <row r="8" spans="1:9">
@@ -7712,8 +8057,8 @@
       <c r="D8" s="21"/>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="34"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="33"/>
       <c r="I8" s="22"/>
     </row>
     <row r="9" spans="1:9">
@@ -7725,8 +8070,8 @@
       <c r="D9" s="21"/>
       <c r="E9" s="17"/>
       <c r="F9" s="18"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="32"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="31"/>
       <c r="I9" s="22"/>
     </row>
     <row r="10" spans="1:9">
@@ -7738,8 +8083,8 @@
       <c r="D10" s="21"/>
       <c r="E10" s="17"/>
       <c r="F10" s="18"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="32"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="31"/>
       <c r="I10" s="22"/>
     </row>
     <row r="11" spans="1:9">
@@ -7751,8 +8096,8 @@
       <c r="D11" s="21"/>
       <c r="E11" s="17"/>
       <c r="F11" s="18"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="32"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="31"/>
       <c r="I11" s="22"/>
     </row>
     <row r="12" spans="1:9">
@@ -7764,8 +8109,8 @@
       <c r="D12" s="21"/>
       <c r="E12" s="17"/>
       <c r="F12" s="18"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="32"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="31"/>
       <c r="I12" s="22"/>
     </row>
     <row r="13" spans="1:9">
@@ -7777,8 +8122,8 @@
       <c r="D13" s="21"/>
       <c r="E13" s="17"/>
       <c r="F13" s="18"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="32"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="31"/>
       <c r="I13" s="22"/>
     </row>
     <row r="14" spans="1:9">
@@ -7790,8 +8135,8 @@
       <c r="D14" s="21"/>
       <c r="E14" s="17"/>
       <c r="F14" s="18"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="32"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="31"/>
       <c r="I14" s="22"/>
     </row>
     <row r="15" spans="1:9">
@@ -7803,8 +8148,8 @@
       <c r="D15" s="21"/>
       <c r="E15" s="17"/>
       <c r="F15" s="18"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="32"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="31"/>
       <c r="I15" s="22"/>
     </row>
     <row r="16" spans="1:9">
@@ -7816,12 +8161,12 @@
       <c r="D16" s="21"/>
       <c r="E16" s="17"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="32"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="31"/>
       <c r="I16" s="22"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="24" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="7"/>
@@ -7829,8 +8174,8 @@
       <c r="D17" s="21"/>
       <c r="E17" s="17"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="32"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="31"/>
       <c r="I17" s="22"/>
     </row>
     <row r="18" spans="1:9">
@@ -7842,8 +8187,8 @@
       <c r="D18" s="21"/>
       <c r="E18" s="17"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="32"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="31"/>
       <c r="I18" s="22"/>
     </row>
     <row r="19" spans="1:9">
@@ -7851,9 +8196,9 @@
       <c r="B19" s="8"/>
       <c r="C19" s="7"/>
       <c r="D19" s="20"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="26"/>
       <c r="H19" s="9"/>
       <c r="I19" s="22"/>
     </row>
@@ -7864,7 +8209,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="14"/>
-      <c r="G20" s="27"/>
+      <c r="G20" s="26"/>
       <c r="H20" s="9"/>
       <c r="I20" s="22"/>
     </row>
@@ -7875,7 +8220,7 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="27"/>
+      <c r="G21" s="26"/>
       <c r="H21" s="9"/>
       <c r="I21" s="22"/>
     </row>
@@ -7886,7 +8231,7 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
-      <c r="G22" s="27"/>
+      <c r="G22" s="26"/>
       <c r="H22" s="9"/>
       <c r="I22" s="22"/>
     </row>
@@ -7897,7 +8242,7 @@
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
-      <c r="G23" s="27"/>
+      <c r="G23" s="26"/>
       <c r="H23" s="9"/>
       <c r="I23" s="22"/>
     </row>
@@ -7908,7 +8253,7 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
-      <c r="G24" s="27"/>
+      <c r="G24" s="26"/>
       <c r="H24" s="9"/>
       <c r="I24" s="22"/>
     </row>
@@ -8288,923 +8633,923 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="49" t="s">
+      <c r="C1" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="E1" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="48" t="s">
+      <c r="F1" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="48" t="s">
+      <c r="G1" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="65" t="s">
+      <c r="H1" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="48" t="s">
+      <c r="I1" s="47" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
+      <c r="A2" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
       <c r="D2" s="21"/>
       <c r="E2" s="17"/>
       <c r="F2" s="11"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="56"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="55"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="62"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
+      <c r="A3" s="61"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
       <c r="D3" s="21"/>
       <c r="E3" s="17"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="56"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="55"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="62"/>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
+      <c r="A4" s="61"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
       <c r="D4" s="21"/>
       <c r="E4" s="17"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="56"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="55"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="62"/>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
+      <c r="A5" s="61"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
       <c r="D5" s="21"/>
       <c r="E5" s="17"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="56"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="55"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="62"/>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
+      <c r="A6" s="61"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
       <c r="D6" s="21"/>
       <c r="E6" s="17"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="66"/>
-      <c r="I6" s="56"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="55"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="62"/>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
+      <c r="A7" s="61"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="40"/>
       <c r="D7" s="21"/>
       <c r="E7" s="17"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="56"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="65"/>
+      <c r="I7" s="55"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="62"/>
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
+      <c r="A8" s="61"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
       <c r="D8" s="21"/>
       <c r="E8" s="17"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="66"/>
-      <c r="I8" s="56"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="65"/>
+      <c r="I8" s="55"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="62"/>
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
+      <c r="A9" s="61"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="40"/>
       <c r="D9" s="21"/>
       <c r="E9" s="17"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="66"/>
-      <c r="I9" s="56"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="65"/>
+      <c r="I9" s="55"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="62"/>
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
+      <c r="A10" s="61"/>
+      <c r="B10" s="40"/>
+      <c r="C10" s="40"/>
       <c r="D10" s="21"/>
       <c r="E10" s="17"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="66"/>
-      <c r="I10" s="56"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="65"/>
+      <c r="I10" s="55"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="62"/>
-      <c r="B11" s="41"/>
-      <c r="C11" s="41"/>
+      <c r="A11" s="61"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
       <c r="D11" s="21"/>
       <c r="E11" s="17"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="66"/>
-      <c r="I11" s="56"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="55"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="62"/>
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
+      <c r="A12" s="61"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
       <c r="D12" s="21"/>
       <c r="E12" s="17"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="66"/>
-      <c r="I12" s="56"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="55"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="62"/>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
+      <c r="A13" s="61"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="40"/>
       <c r="D13" s="21"/>
       <c r="E13" s="17"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="66"/>
-      <c r="I13" s="56"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="55"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="62"/>
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
+      <c r="A14" s="61"/>
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
       <c r="D14" s="21"/>
       <c r="E14" s="17"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="66"/>
-      <c r="I14" s="56"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="65"/>
+      <c r="I14" s="55"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="62"/>
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
+      <c r="A15" s="61"/>
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
       <c r="D15" s="21"/>
       <c r="E15" s="17"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="66"/>
-      <c r="I15" s="56"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="65"/>
+      <c r="I15" s="55"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="62"/>
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
+      <c r="A16" s="61"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="40"/>
       <c r="D16" s="21"/>
       <c r="E16" s="17"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="66"/>
-      <c r="I16" s="56"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="65"/>
+      <c r="I16" s="55"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="62"/>
-      <c r="B17" s="41"/>
-      <c r="C17" s="41"/>
+      <c r="A17" s="61"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="40"/>
       <c r="D17" s="21"/>
       <c r="E17" s="17"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="66"/>
-      <c r="I17" s="56"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="65"/>
+      <c r="I17" s="55"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="62"/>
-      <c r="B18" s="41"/>
-      <c r="C18" s="41"/>
+      <c r="A18" s="61"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="40"/>
       <c r="D18" s="21"/>
       <c r="E18" s="17"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="66"/>
-      <c r="I18" s="56"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="65"/>
+      <c r="I18" s="55"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="62"/>
-      <c r="B19" s="41"/>
-      <c r="C19" s="41"/>
+      <c r="A19" s="61"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="40"/>
       <c r="D19" s="21"/>
       <c r="E19" s="17"/>
       <c r="F19" s="11"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="66"/>
-      <c r="I19" s="56"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="55"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="62"/>
-      <c r="B20" s="41"/>
-      <c r="C20" s="41"/>
+      <c r="A20" s="61"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="40"/>
       <c r="D20" s="21"/>
       <c r="E20" s="17"/>
       <c r="F20" s="11"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="66"/>
-      <c r="I20" s="56"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="65"/>
+      <c r="I20" s="55"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="62"/>
-      <c r="B21" s="41"/>
-      <c r="C21" s="41"/>
+      <c r="A21" s="61"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="40"/>
       <c r="D21" s="21"/>
       <c r="E21" s="17"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="66"/>
-      <c r="I21" s="56"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="65"/>
+      <c r="I21" s="55"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="62"/>
-      <c r="B22" s="41"/>
-      <c r="C22" s="41"/>
+      <c r="A22" s="61"/>
+      <c r="B22" s="40"/>
+      <c r="C22" s="40"/>
       <c r="D22" s="21"/>
       <c r="E22" s="17"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="66"/>
-      <c r="I22" s="56"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="65"/>
+      <c r="I22" s="55"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="62"/>
-      <c r="B23" s="41"/>
-      <c r="C23" s="41"/>
+      <c r="A23" s="61"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="40"/>
       <c r="D23" s="21"/>
       <c r="E23" s="17"/>
       <c r="F23" s="11"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="66"/>
-      <c r="I23" s="56"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="65"/>
+      <c r="I23" s="55"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="62"/>
-      <c r="B24" s="41"/>
-      <c r="C24" s="41"/>
+      <c r="A24" s="61"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="40"/>
       <c r="D24" s="21"/>
       <c r="E24" s="17"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="66"/>
-      <c r="I24" s="56"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="65"/>
+      <c r="I24" s="55"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="62"/>
-      <c r="B25" s="41"/>
-      <c r="C25" s="41"/>
+      <c r="A25" s="61"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="40"/>
       <c r="D25" s="21"/>
       <c r="E25" s="17"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="66"/>
-      <c r="I25" s="56"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="65"/>
+      <c r="I25" s="55"/>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="62"/>
-      <c r="B26" s="41"/>
-      <c r="C26" s="41"/>
+      <c r="A26" s="61"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="40"/>
       <c r="D26" s="21"/>
       <c r="E26" s="17"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="66"/>
-      <c r="I26" s="56"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="65"/>
+      <c r="I26" s="55"/>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="62"/>
-      <c r="B27" s="41"/>
-      <c r="C27" s="41"/>
+      <c r="A27" s="61"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="40"/>
       <c r="D27" s="21"/>
       <c r="E27" s="17"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="66"/>
-      <c r="I27" s="56"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="65"/>
+      <c r="I27" s="55"/>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="62"/>
-      <c r="B28" s="41"/>
-      <c r="C28" s="41"/>
+      <c r="A28" s="61"/>
+      <c r="B28" s="40"/>
+      <c r="C28" s="40"/>
       <c r="D28" s="21"/>
       <c r="E28" s="17"/>
       <c r="F28" s="11"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="66"/>
-      <c r="I28" s="56"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="65"/>
+      <c r="I28" s="55"/>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="62"/>
-      <c r="B29" s="41"/>
-      <c r="C29" s="41"/>
+      <c r="A29" s="61"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="40"/>
       <c r="D29" s="21"/>
       <c r="E29" s="17"/>
       <c r="F29" s="11"/>
-      <c r="G29" s="40"/>
-      <c r="H29" s="66"/>
-      <c r="I29" s="56"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="65"/>
+      <c r="I29" s="55"/>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="62"/>
-      <c r="B30" s="41"/>
-      <c r="C30" s="41"/>
+      <c r="A30" s="61"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="40"/>
       <c r="D30" s="21"/>
       <c r="E30" s="17"/>
       <c r="F30" s="11"/>
-      <c r="G30" s="40"/>
-      <c r="H30" s="66"/>
-      <c r="I30" s="56"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="65"/>
+      <c r="I30" s="55"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="62"/>
-      <c r="B31" s="41"/>
-      <c r="C31" s="41"/>
+      <c r="A31" s="61"/>
+      <c r="B31" s="40"/>
+      <c r="C31" s="40"/>
       <c r="D31" s="21"/>
       <c r="E31" s="17"/>
       <c r="F31" s="11"/>
-      <c r="G31" s="40"/>
-      <c r="H31" s="66"/>
-      <c r="I31" s="56"/>
+      <c r="G31" s="39"/>
+      <c r="H31" s="65"/>
+      <c r="I31" s="55"/>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="62"/>
-      <c r="B32" s="41"/>
-      <c r="C32" s="41"/>
+      <c r="A32" s="61"/>
+      <c r="B32" s="40"/>
+      <c r="C32" s="40"/>
       <c r="D32" s="21"/>
       <c r="E32" s="17"/>
       <c r="F32" s="11"/>
-      <c r="G32" s="40"/>
-      <c r="H32" s="66"/>
-      <c r="I32" s="56"/>
+      <c r="G32" s="39"/>
+      <c r="H32" s="65"/>
+      <c r="I32" s="55"/>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="62"/>
-      <c r="B33" s="41"/>
-      <c r="C33" s="41"/>
+      <c r="A33" s="61"/>
+      <c r="B33" s="40"/>
+      <c r="C33" s="40"/>
       <c r="D33" s="21"/>
       <c r="E33" s="17"/>
       <c r="F33" s="11"/>
-      <c r="G33" s="40"/>
-      <c r="H33" s="66"/>
-      <c r="I33" s="56"/>
+      <c r="G33" s="39"/>
+      <c r="H33" s="65"/>
+      <c r="I33" s="55"/>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="62"/>
-      <c r="B34" s="41"/>
-      <c r="C34" s="41"/>
+      <c r="A34" s="61"/>
+      <c r="B34" s="40"/>
+      <c r="C34" s="40"/>
       <c r="D34" s="21"/>
       <c r="E34" s="17"/>
       <c r="F34" s="11"/>
-      <c r="G34" s="40"/>
-      <c r="H34" s="66"/>
-      <c r="I34" s="56"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="65"/>
+      <c r="I34" s="55"/>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="62"/>
-      <c r="B35" s="41"/>
-      <c r="C35" s="41"/>
+      <c r="A35" s="61"/>
+      <c r="B35" s="40"/>
+      <c r="C35" s="40"/>
       <c r="D35" s="21"/>
       <c r="E35" s="17"/>
       <c r="F35" s="11"/>
-      <c r="G35" s="40"/>
-      <c r="H35" s="66"/>
-      <c r="I35" s="56"/>
+      <c r="G35" s="39"/>
+      <c r="H35" s="65"/>
+      <c r="I35" s="55"/>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="62"/>
-      <c r="B36" s="41"/>
-      <c r="C36" s="41"/>
+      <c r="A36" s="61"/>
+      <c r="B36" s="40"/>
+      <c r="C36" s="40"/>
       <c r="D36" s="21"/>
       <c r="E36" s="17"/>
       <c r="F36" s="11"/>
-      <c r="G36" s="40"/>
-      <c r="H36" s="66"/>
-      <c r="I36" s="56"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="65"/>
+      <c r="I36" s="55"/>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" s="62"/>
-      <c r="B37" s="41"/>
-      <c r="C37" s="41"/>
+      <c r="A37" s="61"/>
+      <c r="B37" s="40"/>
+      <c r="C37" s="40"/>
       <c r="D37" s="21"/>
       <c r="E37" s="17"/>
       <c r="F37" s="11"/>
-      <c r="G37" s="40"/>
-      <c r="H37" s="66"/>
-      <c r="I37" s="56"/>
+      <c r="G37" s="39"/>
+      <c r="H37" s="65"/>
+      <c r="I37" s="55"/>
     </row>
     <row r="38" spans="1:9">
-      <c r="A38" s="62"/>
-      <c r="B38" s="41"/>
-      <c r="C38" s="41"/>
+      <c r="A38" s="61"/>
+      <c r="B38" s="40"/>
+      <c r="C38" s="40"/>
       <c r="D38" s="21"/>
       <c r="E38" s="17"/>
       <c r="F38" s="11"/>
-      <c r="G38" s="40"/>
-      <c r="H38" s="66"/>
-      <c r="I38" s="56"/>
+      <c r="G38" s="39"/>
+      <c r="H38" s="65"/>
+      <c r="I38" s="55"/>
     </row>
     <row r="39" spans="1:9">
-      <c r="A39" s="62"/>
-      <c r="B39" s="41"/>
-      <c r="C39" s="41"/>
+      <c r="A39" s="61"/>
+      <c r="B39" s="40"/>
+      <c r="C39" s="40"/>
       <c r="D39" s="21"/>
       <c r="E39" s="17"/>
       <c r="F39" s="11"/>
-      <c r="G39" s="40"/>
-      <c r="H39" s="66"/>
-      <c r="I39" s="56"/>
+      <c r="G39" s="39"/>
+      <c r="H39" s="65"/>
+      <c r="I39" s="55"/>
     </row>
     <row r="40" spans="1:9">
-      <c r="A40" s="62"/>
-      <c r="B40" s="41"/>
-      <c r="C40" s="41"/>
+      <c r="A40" s="61"/>
+      <c r="B40" s="40"/>
+      <c r="C40" s="40"/>
       <c r="D40" s="21"/>
       <c r="E40" s="17"/>
       <c r="F40" s="11"/>
-      <c r="G40" s="40"/>
-      <c r="H40" s="66"/>
-      <c r="I40" s="56"/>
+      <c r="G40" s="39"/>
+      <c r="H40" s="65"/>
+      <c r="I40" s="55"/>
     </row>
     <row r="41" spans="1:9">
-      <c r="A41" s="62"/>
-      <c r="B41" s="41"/>
-      <c r="C41" s="41"/>
+      <c r="A41" s="61"/>
+      <c r="B41" s="40"/>
+      <c r="C41" s="40"/>
       <c r="D41" s="21"/>
       <c r="E41" s="17"/>
       <c r="F41" s="11"/>
-      <c r="G41" s="40"/>
-      <c r="H41" s="66"/>
-      <c r="I41" s="56"/>
+      <c r="G41" s="39"/>
+      <c r="H41" s="65"/>
+      <c r="I41" s="55"/>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="62"/>
-      <c r="B42" s="41"/>
-      <c r="C42" s="41"/>
+      <c r="A42" s="61"/>
+      <c r="B42" s="40"/>
+      <c r="C42" s="40"/>
       <c r="D42" s="21"/>
       <c r="E42" s="17"/>
       <c r="F42" s="11"/>
-      <c r="G42" s="40"/>
-      <c r="H42" s="66"/>
-      <c r="I42" s="56"/>
+      <c r="G42" s="39"/>
+      <c r="H42" s="65"/>
+      <c r="I42" s="55"/>
     </row>
     <row r="43" spans="1:9">
-      <c r="A43" s="62"/>
-      <c r="B43" s="41"/>
-      <c r="C43" s="41"/>
+      <c r="A43" s="61"/>
+      <c r="B43" s="40"/>
+      <c r="C43" s="40"/>
       <c r="D43" s="21"/>
       <c r="E43" s="17"/>
       <c r="F43" s="11"/>
-      <c r="G43" s="40"/>
-      <c r="H43" s="66"/>
-      <c r="I43" s="56"/>
+      <c r="G43" s="39"/>
+      <c r="H43" s="65"/>
+      <c r="I43" s="55"/>
     </row>
     <row r="44" spans="1:9">
-      <c r="A44" s="62"/>
-      <c r="B44" s="41"/>
-      <c r="C44" s="41"/>
+      <c r="A44" s="61"/>
+      <c r="B44" s="40"/>
+      <c r="C44" s="40"/>
       <c r="D44" s="21"/>
       <c r="E44" s="17"/>
       <c r="F44" s="11"/>
-      <c r="G44" s="40"/>
-      <c r="H44" s="66"/>
-      <c r="I44" s="56"/>
+      <c r="G44" s="39"/>
+      <c r="H44" s="65"/>
+      <c r="I44" s="55"/>
     </row>
     <row r="45" spans="1:9">
-      <c r="A45" s="62"/>
-      <c r="B45" s="41"/>
-      <c r="C45" s="41"/>
+      <c r="A45" s="61"/>
+      <c r="B45" s="40"/>
+      <c r="C45" s="40"/>
       <c r="D45" s="21"/>
       <c r="E45" s="17"/>
       <c r="F45" s="11"/>
-      <c r="G45" s="40"/>
-      <c r="H45" s="66"/>
-      <c r="I45" s="56"/>
+      <c r="G45" s="39"/>
+      <c r="H45" s="65"/>
+      <c r="I45" s="55"/>
     </row>
     <row r="46" spans="1:9">
-      <c r="A46" s="62"/>
-      <c r="B46" s="41"/>
-      <c r="C46" s="41"/>
+      <c r="A46" s="61"/>
+      <c r="B46" s="40"/>
+      <c r="C46" s="40"/>
       <c r="D46" s="21"/>
       <c r="E46" s="17"/>
       <c r="F46" s="11"/>
-      <c r="G46" s="40"/>
-      <c r="H46" s="66"/>
-      <c r="I46" s="56"/>
+      <c r="G46" s="39"/>
+      <c r="H46" s="65"/>
+      <c r="I46" s="55"/>
     </row>
     <row r="47" spans="1:9">
-      <c r="A47" s="62"/>
-      <c r="B47" s="41"/>
-      <c r="C47" s="41"/>
+      <c r="A47" s="61"/>
+      <c r="B47" s="40"/>
+      <c r="C47" s="40"/>
       <c r="D47" s="21"/>
       <c r="E47" s="17"/>
       <c r="F47" s="11"/>
-      <c r="G47" s="40"/>
-      <c r="H47" s="66"/>
-      <c r="I47" s="56"/>
+      <c r="G47" s="39"/>
+      <c r="H47" s="65"/>
+      <c r="I47" s="55"/>
     </row>
     <row r="48" spans="1:9">
-      <c r="A48" s="62"/>
-      <c r="B48" s="41"/>
-      <c r="C48" s="41"/>
+      <c r="A48" s="61"/>
+      <c r="B48" s="40"/>
+      <c r="C48" s="40"/>
       <c r="D48" s="21"/>
       <c r="E48" s="17"/>
       <c r="F48" s="11"/>
-      <c r="G48" s="40"/>
-      <c r="H48" s="66"/>
-      <c r="I48" s="56"/>
+      <c r="G48" s="39"/>
+      <c r="H48" s="65"/>
+      <c r="I48" s="55"/>
     </row>
     <row r="49" spans="1:9">
-      <c r="A49" s="62"/>
-      <c r="B49" s="41"/>
-      <c r="C49" s="41"/>
+      <c r="A49" s="61"/>
+      <c r="B49" s="40"/>
+      <c r="C49" s="40"/>
       <c r="D49" s="21"/>
       <c r="E49" s="17"/>
       <c r="F49" s="11"/>
-      <c r="G49" s="40"/>
-      <c r="H49" s="66"/>
-      <c r="I49" s="56"/>
+      <c r="G49" s="39"/>
+      <c r="H49" s="65"/>
+      <c r="I49" s="55"/>
     </row>
     <row r="50" spans="1:9">
-      <c r="A50" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="B50" s="41"/>
-      <c r="C50" s="41"/>
+      <c r="A50" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="40"/>
+      <c r="C50" s="40"/>
       <c r="D50" s="21"/>
       <c r="E50" s="17"/>
       <c r="F50" s="11"/>
-      <c r="G50" s="40"/>
-      <c r="H50" s="67"/>
-      <c r="I50" s="41"/>
+      <c r="G50" s="39"/>
+      <c r="H50" s="66"/>
+      <c r="I50" s="40"/>
     </row>
     <row r="51" spans="1:9">
-      <c r="A51" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="B51" s="41"/>
-      <c r="C51" s="41"/>
+      <c r="A51" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="B51" s="40"/>
+      <c r="C51" s="40"/>
       <c r="D51" s="21"/>
       <c r="E51" s="17"/>
       <c r="F51" s="11"/>
-      <c r="G51" s="40"/>
-      <c r="H51" s="67"/>
-      <c r="I51" s="41"/>
+      <c r="G51" s="39"/>
+      <c r="H51" s="66"/>
+      <c r="I51" s="40"/>
     </row>
     <row r="52" spans="1:9">
-      <c r="A52" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="B52" s="41"/>
-      <c r="C52" s="41"/>
+      <c r="A52" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" s="40"/>
+      <c r="C52" s="40"/>
       <c r="D52" s="21"/>
       <c r="E52" s="17"/>
       <c r="F52" s="11"/>
-      <c r="G52" s="40"/>
-      <c r="H52" s="67"/>
-      <c r="I52" s="41"/>
+      <c r="G52" s="39"/>
+      <c r="H52" s="66"/>
+      <c r="I52" s="40"/>
     </row>
     <row r="53" spans="1:9">
-      <c r="A53" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="B53" s="41"/>
-      <c r="C53" s="41"/>
+      <c r="A53" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="B53" s="40"/>
+      <c r="C53" s="40"/>
       <c r="D53" s="21"/>
       <c r="E53" s="17"/>
       <c r="F53" s="11"/>
-      <c r="G53" s="40"/>
-      <c r="H53" s="68"/>
-      <c r="I53" s="41"/>
+      <c r="G53" s="39"/>
+      <c r="H53" s="67"/>
+      <c r="I53" s="40"/>
     </row>
     <row r="54" spans="1:9">
-      <c r="A54" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="B54" s="41"/>
-      <c r="C54" s="41"/>
+      <c r="A54" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="B54" s="40"/>
+      <c r="C54" s="40"/>
       <c r="D54" s="21"/>
       <c r="E54" s="17"/>
       <c r="F54" s="11"/>
-      <c r="G54" s="40"/>
-      <c r="H54" s="67"/>
-      <c r="I54" s="41"/>
+      <c r="G54" s="39"/>
+      <c r="H54" s="66"/>
+      <c r="I54" s="40"/>
     </row>
     <row r="55" spans="1:9">
-      <c r="A55" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="B55" s="41"/>
-      <c r="C55" s="41"/>
+      <c r="A55" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="B55" s="40"/>
+      <c r="C55" s="40"/>
       <c r="D55" s="21"/>
       <c r="E55" s="17"/>
       <c r="F55" s="11"/>
-      <c r="G55" s="40"/>
-      <c r="H55" s="67"/>
-      <c r="I55" s="41"/>
+      <c r="G55" s="39"/>
+      <c r="H55" s="66"/>
+      <c r="I55" s="40"/>
     </row>
     <row r="56" spans="1:9">
-      <c r="A56" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="B56" s="41"/>
-      <c r="C56" s="41"/>
+      <c r="A56" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="B56" s="40"/>
+      <c r="C56" s="40"/>
       <c r="D56" s="21"/>
       <c r="E56" s="17"/>
       <c r="F56" s="11"/>
-      <c r="G56" s="40"/>
-      <c r="H56" s="67"/>
-      <c r="I56" s="41"/>
+      <c r="G56" s="39"/>
+      <c r="H56" s="66"/>
+      <c r="I56" s="40"/>
     </row>
     <row r="57" spans="1:9">
-      <c r="A57" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="B57" s="41"/>
-      <c r="C57" s="41"/>
+      <c r="A57" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="B57" s="40"/>
+      <c r="C57" s="40"/>
       <c r="D57" s="21"/>
       <c r="E57" s="17"/>
       <c r="F57" s="11"/>
-      <c r="G57" s="40"/>
-      <c r="H57" s="67"/>
-      <c r="I57" s="41"/>
+      <c r="G57" s="39"/>
+      <c r="H57" s="66"/>
+      <c r="I57" s="40"/>
     </row>
     <row r="58" spans="1:9">
-      <c r="A58" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="B58" s="41"/>
-      <c r="C58" s="41"/>
+      <c r="A58" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="B58" s="40"/>
+      <c r="C58" s="40"/>
       <c r="D58" s="21"/>
       <c r="E58" s="17"/>
       <c r="F58" s="11"/>
-      <c r="G58" s="40"/>
-      <c r="H58" s="67"/>
-      <c r="I58" s="41"/>
+      <c r="G58" s="39"/>
+      <c r="H58" s="66"/>
+      <c r="I58" s="40"/>
     </row>
     <row r="59" spans="1:9">
-      <c r="A59" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="B59" s="41"/>
-      <c r="C59" s="41"/>
+      <c r="A59" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="B59" s="40"/>
+      <c r="C59" s="40"/>
       <c r="D59" s="21"/>
       <c r="E59" s="17"/>
       <c r="F59" s="11"/>
-      <c r="G59" s="40"/>
-      <c r="H59" s="67"/>
-      <c r="I59" s="41"/>
+      <c r="G59" s="39"/>
+      <c r="H59" s="66"/>
+      <c r="I59" s="40"/>
     </row>
     <row r="60" spans="1:9">
-      <c r="A60" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="B60" s="41"/>
-      <c r="C60" s="41"/>
+      <c r="A60" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="B60" s="40"/>
+      <c r="C60" s="40"/>
       <c r="D60" s="21"/>
       <c r="E60" s="17"/>
       <c r="F60" s="11"/>
-      <c r="G60" s="40"/>
-      <c r="H60" s="67"/>
-      <c r="I60" s="41"/>
+      <c r="G60" s="39"/>
+      <c r="H60" s="66"/>
+      <c r="I60" s="40"/>
     </row>
     <row r="61" spans="1:9">
-      <c r="A61" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="B61" s="41"/>
-      <c r="C61" s="41"/>
+      <c r="A61" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="B61" s="40"/>
+      <c r="C61" s="40"/>
       <c r="D61" s="21"/>
       <c r="E61" s="17"/>
       <c r="F61" s="11"/>
-      <c r="G61" s="40"/>
-      <c r="H61" s="67"/>
-      <c r="I61" s="41"/>
+      <c r="G61" s="39"/>
+      <c r="H61" s="66"/>
+      <c r="I61" s="40"/>
     </row>
     <row r="62" spans="1:9">
-      <c r="A62" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="B62" s="41"/>
-      <c r="C62" s="41"/>
+      <c r="A62" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="B62" s="40"/>
+      <c r="C62" s="40"/>
       <c r="D62" s="21"/>
       <c r="E62" s="17"/>
       <c r="F62" s="11"/>
-      <c r="G62" s="40"/>
-      <c r="H62" s="67"/>
-      <c r="I62" s="41"/>
+      <c r="G62" s="39"/>
+      <c r="H62" s="66"/>
+      <c r="I62" s="40"/>
     </row>
     <row r="63" spans="1:9">
-      <c r="A63" s="63"/>
-      <c r="B63" s="41"/>
-      <c r="C63" s="41"/>
+      <c r="A63" s="62"/>
+      <c r="B63" s="40"/>
+      <c r="C63" s="40"/>
       <c r="D63" s="21"/>
       <c r="E63" s="12"/>
       <c r="F63" s="11"/>
-      <c r="G63" s="40"/>
-      <c r="H63" s="69"/>
-      <c r="I63" s="41"/>
+      <c r="G63" s="39"/>
+      <c r="H63" s="68"/>
+      <c r="I63" s="40"/>
     </row>
     <row r="64" spans="1:9">
-      <c r="A64" s="63"/>
-      <c r="B64" s="41"/>
-      <c r="C64" s="41"/>
+      <c r="A64" s="62"/>
+      <c r="B64" s="40"/>
+      <c r="C64" s="40"/>
       <c r="D64" s="21"/>
       <c r="E64" s="12"/>
       <c r="F64" s="11"/>
-      <c r="G64" s="40"/>
-      <c r="H64" s="69"/>
-      <c r="I64" s="41"/>
+      <c r="G64" s="39"/>
+      <c r="H64" s="68"/>
+      <c r="I64" s="40"/>
     </row>
     <row r="65" spans="1:9">
-      <c r="A65" s="63"/>
-      <c r="B65" s="41"/>
-      <c r="C65" s="41"/>
+      <c r="A65" s="62"/>
+      <c r="B65" s="40"/>
+      <c r="C65" s="40"/>
       <c r="D65" s="21"/>
       <c r="E65" s="12"/>
       <c r="F65" s="11"/>
-      <c r="G65" s="40"/>
-      <c r="H65" s="69"/>
-      <c r="I65" s="41"/>
+      <c r="G65" s="39"/>
+      <c r="H65" s="68"/>
+      <c r="I65" s="40"/>
     </row>
     <row r="66" spans="1:9">
-      <c r="A66" s="63"/>
-      <c r="B66" s="41"/>
-      <c r="C66" s="41"/>
+      <c r="A66" s="62"/>
+      <c r="B66" s="40"/>
+      <c r="C66" s="40"/>
       <c r="D66" s="21"/>
       <c r="E66" s="12"/>
       <c r="F66" s="11"/>
-      <c r="G66" s="40"/>
-      <c r="H66" s="69"/>
-      <c r="I66" s="41"/>
+      <c r="G66" s="39"/>
+      <c r="H66" s="68"/>
+      <c r="I66" s="40"/>
     </row>
     <row r="67" spans="1:9">
-      <c r="A67" s="63"/>
-      <c r="B67" s="41"/>
-      <c r="C67" s="41"/>
+      <c r="A67" s="62"/>
+      <c r="B67" s="40"/>
+      <c r="C67" s="40"/>
       <c r="D67" s="21"/>
       <c r="E67" s="12"/>
       <c r="F67" s="11"/>
-      <c r="G67" s="40"/>
-      <c r="H67" s="69"/>
-      <c r="I67" s="41"/>
+      <c r="G67" s="39"/>
+      <c r="H67" s="68"/>
+      <c r="I67" s="40"/>
     </row>
     <row r="68" spans="1:9">
-      <c r="A68" s="63"/>
-      <c r="B68" s="41"/>
-      <c r="C68" s="41"/>
+      <c r="A68" s="62"/>
+      <c r="B68" s="40"/>
+      <c r="C68" s="40"/>
       <c r="D68" s="21"/>
       <c r="E68" s="12"/>
       <c r="F68" s="11"/>
-      <c r="G68" s="40"/>
-      <c r="H68" s="69"/>
-      <c r="I68" s="41"/>
+      <c r="G68" s="39"/>
+      <c r="H68" s="68"/>
+      <c r="I68" s="40"/>
     </row>
     <row r="69" spans="1:9">
-      <c r="A69" s="63"/>
-      <c r="B69" s="41"/>
-      <c r="C69" s="41"/>
+      <c r="A69" s="62"/>
+      <c r="B69" s="40"/>
+      <c r="C69" s="40"/>
       <c r="D69" s="21"/>
       <c r="E69" s="12"/>
       <c r="F69" s="11"/>
-      <c r="G69" s="40"/>
-      <c r="H69" s="69"/>
-      <c r="I69" s="41"/>
+      <c r="G69" s="39"/>
+      <c r="H69" s="68"/>
+      <c r="I69" s="40"/>
     </row>
     <row r="70" spans="1:9">
-      <c r="A70" s="63"/>
-      <c r="B70" s="41"/>
-      <c r="C70" s="41"/>
+      <c r="A70" s="62"/>
+      <c r="B70" s="40"/>
+      <c r="C70" s="40"/>
       <c r="D70" s="21"/>
       <c r="E70" s="12"/>
       <c r="F70" s="11"/>
-      <c r="G70" s="40"/>
-      <c r="H70" s="69"/>
-      <c r="I70" s="41"/>
+      <c r="G70" s="39"/>
+      <c r="H70" s="68"/>
+      <c r="I70" s="40"/>
     </row>
     <row r="71" spans="1:9">
-      <c r="A71" s="63"/>
-      <c r="B71" s="41"/>
-      <c r="C71" s="41"/>
+      <c r="A71" s="62"/>
+      <c r="B71" s="40"/>
+      <c r="C71" s="40"/>
       <c r="D71" s="21"/>
       <c r="E71" s="12"/>
       <c r="F71" s="11"/>
-      <c r="G71" s="40"/>
-      <c r="H71" s="69"/>
-      <c r="I71" s="41"/>
+      <c r="G71" s="39"/>
+      <c r="H71" s="68"/>
+      <c r="I71" s="40"/>
     </row>
     <row r="72" spans="1:9">
-      <c r="A72" s="63"/>
-      <c r="B72" s="41"/>
-      <c r="C72" s="41"/>
+      <c r="A72" s="62"/>
+      <c r="B72" s="40"/>
+      <c r="C72" s="40"/>
       <c r="D72" s="21"/>
       <c r="E72" s="12"/>
       <c r="F72" s="11"/>
-      <c r="G72" s="40"/>
-      <c r="H72" s="69"/>
-      <c r="I72" s="41"/>
+      <c r="G72" s="39"/>
+      <c r="H72" s="68"/>
+      <c r="I72" s="40"/>
     </row>
     <row r="73" spans="1:9">
-      <c r="A73" s="63"/>
-      <c r="B73" s="41"/>
-      <c r="C73" s="41"/>
+      <c r="A73" s="62"/>
+      <c r="B73" s="40"/>
+      <c r="C73" s="40"/>
       <c r="D73" s="21"/>
       <c r="E73" s="12"/>
       <c r="F73" s="11"/>
-      <c r="G73" s="40"/>
-      <c r="H73" s="69"/>
-      <c r="I73" s="41"/>
+      <c r="G73" s="39"/>
+      <c r="H73" s="68"/>
+      <c r="I73" s="40"/>
     </row>
     <row r="74" spans="1:9">
-      <c r="A74" s="63"/>
-      <c r="B74" s="41"/>
-      <c r="C74" s="41"/>
+      <c r="A74" s="62"/>
+      <c r="B74" s="40"/>
+      <c r="C74" s="40"/>
       <c r="D74" s="21"/>
       <c r="E74" s="12"/>
       <c r="F74" s="11"/>
-      <c r="G74" s="40"/>
-      <c r="H74" s="69"/>
-      <c r="I74" s="41"/>
+      <c r="G74" s="39"/>
+      <c r="H74" s="68"/>
+      <c r="I74" s="40"/>
     </row>
     <row r="75" spans="1:9">
-      <c r="A75" s="63"/>
+      <c r="A75" s="62"/>
       <c r="B75" s="17"/>
-      <c r="C75" s="41"/>
+      <c r="C75" s="40"/>
       <c r="D75" s="21"/>
       <c r="E75" s="17"/>
       <c r="F75" s="11"/>
-      <c r="G75" s="40"/>
-      <c r="H75" s="69"/>
+      <c r="G75" s="39"/>
+      <c r="H75" s="68"/>
       <c r="I75" s="12"/>
     </row>
     <row r="76" spans="1:9">
-      <c r="D76" s="70"/>
-      <c r="F76" s="60"/>
+      <c r="D76" s="69"/>
+      <c r="F76" s="59"/>
     </row>
     <row r="77" spans="1:9">
-      <c r="D77" s="70"/>
-      <c r="F77" s="60"/>
+      <c r="D77" s="69"/>
+      <c r="F77" s="59"/>
     </row>
     <row r="78" spans="1:9">
-      <c r="D78" s="70"/>
-      <c r="F78" s="60"/>
+      <c r="D78" s="69"/>
+      <c r="F78" s="59"/>
     </row>
     <row r="79" spans="1:9">
-      <c r="D79" s="70"/>
-      <c r="F79" s="60"/>
+      <c r="D79" s="69"/>
+      <c r="F79" s="59"/>
     </row>
     <row r="80" spans="1:9">
-      <c r="D80" s="70"/>
-      <c r="F80" s="60"/>
+      <c r="D80" s="69"/>
+      <c r="F80" s="59"/>
     </row>
     <row r="81" spans="4:6">
-      <c r="D81" s="70"/>
-      <c r="F81" s="60"/>
+      <c r="D81" s="69"/>
+      <c r="F81" s="59"/>
     </row>
     <row r="82" spans="4:6">
-      <c r="D82" s="70"/>
-      <c r="F82" s="60"/>
+      <c r="D82" s="69"/>
+      <c r="F82" s="59"/>
     </row>
     <row r="83" spans="4:6">
-      <c r="D83" s="70"/>
-      <c r="F83" s="60"/>
+      <c r="D83" s="69"/>
+      <c r="F83" s="59"/>
     </row>
     <row r="84" spans="4:6">
-      <c r="D84" s="70"/>
-      <c r="F84" s="60"/>
+      <c r="D84" s="69"/>
+      <c r="F84" s="59"/>
     </row>
     <row r="85" spans="4:6">
-      <c r="D85" s="70"/>
-      <c r="F85" s="60"/>
+      <c r="D85" s="69"/>
+      <c r="F85" s="59"/>
     </row>
     <row r="86" spans="4:6">
-      <c r="D86" s="70"/>
-      <c r="F86" s="60"/>
+      <c r="D86" s="69"/>
+      <c r="F86" s="59"/>
     </row>
     <row r="87" spans="4:6">
-      <c r="D87" s="70"/>
-      <c r="F87" s="60"/>
+      <c r="D87" s="69"/>
+      <c r="F87" s="59"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
@@ -9240,49 +9585,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-543957</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-543957</Url>
-      <Description>QAFFA7D2F2TC-2102087286-543957</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="45" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="489f8e21b9a70c9d7a16fa4497d5b683">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2f3b4a981d4ba54fcf1b71789fe9b31f" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -9666,7 +9968,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -9716,7 +10018,7 @@
 </spe:Receivers>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -9725,18 +10027,61 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-543957</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-543957</Url>
+      <Description>QAFFA7D2F2TC-2102087286-543957</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{085BABE9-4E2E-49DF-BDAB-445AA4DA56A3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{085BABE9-4E2E-49DF-BDAB-445AA4DA56A3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>